--- a/99_Others/Supplement.xlsx
+++ b/99_Others/Supplement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\portfolio\99_Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1F2AF3-92FF-4741-8C3A-3A3E0627956E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2484527-9E6A-4CAF-A4F7-853B90A40F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC6BFF53-95C0-4792-9171-E38E58216003}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{DC6BFF53-95C0-4792-9171-E38E58216003}"/>
   </bookViews>
   <sheets>
     <sheet name="言語別" sheetId="2" r:id="rId1"/>
@@ -2183,34 +2183,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>実務でC言語を取り扱う機会があったため学習。配列がポインタであることなど理解しました。</t>
-    <rPh sb="0" eb="2">
-      <t>ジツム</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>ｃ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>アツカ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>キカイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ガクシュウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ハイレツ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>リカイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Javaの現場に参画時に通勤時間で読んでいました。デバッグや実行、リランチなどはできるが、時間効率などにつながる設定などは行えていない</t>
     <rPh sb="5" eb="7">
       <t>ゲンバ</t>
@@ -2549,6 +2521,37 @@
     </rPh>
     <rPh sb="30" eb="32">
       <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実務でC言語を取り扱う機会があったため学習。ポインタがメモリアドレスを指し示しているという概念を学びました。</t>
+    <rPh sb="0" eb="2">
+      <t>ジツム</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ｃ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アツカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>サシシメ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ガイネン</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>マナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3106,7 +3109,7 @@
         <v>124</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>122</v>
@@ -3169,10 +3172,10 @@
         <v>125</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F10" s="1">
         <v>2026</v>
@@ -3751,7 +3754,7 @@
         <v>26</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>30</v>
@@ -4044,7 +4047,7 @@
         <v>54</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>90</v>
@@ -4086,7 +4089,7 @@
         <v>64</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1">
@@ -4097,7 +4100,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B11" s="1" t="s">
         <v>49</v>
       </c>
@@ -4105,7 +4108,7 @@
         <v>55</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>68</v>
@@ -4145,7 +4148,7 @@
         <v>57</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1">
@@ -4202,7 +4205,7 @@
         <v>26</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1">
@@ -4221,7 +4224,7 @@
         <v>56</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1">
@@ -4240,7 +4243,7 @@
         <v>67</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1">

--- a/99_Others/Supplement.xlsx
+++ b/99_Others/Supplement.xlsx
@@ -1,28 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\portfolio\99_Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2484527-9E6A-4CAF-A4F7-853B90A40F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55371FD7-103B-47FE-88D9-3075060757A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{DC6BFF53-95C0-4792-9171-E38E58216003}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC6BFF53-95C0-4792-9171-E38E58216003}"/>
   </bookViews>
   <sheets>
-    <sheet name="言語別" sheetId="2" r:id="rId1"/>
-    <sheet name="アプリ別" sheetId="1" r:id="rId2"/>
-    <sheet name="教材別" sheetId="3" r:id="rId3"/>
-    <sheet name="業務別" sheetId="4" r:id="rId4"/>
+    <sheet name="仕事の進め方や考え方" sheetId="5" r:id="rId1"/>
+    <sheet name="言語別" sheetId="2" r:id="rId2"/>
+    <sheet name="業務別" sheetId="4" r:id="rId3"/>
+    <sheet name="教材別" sheetId="3" r:id="rId4"/>
+    <sheet name="ツール別" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">アプリ別!$B$5:$H$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">教材別!$B$5:$H$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">業務別!$B$5:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">言語別!$B$5:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ツール別!$B$5:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">教材別!$B$5:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">業務別!$B$5:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">言語別!$B$5:$H$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">仕事の進め方や考え方!$A$1:$O$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="220">
   <si>
     <t>Slack</t>
   </si>
@@ -555,16 +557,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メンションなど使用経験があります。</t>
-    <rPh sb="7" eb="9">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ケイケン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Batch</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -579,13 +571,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>サードパーティアプリ別</t>
-    <rPh sb="10" eb="11">
-      <t>ベツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>教材別</t>
     <rPh sb="0" eb="2">
       <t>キョウザイ</t>
@@ -772,10 +757,6 @@
     <rPh sb="31" eb="33">
       <t>シヨウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Git</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -950,28 +931,6 @@
       <t>タイオウ</t>
     </rPh>
     <rPh sb="19" eb="21">
-      <t>ケイケン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>障害発生時の事象の報告など経験あり</t>
-    <rPh sb="0" eb="2">
-      <t>ショウガイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジショウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ホウコク</t>
-    </rPh>
-    <rPh sb="13" eb="15">
       <t>ケイケン</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1288,164 +1247,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ネットワークドライブの取得、加工処理
-・C#の関数をimportしてJSONを設定ファイルとしたiniファイル情報取得処理</t>
-    <rPh sb="12" eb="14">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カコウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>カンスウ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>ショリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Stirling</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>バイナリエディタ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・ライブラリを使用しないJSONデータの作成や構文チェックおよび、制御文字のエスケープ対応
-・ライブラリを使用しないXMLデータの作成や構文チェック、実体参照文字のエスケープ対応
-・パック10進数からゾーン10進数への変換処理作成
-・処理の追加に伴うエラーメッセージの追加
-・通帳MSデータ読み取り後のデータの加工処理
-・他プロセスの変更したグローバル変数などと連携した処理の実装
-・画面項目の変更に伴う入力チェック処理の追加</t>
-    <rPh sb="7" eb="9">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>コウブン</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>セイギョ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="68" eb="70">
-      <t>コウブン</t>
-    </rPh>
-    <rPh sb="75" eb="77">
-      <t>ジッタイ</t>
-    </rPh>
-    <rPh sb="77" eb="79">
-      <t>サンショウ</t>
-    </rPh>
-    <rPh sb="79" eb="81">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="87" eb="89">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="96" eb="98">
-      <t>シンスウ</t>
-    </rPh>
-    <rPh sb="105" eb="107">
-      <t>シンスウ</t>
-    </rPh>
-    <rPh sb="109" eb="111">
-      <t>ヘンカン</t>
-    </rPh>
-    <rPh sb="111" eb="113">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="113" eb="115">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="117" eb="119">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="120" eb="122">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="123" eb="124">
-      <t>トモナ</t>
-    </rPh>
-    <rPh sb="134" eb="136">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="138" eb="140">
-      <t>ツウチョウ</t>
-    </rPh>
-    <rPh sb="145" eb="146">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="147" eb="148">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="149" eb="150">
-      <t>ゴ</t>
-    </rPh>
-    <rPh sb="155" eb="157">
-      <t>カコウ</t>
-    </rPh>
-    <rPh sb="157" eb="159">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="161" eb="162">
-      <t>ホカ</t>
-    </rPh>
-    <rPh sb="167" eb="169">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="176" eb="178">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="181" eb="183">
-      <t>レンケイ</t>
-    </rPh>
-    <rPh sb="185" eb="187">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="188" eb="190">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="200" eb="201">
-      <t>トモナ</t>
-    </rPh>
-    <rPh sb="202" eb="204">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="208" eb="210">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="211" eb="213">
-      <t>ツイカ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1495,60 +1301,6 @@
     </rPh>
     <rPh sb="22" eb="24">
       <t>タントウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・通販サイトの期間限定セールロジック修正（2BUYや消費税など）
-・買い物かごストック処理の修正</t>
-    <rPh sb="1" eb="3">
-      <t>ツウハン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>キカン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="26" eb="29">
-      <t>ショウヒゼイ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>モノ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>シュウセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・パンくずリストの修正
-・コントローラーの修正
-・DTOの修正
-・ログイン時の入力チェック</t>
-    <rPh sb="9" eb="11">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ニュウリョク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1849,38 +1601,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>業界でのシェア率が高く、普段使いしています。</t>
-    <rPh sb="0" eb="2">
-      <t>ギョウカイ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>リツ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>フダン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ヅカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ほかブラウザから見えるHTMLレイアウトの調査などに使用することがありました。</t>
-    <rPh sb="8" eb="9">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>チョウサ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>時刻指定保存機能を使用してスクリーンセーバー中のアプリの画面状態を撮影して障害の発生条件を特定した実績があります。</t>
     <rPh sb="0" eb="2">
       <t>ジコク</t>
@@ -1995,41 +1715,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>環境構築と使用ができます。
-実務ではコンパイル担当が別に存在したので、実務的な使用については懸念あり。</t>
-    <rPh sb="0" eb="2">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウチク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ジツム</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>タントウ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="35" eb="38">
-      <t>ジツムテキ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>ケネン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ファイルの自動バックアップ、排他制御を設定した使い方ができます。</t>
     <rPh sb="5" eb="7">
       <t>ジドウ</t>
@@ -2163,26 +1848,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>コマンドラインでGit add～Git pushまでの操作ができます。
-履歴の取り消しなどに不安があります。</t>
-    <rPh sb="27" eb="29">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>リレキ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ケ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>フアン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Javaの現場に参画時に通勤時間で読んでいました。デバッグや実行、リランチなどはできるが、時間効率などにつながる設定などは行えていない</t>
     <rPh sb="5" eb="7">
       <t>ゲンバ</t>
@@ -2390,54 +2055,266 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Webデザインの職業訓練に半年ほど専門で通っていたので、体系的な知識があります。1からファイルを作成し、Jqueryの実装やWordPressへの対応など行いポートフォリオ作品を作成した経験があります。</t>
-    <rPh sb="8" eb="10">
-      <t>ショクギョウ</t>
-    </rPh>
+    <t>ブックやシート、セルの中で完結するような操作が主ですが、実装経験があります。</t>
+    <rPh sb="11" eb="12">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンケツ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実務でC言語を取り扱う機会があったため学習。ポインタがアドレスを指し示す概念であることなど理解しました。</t>
+    <rPh sb="0" eb="2">
+      <t>ジツム</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ｃ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アツカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>サシシメ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ガイネン</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>リカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>XMLの構文チェックなどに使用していた経験があります。</t>
+    <rPh sb="4" eb="6">
+      <t>コウブン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Internet explorer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ネットワークドライブの取得、加工処理
+・C#の関数をimportしてJSONを設定ファイルとしたiniファイル情報取得処理
+・ストアアプリのバージョンチェック
+・サービス実行状態のチェック</t>
+    <rPh sb="12" eb="14">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カコウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コマンドラインでGit add～Git pushまでの操作ができます。
+履歴の取り消しなどに、自分の知らない処理がないかなど不安があります。</t>
+    <rPh sb="27" eb="29">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>フアン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>thunderbird</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メーラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Oracle SQL Developer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IP Messenger</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ツール別</t>
+    <rPh sb="3" eb="4">
+      <t>ベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リモートデスクトップ接続</t>
     <rPh sb="10" eb="12">
-      <t>クンレン</t>
+      <t>セツゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Git Bash</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Source Tree</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>毎日、プルする作法を身に着けております。</t>
+    <rPh sb="0" eb="2">
+      <t>マイニチ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サホウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メンションを指定する作法を身に着けております。</t>
+    <rPh sb="6" eb="8">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サホウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メッセージの送信やログの設定などができます。</t>
+    <rPh sb="6" eb="8">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>障害発生時の事象の報告など経験あり。再現手順を記載することを意識していました。</t>
+    <rPh sb="0" eb="2">
+      <t>ショウガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジショウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホウコク</t>
     </rPh>
     <rPh sb="13" eb="15">
-      <t>ハントシ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>センモン</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>カヨ</t>
-    </rPh>
-    <rPh sb="28" eb="31">
-      <t>タイケイテキ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>チシキ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="77" eb="78">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="86" eb="88">
-      <t>サクヒン</t>
-    </rPh>
-    <rPh sb="89" eb="91">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="93" eb="95">
       <t>ケイケン</t>
     </rPh>
+    <rPh sb="18" eb="20">
+      <t>サイゲン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>イシキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>環境構築と使用ができます。
-実務ではあまり使用する機会に恵まれなかったため、jarやwar、クラスライブラリ、pomなど不安あり。</t>
+実務ではコンパイル担当が別に存在したので、言語コード設定など実務的な使用については懸念あり。</t>
     <rPh sb="0" eb="2">
       <t>カンキョウ</t>
     </rPh>
@@ -2450,6 +2327,47 @@
     <rPh sb="14" eb="16">
       <t>ジツム</t>
     </rPh>
+    <rPh sb="23" eb="25">
+      <t>タントウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ゲンゴ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="44" eb="47">
+      <t>ジツムテキ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ケネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>環境構築と使用ができます。
+実務ではあまり使用する機会に恵まれなかったため、jarやwar、クラスライブラリ、pomのほか、まだまだ知らなそうなことが多そうと考えています。</t>
+    <rPh sb="0" eb="2">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジツム</t>
+    </rPh>
     <rPh sb="21" eb="23">
       <t>シヨウ</t>
     </rPh>
@@ -2459,13 +2377,313 @@
     <rPh sb="28" eb="29">
       <t>メグ</t>
     </rPh>
-    <rPh sb="60" eb="62">
-      <t>フアン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・シートの値を引数とした正規表現の作成処理
+    <rPh sb="66" eb="67">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゾンビセッションを残さないように接続を終了する作法を心得ております。</t>
+    <rPh sb="9" eb="10">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サホウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ココロエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファイルなどを送信する際にウイルスチェックをする癖がついております。</t>
+    <rPh sb="7" eb="9">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>クセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ほかブラウザから見えるHTMLレイアウトの調査などに使用することがあります。</t>
+    <rPh sb="8" eb="9">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テキストエディタに実行するSQLのシナリオを書いてから、実行する癖があります。
+例)Savepoint→Select→Delete→RollBack</t>
+    <rPh sb="9" eb="11">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>クセ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>怪しいメールのマクロを実行しない作法を心得ており、
+万が一のウイルス感染時のLAN抜き、報告対応ができます。</t>
+    <rPh sb="0" eb="1">
+      <t>アヤ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サホウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ココロエ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>マン</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>カンセン</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ホウコク</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ライブラリを使用しないJSONデータの作成や構文チェックおよび、制御文字のエスケープ対応
+・ライブラリを使用しないXMLデータの作成や構文チェック、実体参照文字のエスケープ対応
+・パック10進数からゾーン10進数への変換処理作成
+・処理の追加に伴うエラーメッセージの追加・他プロセスの変更したグローバル変数などと連携した処理の実装
+・画面項目の変更に伴う入力チェック処理の追加</t>
+    <rPh sb="7" eb="9">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>コウブン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>コウブン</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ジッタイ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>シンスウ</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>シンスウ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="113" eb="115">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>トモナ</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="137" eb="138">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="143" eb="145">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="152" eb="154">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="157" eb="159">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="161" eb="163">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="164" eb="166">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="176" eb="177">
+      <t>トモナ</t>
+    </rPh>
+    <rPh sb="178" eb="180">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="184" eb="186">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="187" eb="189">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・通販サイトの期間限定セールロジック修正（2BUY価格や消費税など）
+・買い物かごストック処理の修正</t>
+    <rPh sb="1" eb="3">
+      <t>ツウハン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キカン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カカク</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>ショウヒゼイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・設計書レイアウト確認テスト後のパンくずリストの文言修正
+・コントローラーの修正
+・DBに命名規則変更伴うDTOのフィールド名修正
+・ログイン時の入力チェック(メールアドレスの@の有無や記号の有無のチェック）</t>
+    <rPh sb="1" eb="4">
+      <t>セッケイショ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>モンゴン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>トモナ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>ウム</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>キゴウ</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>ウム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・シートの値を引数とした正規表現の作成およびクリップボードへの格納処理
 ・フォームコントロールを契機としたPDF出力や外部ブック保存、自動フィルタ</t>
     <rPh sb="5" eb="6">
       <t>アタイ</t>
@@ -2482,77 +2700,225 @@
     <rPh sb="17" eb="19">
       <t>サクセイ</t>
     </rPh>
-    <rPh sb="19" eb="21">
+    <rPh sb="31" eb="33">
+      <t>カクノウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
       <t>ショリ</t>
     </rPh>
-    <rPh sb="34" eb="36">
+    <rPh sb="48" eb="50">
       <t>ケイキ</t>
     </rPh>
-    <rPh sb="42" eb="44">
+    <rPh sb="56" eb="58">
       <t>シュツリョク</t>
     </rPh>
-    <rPh sb="45" eb="47">
+    <rPh sb="59" eb="61">
       <t>ガイブ</t>
     </rPh>
-    <rPh sb="50" eb="52">
+    <rPh sb="64" eb="66">
       <t>ホゾン</t>
     </rPh>
-    <rPh sb="53" eb="55">
+    <rPh sb="67" eb="69">
       <t>ジドウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ブックやシート、セルの中で完結するような操作が主ですが、実装経験があります。</t>
-    <rPh sb="11" eb="12">
-      <t>ナカ</t>
+    <t>Webデザインの職業訓練に半年ほど専門で通っていたので、体系的な知識があります。1からファイルを作成し、Jqueryの実装やWordPressへの対応など行いポートフォリオ作品を作成した経験があります。作成レイアウトは横幅がブラウザに収まることを前提としたレイアウトで作成する癖があります。</t>
+    <rPh sb="8" eb="10">
+      <t>ショクギョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>クンレン</t>
     </rPh>
     <rPh sb="13" eb="15">
-      <t>カンケツ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
+      <t>ハントシ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>センモン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カヨ</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>タイケイテキ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>チシキ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
       <t>ジッソウ</t>
     </rPh>
-    <rPh sb="30" eb="32">
+    <rPh sb="73" eb="75">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>サクヒン</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>実務でC言語を取り扱う機会があったため学習。ポインタがメモリアドレスを指し示しているという概念を学びました。</t>
-    <rPh sb="0" eb="2">
-      <t>ジツム</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>ｃ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>アツカ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>キカイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ガクシュウ</t>
-    </rPh>
-    <rPh sb="35" eb="38">
-      <t>サシシメ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ガイネン</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>マナ</t>
-    </rPh>
+    <rPh sb="101" eb="103">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>ヨコハバ</t>
+    </rPh>
+    <rPh sb="117" eb="118">
+      <t>オサ</t>
+    </rPh>
+    <rPh sb="123" eb="125">
+      <t>ゼンテイ</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="138" eb="139">
+      <t>クセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>障害多発で連鎖退場するような口うるさい現場を経験しているため、できれば最低限、パワハラチックなことがない人が好ましい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題は何十年も在籍していないとわからない細かで複雑な業務仕様が絡んだ実装かそうでない実装かだけだと考えております。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>理由は、優秀な人の負担からくる連鎖退職、実装を任されないフラストレーションからくる連鎖退職が起こることが目に見えているからです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>優秀な人は負担が減ることを望み、実装を任されない人はスキルアップしない将来に不安を抱くものだと考えています。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>年下や後輩に対して、怒ったりなどはしない性格だと心得ております。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕事の進め方や考え方などについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下、現場のミスマッチを防ぐために私の考えや求めていることを記載いたします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まず、どんな軽い仕事でもバッファを消費することなく、いち早く終わらせるべきだと考えております。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しかし、仕事がない場合、自分から積極的にタスクをもらいに行くべきか、マネジメントサイドからの指示を待つべきなのかはいつも迷います。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>理由としては完ぺきにマネジメントをコントロールしているマネージャーから見るとプレイヤーからの質問は邪魔になる恐れがあるからです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もし、仮に放置されたとしても業務を知っていれば、業務自動化を行えるだけの非コンパイル言語の知識は保有しております。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>また口頭ベースでスピーディーな連携で作業を進める現場なのか、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バグ管理表やＷＢＳなどドキュメントベースで進めていく口数少ない現場なのかも早く知っておくことで</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>より円滑な仕事ができると考えております。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>言語自体の理解については、後から参画しても追いつくものだと考えております。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なぜなら、事実上、必要となるライブラリや実装のパターンには限りがあるからです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>できればテストのみでなく実装させていただけるととてもうれしく思います。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なおかつ優秀な人のワンマンチームで構成されていないチームが好ましいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ただし、事務的で不愛想な人物だと振り返っています。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>面談での私への質問について</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>疑問の余地なく疑問に思ったことは全て質問していただきたいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1.仕事の進め方やルールについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.言語について</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.実装について</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.リーダーについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5.自身の性格について</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特別、一つの言語にこだわる姿勢はなく、まずは高圧的な態度をなるべく使用せず、かつプロジェクトが炎上していないことを重視します。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その次に言語としては将来性のありそうな言語や伝統のある言語であれば特に問題ないと考えています。</t>
+    <rPh sb="22" eb="24">
+      <t>デントウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ゲンゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>熟練のC言語プログラマでもメモリ管理を失敗するときや忘れるときはあるので、威圧的な態度や言葉で解決を目指すのではなく</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>具体的な改善を求める姿勢のあるリーダーと、ご一緒させていただきたいと考えております。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>邪魔をしないために質問を控えた結果、マネージャーからは「仕事をもらいに来るのを待っていた」なんて言われてしまうといった状況に</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なってしまうのはもったいないので、こういった事態になることを防げればと考えております。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2674,7 +3040,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2697,6 +3063,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3032,6 +3404,184 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE6DB4A-4BEF-422E-B305-35232E53060A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:B41"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B2" s="9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B6" s="9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B18" s="9" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B22" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B25" s="9" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B26" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B27" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B28" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B29" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B31" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B32" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B36" s="9" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B37" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B38" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B40" s="9" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B41" t="s">
+        <v>208</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="97" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="14" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA1598E-5D04-43CF-BF63-14626A784353}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3049,12 +3599,12 @@
   <sheetData>
     <row r="2" spans="2:8" ht="30" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3068,30 +3618,30 @@
         <v>17</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="169.5" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:8" ht="150.75" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B6" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="F6" s="1">
         <v>2026</v>
@@ -3106,13 +3656,13 @@
         <v>74</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F7" s="1">
         <v>2026</v>
@@ -3124,16 +3674,16 @@
     </row>
     <row r="8" spans="2:8" ht="56.25" x14ac:dyDescent="0.4">
       <c r="B8" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F8" s="1">
         <v>2026</v>
@@ -3143,18 +3693,18 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:8" ht="75" x14ac:dyDescent="0.4">
       <c r="B9" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="F9" s="1">
         <v>2026</v>
@@ -3169,13 +3719,13 @@
         <v>75</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="F10" s="1">
         <v>2026</v>
@@ -3187,16 +3737,16 @@
     </row>
     <row r="11" spans="2:8" ht="56.25" x14ac:dyDescent="0.4">
       <c r="B11" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F11" s="1">
         <v>2026</v>
@@ -3211,13 +3761,13 @@
         <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="F12" s="1">
         <v>2026</v>
@@ -3229,16 +3779,16 @@
     </row>
     <row r="13" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B13" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="F13" s="1">
         <v>2018</v>
@@ -3250,13 +3800,13 @@
     </row>
     <row r="14" spans="2:8" ht="56.25" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="1">
@@ -3269,22 +3819,22 @@
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B17" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B18" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3295,661 +3845,152 @@
   </autoFilter>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="61" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="60" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21FFF12F-B684-4050-9B34-306B03FBB89B}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51530BB6-C9E5-4DB5-8565-004D9E44C6B2}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H39"/>
+  <dimension ref="B2:F15"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="21.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="75.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.875" customWidth="1"/>
-    <col min="8" max="8" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="79.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="5.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="30" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" ht="30" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="7" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="H5" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="6">
+    <row r="6" spans="2:6" ht="38.25" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2015</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="2:6" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2026</v>
+      </c>
+      <c r="E7" s="3">
         <v>0.7</v>
       </c>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="2:6" ht="75" x14ac:dyDescent="0.4">
       <c r="B8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="2:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B12" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B13" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B15" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B17" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B18" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B19" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G25" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="2:8" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="B26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G26" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="H26" s="1"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B27" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G28" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G30" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B33" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F33" s="1"/>
-      <c r="G33" s="3">
+      <c r="D9" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E9" s="3">
         <v>0.05</v>
       </c>
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B34" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G34" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B36" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B37" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B38" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B39" t="s">
-        <v>152</v>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B10" s="1"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:H5" xr:uid="{21FFF12F-B684-4050-9B34-306B03FBB89B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:H34">
-      <sortCondition descending="1" ref="G5"/>
+  <autoFilter ref="B5:F5" xr:uid="{51530BB6-C9E5-4DB5-8565-004D9E44C6B2}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:F9">
+      <sortCondition descending="1" ref="E5"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="58" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="94" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AB8815A-545D-43FD-9F73-16180910990E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3968,12 +4009,12 @@
   <sheetData>
     <row r="2" spans="2:8" ht="30" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3987,13 +4028,13 @@
         <v>17</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>69</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>18</v>
@@ -4007,7 +4048,7 @@
         <v>66</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>68</v>
@@ -4016,7 +4057,7 @@
         <v>2018</v>
       </c>
       <c r="G6" s="3">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="H6" s="1"/>
     </row>
@@ -4028,7 +4069,7 @@
         <v>64</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1">
@@ -4041,16 +4082,16 @@
     </row>
     <row r="8" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B8" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F8" s="1">
         <v>2024</v>
@@ -4068,10 +4109,10 @@
         <v>54</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F9" s="1">
         <v>2024</v>
@@ -4089,7 +4130,7 @@
         <v>64</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1">
@@ -4108,7 +4149,7 @@
         <v>55</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>68</v>
@@ -4129,7 +4170,7 @@
         <v>57</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1">
@@ -4148,7 +4189,7 @@
         <v>57</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1">
@@ -4167,7 +4208,7 @@
         <v>57</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1">
@@ -4186,7 +4227,7 @@
         <v>65</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1">
@@ -4205,7 +4246,7 @@
         <v>26</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1">
@@ -4224,7 +4265,7 @@
         <v>56</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1">
@@ -4243,7 +4284,7 @@
         <v>67</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1">
@@ -4262,7 +4303,7 @@
         <v>21</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1">
@@ -4281,7 +4322,7 @@
         <v>21</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1">
@@ -4300,7 +4341,7 @@
         <v>55</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1">
@@ -4331,22 +4372,22 @@
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B25" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B26" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B27" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B28" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -4361,143 +4402,892 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51530BB6-C9E5-4DB5-8565-004D9E44C6B2}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21FFF12F-B684-4050-9B34-306B03FBB89B}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F15"/>
+  <dimension ref="B2:I47"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="79.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.625" customWidth="1"/>
+    <col min="3" max="3" width="21.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="75.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12.875" customWidth="1"/>
+    <col min="9" max="9" width="5.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="30" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" ht="30" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B14" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B17" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1">
+        <v>2018</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B22" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B24" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B25" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1">
+        <v>2019</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B26" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1">
+        <v>2018</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1">
+        <v>2018</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1">
+        <v>2018</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H31" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B33" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B34" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H34" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B35" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1">
+        <v>2018</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H36" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H37" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2019</v>
+      </c>
+      <c r="H38" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B39" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H39" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B40" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="38.25" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="C40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2018</v>
+      </c>
+      <c r="H40" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B44" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B45" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B46" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B47" t="s">
         <v>142</v>
       </c>
-      <c r="D6" s="1">
-        <v>2016</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="2:6" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="B7" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="2:6" ht="75" x14ac:dyDescent="0.4">
-      <c r="B8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D8" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="2:6" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="B9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B10" s="1"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B12" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B14" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B15" t="s">
-        <v>152</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:F5" xr:uid="{51530BB6-C9E5-4DB5-8565-004D9E44C6B2}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:F9">
-      <sortCondition descending="1" ref="E5"/>
+  <autoFilter ref="B5:I5" xr:uid="{21FFF12F-B684-4050-9B34-306B03FBB89B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:I40">
+      <sortCondition descending="1" ref="H5"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="94" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="47" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/99_Others/Supplement.xlsx
+++ b/99_Others/Supplement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\portfolio\99_Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD4252B-9510-493F-BCE8-65F85651F9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF72773-8BBD-4C02-A808-208BA11E0ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">資格別!$A$4:$G$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Windows機能別!$A$1:$D$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">ツール別!$A$1:$H$56</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">画面証跡!$A$1:$O$237</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">画面証跡!$A$1:$N$186</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">教材別!$A$1:$F$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">業務別!$A$1:$F$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">言語別!$A$1:$H$22</definedName>
@@ -71,13 +71,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="490">
   <si>
     <t>説明</t>
     <rPh sb="0" eb="2">
       <t>セツメイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <r>
@@ -118,14 +118,14 @@
     <rPh sb="33" eb="34">
       <t>サイワ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>目次</t>
     <rPh sb="0" eb="2">
       <t>モクジ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>資格別</t>
@@ -135,7 +135,7 @@
     <rPh sb="2" eb="3">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>客観的なスキル指標</t>
@@ -145,11 +145,11 @@
     <rPh sb="7" eb="9">
       <t>シヒョウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>工程別</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ウォーターフォールやアジャイルでの工程、役割での観点</t>
@@ -162,7 +162,7 @@
     <rPh sb="24" eb="26">
       <t>カンテン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>言語別</t>
@@ -172,7 +172,7 @@
     <rPh sb="2" eb="3">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>経験してきたプログラミング・マークアップ言語</t>
@@ -182,7 +182,7 @@
     <rPh sb="20" eb="22">
       <t>ゲンゴ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>教材別</t>
@@ -192,7 +192,7 @@
     <rPh sb="2" eb="3">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>業務時間外の勉強してきた本の内容</t>
@@ -214,14 +214,14 @@
     <rPh sb="14" eb="16">
       <t>ナイヨウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ツール別</t>
     <rPh sb="3" eb="4">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>業界標準のツール別の理解度やツールを通して経験した業務など</t>
@@ -246,7 +246,7 @@
     <rPh sb="25" eb="27">
       <t>ギョウム</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Windows機能別</t>
@@ -256,7 +256,7 @@
     <rPh sb="9" eb="10">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>実務で使用する頻度の高い機能の経験</t>
@@ -278,7 +278,7 @@
     <rPh sb="15" eb="17">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>業務別</t>
@@ -288,7 +288,7 @@
     <rPh sb="2" eb="3">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>システム開発の際、付随して必要になったIT以外の業務知識について</t>
@@ -313,7 +313,7 @@
     <rPh sb="26" eb="28">
       <t>チシキ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>仕事の進め方や考え方</t>
@@ -332,7 +332,7 @@
     <rPh sb="9" eb="10">
       <t>カタ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>個人の仕事の考え方などのご説明</t>
@@ -351,7 +351,7 @@
     <rPh sb="13" eb="15">
       <t>セツメイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>■面談前の留意点</t>
@@ -364,7 +364,7 @@
     <rPh sb="5" eb="8">
       <t>リュウイテン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>誤字脱字など十分注意したつもりではありますが、</t>
@@ -380,11 +380,11 @@
     <rPh sb="8" eb="10">
       <t>チュウイトクジュウヨウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>本書は頻繁に書き換えるため「理解度」列など、うっかり記載を間違えてしまう場合を懸念しております。</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>特に重要なスキルについては、よりミスマッチが発生しないように面談などで、</t>
@@ -394,11 +394,11 @@
     <rPh sb="30" eb="32">
       <t>メンダン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>事前にご確認していただければと思います。</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>観点別のスキル感や工夫した点、お作法などを記述します。メインはスキルシートやポートフォリオ成果物をご確認ください。</t>
@@ -429,7 +429,7 @@
     <rPh sb="50" eb="52">
       <t>カクニン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>※合格したものに限り記載し、受験中の資格は省きます。</t>
@@ -451,7 +451,7 @@
     <rPh sb="21" eb="22">
       <t>ハブ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>資格名</t>
@@ -461,15 +461,15 @@
     <rPh sb="2" eb="3">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>コメント</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>デジタルバッジ</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>合格点数</t>
@@ -479,7 +479,7 @@
     <rPh sb="3" eb="4">
       <t>スウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>受験回数</t>
@@ -489,7 +489,7 @@
     <rPh sb="2" eb="4">
       <t>カイスウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>学習期間</t>
@@ -499,7 +499,7 @@
     <rPh sb="2" eb="4">
       <t>キカン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>取得日付</t>
@@ -509,7 +509,7 @@
     <rPh sb="2" eb="4">
       <t>ヒヅケ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>HTML5プロフェッショナル認定試験 レベル1</t>
@@ -534,7 +534,7 @@
     <rPh sb="22" eb="23">
       <t>フカ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>約70点</t>
@@ -544,32 +544,32 @@
     <rPh sb="3" eb="4">
       <t>テン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>1か月</t>
     <rPh sb="2" eb="3">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>https://catalog-education.oracle.com/pls/certview/sharebadge?id=1B95E9A663D35A568BF9D4E2A771FE0D11ABCC4B3C5B1CA8B5BDFF58028CC4FE</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>約60点</t>
     <rPh sb="0" eb="1">
       <t>ヤク</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>1年</t>
     <rPh sb="1" eb="2">
       <t>ネン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>カプセル化や例外処理、継承、ポリモーフィズムなど基本的な文法などを学びました。</t>
@@ -594,18 +594,18 @@
     <rPh sb="33" eb="34">
       <t>マナ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>https://catalog-education.oracle.com/pls/certview/sharebadge?id=53530D71C1F9D80C808FB90F92AA21C7099A92F2E5180E51AD2F324C39097648</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>約90点</t>
     <rPh sb="0" eb="1">
       <t>ヤク</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>タイピング技能検定 イータイピング・マスター 1級</t>
@@ -618,7 +618,7 @@
     <rPh sb="24" eb="25">
       <t>キュウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>使用頻度の高い単語と苦手な単語を専門的に練習した経験あり。標準運指を崩し最適化適用済。実務では緩急や静音を意識しております。</t>
@@ -679,14 +679,14 @@
     <rPh sb="53" eb="55">
       <t>イシキ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>2年</t>
     <rPh sb="1" eb="2">
       <t>ネン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>工程別</t>
@@ -696,21 +696,21 @@
     <rPh sb="2" eb="3">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>大分類</t>
     <rPh sb="0" eb="3">
       <t>ダイブンルイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>中分類</t>
     <rPh sb="0" eb="3">
       <t>チュウブンルイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>作業内容や工夫した点など</t>
@@ -726,18 +726,18 @@
     <rPh sb="9" eb="10">
       <t>テン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>理解度 ※１</t>
     <rPh sb="0" eb="3">
       <t>リカイド</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ウォーターフォール</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>要件定義</t>
@@ -747,7 +747,7 @@
     <rPh sb="2" eb="4">
       <t>テイギ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>－</t>
@@ -766,7 +766,7 @@
     <rPh sb="13" eb="15">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>基本設計</t>
@@ -776,7 +776,7 @@
     <rPh sb="2" eb="4">
       <t>セッケイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>詳細設計</t>
@@ -786,7 +786,7 @@
     <rPh sb="2" eb="4">
       <t>セッケイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>プログラムデザイン設計書にて他プロセス連携時のシーケンス図の記載実績あり。</t>
@@ -811,14 +811,14 @@
     <rPh sb="32" eb="34">
       <t>ジッセキ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>実装</t>
     <rPh sb="0" eb="2">
       <t>ジッソウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>※言語別シート参照</t>
@@ -831,46 +831,46 @@
     <rPh sb="7" eb="9">
       <t>サンショウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>単体テスト</t>
     <rPh sb="0" eb="2">
       <t>タンタイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>机上</t>
     <rPh sb="0" eb="2">
       <t>キジョウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ソースコードを画面証跡とした机上デバッグの実績あり</t>
     <rPh sb="21" eb="23">
       <t>ジッセキ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>実機</t>
     <rPh sb="0" eb="2">
       <t>ジッキ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>テストコード</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>結合テスト</t>
     <rPh sb="0" eb="2">
       <t>ケツゴウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>内部結合</t>
@@ -880,7 +880,7 @@
     <rPh sb="2" eb="4">
       <t>ケツゴウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>外部結合</t>
@@ -890,22 +890,22 @@
     <rPh sb="2" eb="4">
       <t>ケツゴウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>運用</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>性能</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>負荷</t>
     <rPh sb="0" eb="2">
       <t>フカ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>以下は消化した内容の一例
@@ -931,15 +931,15 @@
     <rPh sb="24" eb="26">
       <t>シケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>イレギュラー</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>デグレード</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>運用・保守</t>
@@ -949,7 +949,7 @@
     <rPh sb="3" eb="5">
       <t>ホシュ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>夜間バッチ監視経験あり　※スキルシート参照</t>
@@ -965,15 +965,15 @@
     <rPh sb="19" eb="21">
       <t>サンショウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ヘルプデスク</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>－</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>問い合わせ回答の経験あり　※スキルシート参照</t>
@@ -992,11 +992,11 @@
     <rPh sb="20" eb="22">
       <t>サンショウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>PMO</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>進捗管理の経験あり　※スキルシート参照</t>
@@ -1012,11 +1012,11 @@
     <rPh sb="17" eb="19">
       <t>サンショウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>アジャイル</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>実務経験なし。スクラムやスプリントなどの用語は応用情報の学習で知っているくらいのレベル感です。</t>
@@ -1044,7 +1044,7 @@
     <rPh sb="43" eb="44">
       <t>カン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>※１　理解度についての値の定義を以下に示す。</t>
@@ -1063,7 +1063,7 @@
     <rPh sb="19" eb="20">
       <t>シメ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>70%～100%：一人で実践できる</t>
@@ -1073,7 +1073,7 @@
     <rPh sb="12" eb="14">
       <t>ジッセン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>40%～69%：一人で実践できるが細かいところを指摘される不安がある</t>
@@ -1092,7 +1092,7 @@
     <rPh sb="29" eb="31">
       <t>フアン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>0%～ 39%：忘れてしまっている可能性があるが経験がある</t>
@@ -1105,7 +1105,7 @@
     <rPh sb="24" eb="26">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>※構文だけ勉強した言語は除き、実務上、成果物を作成した言語のみの記載とします。</t>
@@ -1139,14 +1139,14 @@
     <rPh sb="32" eb="34">
       <t>キサイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>言語</t>
     <rPh sb="0" eb="2">
       <t>ゲンゴ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>実装経験や取扱経験</t>
@@ -1162,7 +1162,7 @@
     <rPh sb="7" eb="9">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>最終実装年</t>
@@ -1175,29 +1175,29 @@
     <rPh sb="4" eb="5">
       <t>ネン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>優先度</t>
     <rPh sb="0" eb="3">
       <t>ユウセンド</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>C言語</t>
     <rPh sb="0" eb="3">
       <t>ｃ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Java</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>PowerShell</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>内部向けの業務改善ツールを作成した経験があります。(50ステップ×10ファイル程度)</t>
@@ -1222,11 +1222,11 @@
     <rPh sb="39" eb="41">
       <t>テイド</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Excel VBA</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>500行規模のログ取得ツール作成経験あり(1件)</t>
@@ -1248,11 +1248,11 @@
     <rPh sb="22" eb="23">
       <t>ケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Batch</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>コマンドプロンプト単体のコマンドも含めるとコピーやリネーム、検索などできます。</t>
@@ -1265,15 +1265,15 @@
     <rPh sb="30" eb="32">
       <t>ケンサク</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>HTML</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>JavaScript</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>デベロッパーツールからデバッグなどができます。
@@ -1312,7 +1312,7 @@
     <rPh sb="115" eb="117">
       <t>キョウミ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>・RegExpを使用したXML閉じタグ後やJSON波括弧後の改行挿入処理
@@ -1381,11 +1381,11 @@
     <rPh sb="85" eb="87">
       <t>ショリ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Perl</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ファッション系サイトのフロント、バックエンドの実装など担当しました。
@@ -1487,15 +1487,15 @@
     <rPh sb="207" eb="208">
       <t>オコナ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>VBScript</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>C++</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>※実際に購入したものとし、Kindle Unlimitedでのレンタル読書は除きます。</t>
@@ -1511,14 +1511,14 @@
     <rPh sb="38" eb="39">
       <t>ノゾ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>分類</t>
     <rPh sb="0" eb="2">
       <t>ブンルイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>学習した書籍</t>
@@ -1528,7 +1528,7 @@
     <rPh sb="4" eb="6">
       <t>ショセキ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>実務へのプラスな影響</t>
@@ -1538,7 +1538,7 @@
     <rPh sb="8" eb="10">
       <t>エイキョウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>学習時期（年）</t>
@@ -1551,14 +1551,14 @@
     <rPh sb="5" eb="6">
       <t>ネン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>IT系</t>
     <rPh sb="2" eb="3">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>C言語ポインタ完全制覇</t>
@@ -1571,11 +1571,11 @@
     <rPh sb="9" eb="11">
       <t>セイハ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>〇</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Git入門コマンドライン演習８０</t>
@@ -1585,11 +1585,11 @@
     <rPh sb="12" eb="14">
       <t>エンシュウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>JavaエンジニアのためのEclipseパーフェクトガイド</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>JP1認定エンジニア V12対応</t>
@@ -1599,11 +1599,11 @@
     <rPh sb="14" eb="16">
       <t>タイオウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Linuxシェルスクリプト ショートガイダンス</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>実務でシェルスクリプトを解析する機会があったため学習したが、スクリプト作成までは至らなかった。Linuxコマンドはパイプラインを使用した当日日付とエラー識別子の含まれるGrepコマンドの作成経験がありました。知らないコマンドは、いきなり本番環境でコマンドで試さず、試験環境で試す作法を心得ております。</t>
@@ -1673,7 +1673,7 @@
     <rPh sb="142" eb="144">
       <t>ココロエ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Oracleデータベースの基本と仕組み(第6版)</t>
@@ -1689,7 +1689,7 @@
     <rPh sb="22" eb="23">
       <t>ハン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Subversion実践入門</t>
@@ -1699,7 +1699,7 @@
     <rPh sb="12" eb="14">
       <t>ニュウモン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>アウトルック最速仕事術</t>
@@ -1712,7 +1712,7 @@
     <rPh sb="10" eb="11">
       <t>ジュツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>即戦力のDB2管理術</t>
@@ -1725,7 +1725,7 @@
     <rPh sb="9" eb="10">
       <t>ジュツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>達人に学ぶSQL徹底指南書(第2版)</t>
@@ -1750,14 +1750,14 @@
     <rPh sb="16" eb="17">
       <t>ハン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>独習アセンブラ</t>
     <rPh sb="0" eb="2">
       <t>ドクシュウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>一応勉強してみたかったため学習したが、実務に生かす場面もなく、プラスになったものはなかった。</t>
@@ -1779,14 +1779,14 @@
     <rPh sb="25" eb="27">
       <t>バメン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ネットワークはなぜ繋がるのか</t>
     <rPh sb="9" eb="10">
       <t>ツナ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>〇</t>
@@ -1796,11 +1796,11 @@
     <rPh sb="14" eb="16">
       <t>ニュウモン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>マスタリング TCP/IP</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>資格系</t>
@@ -1810,7 +1810,7 @@
     <rPh sb="2" eb="3">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>JavaGold SE8 オラクル認定資格教科書</t>
@@ -1823,7 +1823,7 @@
     <rPh sb="21" eb="24">
       <t>キョウカショ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Java Gold紫本。約３周</t>
@@ -1839,7 +1839,7 @@
     <rPh sb="14" eb="15">
       <t>シュウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>JavaSilver SE8 オラクル認定資格教科書</t>
@@ -1852,7 +1852,7 @@
     <rPh sb="23" eb="26">
       <t>キョウカショ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Java Silver紫本。約３周</t>
@@ -1868,28 +1868,28 @@
     <rPh sb="16" eb="17">
       <t>シュウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Javaプログラマ Gold SE8 スピードマスター問題集</t>
     <rPh sb="27" eb="30">
       <t>モンダイシュウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Javaプログラマ Silver SE11 スピードマスター問題集</t>
     <rPh sb="30" eb="33">
       <t>モンダイシュウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>LPIC レベル1 スピードマスター問題集</t>
     <rPh sb="18" eb="21">
       <t>モンダイシュウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>応用情報技術者2024 午後問題の重点対策</t>
@@ -1914,18 +1914,18 @@
     <rPh sb="19" eb="21">
       <t>タイサク</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ORACLE MASTER Bronze 12c SQL基礎 スタディガイド</t>
     <rPh sb="28" eb="30">
       <t>キソ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t xml:space="preserve">ORACLE MASTER Bronze DBA11g スタディガイド </t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>キタミ式応用情報技術者</t>
@@ -1941,7 +1941,7 @@
     <rPh sb="8" eb="11">
       <t>ギジュツシャ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>徹底攻略 Java SE8 Gold 問題集</t>
@@ -1954,14 +1954,14 @@
     <rPh sb="19" eb="22">
       <t>モンダイシュウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Java Gold黒本。約３周</t>
     <rPh sb="9" eb="10">
       <t>クロ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>徹底攻略 Java SE8 Silver 問題集</t>
@@ -1974,7 +1974,7 @@
     <rPh sb="21" eb="24">
       <t>モンダイシュウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Java Silver黒本。約３周しました。ループ文を読み取る力やデータ型を考慮する基本的な能力が身についたと振り返っています。</t>
@@ -2014,7 +2014,7 @@
     <rPh sb="57" eb="58">
       <t>カエ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>徹底攻略 OracleMasterBronze 12c基礎 問題集</t>
@@ -2033,11 +2033,11 @@
     <rPh sb="32" eb="33">
       <t>シュウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ネスペR4</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>一応勉強してみたかったため、模擬試験を1周半解きました。
@@ -2084,7 +2084,7 @@
     <rPh sb="62" eb="63">
       <t>カン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>非IT系</t>
@@ -2094,7 +2094,7 @@
     <rPh sb="3" eb="4">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>答え方が人生を変える　最強の答え方</t>
@@ -2119,7 +2119,7 @@
     <rPh sb="16" eb="17">
       <t>カタ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>コミュニケーションは質問力ではなく回答力であるというのが本書の基本的な概念。
@@ -2208,7 +2208,7 @@
     <rPh sb="170" eb="172">
       <t>ブブン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>仕事で必要な「本当のコミュニケーション能力」はどう身につければいいのか</t>
@@ -2227,7 +2227,7 @@
     <rPh sb="25" eb="26">
       <t>ミ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>軽微なスキルアピールとなってしまいますが、業界標準スキルとなるため記載します。</t>
@@ -2243,7 +2243,7 @@
     <rPh sb="33" eb="35">
       <t>キサイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>サードパーティ製アプリ名</t>
@@ -2253,14 +2253,14 @@
     <rPh sb="11" eb="12">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>区分</t>
     <rPh sb="0" eb="2">
       <t>クブン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>実務使用経験</t>
@@ -2273,7 +2273,7 @@
     <rPh sb="4" eb="6">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>自宅学習経験</t>
@@ -2286,49 +2286,49 @@
     <rPh sb="4" eb="6">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>VisualStudio 2022</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>IDE</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>有</t>
     <rPh sb="0" eb="1">
       <t>ア</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Eclipse/STS</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Windbg</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>デバッガ</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>A5:SQL Mk-2</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>DB</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>WinMerge</t>
   </si>
   <si>
     <t>Diff</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>開発案件別のソースコードに差分を移植する作業を行っていた経験があるため、
@@ -2375,33 +2375,33 @@
     <rPh sb="66" eb="67">
       <t>カタ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>JMeter</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>試験用ドライバ</t>
     <rPh sb="0" eb="3">
       <t>シケンヨウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>JP1</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ジョブ管理</t>
     <rPh sb="3" eb="5">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Systemwalker</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>システムの本番リリース直後の約１か月、夜間監視のため使用していた経験があります。障害発生を検知してエスカレーションする立ち位置ではありましたが、万が一に備え自力でのジョブ停止やスキップなどの操作を学んだうえでの監視業務を担当していました。</t>
@@ -2471,26 +2471,26 @@
     <rPh sb="110" eb="112">
       <t>タントウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Jira Service Desk</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>チケット管理ツール</t>
     <rPh sb="4" eb="6">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Backlog</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Teams</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>システム障害の調査の時など事象再現できない場合、画面共有などでエスカレーションするなどした経験があります。また通信障害などに備えスマホなどでも参加できるように準備をしておくなど工夫していました。</t>
@@ -2539,18 +2539,18 @@
     <rPh sb="88" eb="90">
       <t>クフウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Source Tree</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>バージョン管理</t>
     <rPh sb="5" eb="7">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>中規模開発でのコンフリクトを経験しているため、定期的にプルする作法を身に着けております。</t>
@@ -2575,52 +2575,35 @@
     <rPh sb="36" eb="37">
       <t>ツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Git Bash</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>コマンドラインでGit add～Git pushやAmendなどの操作ができます。
-ほか、署名付きコミットの設定など。</t>
-    <rPh sb="33" eb="35">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ショメイ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>セッテイ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>TeraTerm</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>リモート接続</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>PowerPoint</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Office</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Excel</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>OutLook</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>スケジュールの設定やメールサーバの接続ができます。
@@ -2643,25 +2626,25 @@
     <rPh sb="55" eb="57">
       <t>クフウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>WinShot</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>キャプチャ系</t>
     <rPh sb="5" eb="6">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>サクラエディタ</t>
   </si>
   <si>
     <t>テキストエディタ</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>秀丸</t>
@@ -2671,15 +2654,15 @@
   </si>
   <si>
     <t>ブラウザ</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>thunderbird</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>メーラー</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>thunderbird固有の技術ではないですが、怪しいメールのマクロを実行しない作法を心得ており、万が一のウイルス感染時のLAN抜き、報告対応ができます。</t>
@@ -2722,11 +2705,11 @@
     <rPh sb="69" eb="71">
       <t>タイオウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Oracle SQL Developer</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>MySQL Workbench</t>
@@ -2736,11 +2719,11 @@
   </si>
   <si>
     <t>FileZilla</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>FTP</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Mac端末を使用していた時期があるため、レンタルサーバへのHTML、JSなどを用いたポートフォリオのアップロード経験があります。</t>
@@ -2759,40 +2742,40 @@
     <rPh sb="56" eb="58">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>WinSCP</t>
   </si>
   <si>
     <t>Microsoft Access</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Office</t>
   </si>
   <si>
     <t>Word</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Virtual Box</t>
   </si>
   <si>
     <t>VM</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ウイルスバスター</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>アンチウイルスソフト</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Symantec</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>インターネットから不要なファイルを無断でインストールしないなど留意し、セキュリティソフトにトラップされないように意識しておりました。</t>
@@ -2808,7 +2791,7 @@
     <rPh sb="56" eb="58">
       <t>イシキ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t xml:space="preserve">Norton </t>
@@ -2824,11 +2807,11 @@
     <rPh sb="24" eb="26">
       <t>サホウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Zabbix</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>運用管理ツール</t>
@@ -2838,11 +2821,11 @@
     <rPh sb="2" eb="4">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Redmine</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>チケットの作成経験あり</t>
@@ -2852,11 +2835,11 @@
     <rPh sb="7" eb="9">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Rocket.Chat</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Slack</t>
@@ -2897,11 +2880,11 @@
     <rPh sb="46" eb="47">
       <t>ツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>SVN</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>設計書を管理しているSVNにコミットやチェックアウト経験あり</t>
@@ -2914,26 +2897,26 @@
     <rPh sb="26" eb="28">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Stirling</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>バイナリエディタ</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>SharePoint</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ファイル共有</t>
     <rPh sb="4" eb="6">
       <t>キョウユウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>OneDriveと連携しローカル上のエクスプローラーから操作した経験あり</t>
@@ -2949,18 +2932,18 @@
     <rPh sb="32" eb="34">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Firefox</t>
   </si>
   <si>
     <t>Internet Explorer</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Photoshop</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>レイヤーを使用した基本的な操作やWeb用画像のスライスなど</t>
@@ -2979,11 +2962,11 @@
     <rPh sb="20" eb="22">
       <t>ガゾウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>IP Messenger</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ネットワーク使用不可の現場の経験があるため、メッセージの送信やログの設定など基本的な使用ができます。</t>
@@ -3011,25 +2994,25 @@
     <rPh sb="42" eb="44">
       <t>シヨウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Windows機能別</t>
     <rPh sb="9" eb="10">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Windows機能名</t>
     <rPh sb="7" eb="10">
       <t>キノウメイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>VBE(Visual Basic Editor)</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>クラスの作成やイミディエイトウィンドウの使用など基本的な操作が可能です。</t>
@@ -3048,11 +3031,11 @@
     <rPh sb="31" eb="33">
       <t>カノウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Windows PowerShell ISE</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>デバッグや変数の値の確認といった基本的な操作が可能です。</t>
@@ -3074,11 +3057,11 @@
     <rPh sb="23" eb="25">
       <t>カノウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>hosts</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>バッチ処理でhostsを書き換え、試験環境を変更する現場を経験しています。</t>
@@ -3106,11 +3089,11 @@
     <rPh sb="29" eb="31">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>コマンドプロンプト</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ほかの人が書いたバッチを解析した経験があるので、pauseや変数値をechoで出力するなどして、エラーを自力で特定できます。</t>
@@ -3141,15 +3124,15 @@
     <rPh sb="55" eb="57">
       <t>トクテイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>グループポリシー</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>レジストリ</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>過去３世代（次期・現行・旧環境）のシステムの設定値をドキュメント化した経験あります。</t>
@@ -3168,11 +3151,11 @@
     <rPh sb="35" eb="37">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>イベントビューア</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>次期開発システムで異常なイベントが取得されていないか調査する必要があったため、CSV化して次期と現行のログを比較した経験があります。</t>
@@ -3209,18 +3192,18 @@
     <rPh sb="58" eb="60">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>エクスプローラー</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>共有フォルダ</t>
     <rPh sb="0" eb="2">
       <t>キョウユウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>システムの移行手順に従い、お客様環境の共有フォルダで参照できるユーザーの追加やアクセス許可などを設定した経験があります。また、お客様環境での作業がスムーズになるように事前に共有フォルダにアクセスするユーザーを作成するためにバッチを準備・実行した経験があります。</t>
@@ -3287,11 +3270,11 @@
     <rPh sb="122" eb="124">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>タスクマネージャー</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>環境変数</t>
@@ -3301,15 +3284,15 @@
     <rPh sb="2" eb="4">
       <t>ヘンスウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>過去３世代（次期・現行・旧環境）のシステムの設定値をドキュメント化し、現行の設定値と同じになるように次期業務システムの設定を行った経験があります。</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ペイント</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>スリープ画面時にPrintScreenキーを押すことにより、スリープを解除しながらデスクトップアプリの様子を撮影し、スリープ中の障害発生条件を解決した経験があります。ほか、レガシー環境など証跡自動取得ツールがない状態で活用することが多かったので、１分間に証跡が5つ程度保存することができます。</t>
@@ -3382,11 +3365,11 @@
     <rPh sb="134" eb="136">
       <t>ホゾン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ワードパッド</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Officeのインストールされていない試験端末での作業経験があり、試験端末でも参照できる手順書を作成した実績があります。(約50件)</t>
@@ -3429,14 +3412,14 @@
     <rPh sb="64" eb="65">
       <t>ケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>リモートデスクトップ接続</t>
     <rPh sb="10" eb="12">
       <t>セツゾク</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>多人数で共通の端末をリモート接続する現場経験があったので、ゾンビセッションを残さないように接続を終了する作法を心得ております。</t>
@@ -3473,11 +3456,11 @@
     <rPh sb="55" eb="57">
       <t>ココロエ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>サービス</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>過去３世代のシステムの設定値をドキュメント化した経験があり、
@@ -3518,11 +3501,11 @@
     <rPh sb="73" eb="75">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ノートパッド</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ファイル名を指定して実行</t>
@@ -3535,14 +3518,14 @@
     <rPh sb="10" eb="12">
       <t>ジッコウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>電卓</t>
     <rPh sb="0" eb="2">
       <t>デンタク</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>カウンタとして使用したり、16進数や2進数の値のチェックなどに使用した経験あり</t>
@@ -3564,15 +3547,15 @@
     <rPh sb="35" eb="37">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>IME</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>LANケーブル</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>業務中LANケーブルの抜き差しを行う場合でも、VLANを意識して、元のケーブル差込口に戻すことができます。</t>
@@ -3606,7 +3589,7 @@
     <rPh sb="43" eb="44">
       <t>モド</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>外付けUSB</t>
@@ -3616,11 +3599,11 @@
     <rPh sb="1" eb="2">
       <t>ヅ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>クロック</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ラップ機能などを使用し、業務システムのCSVエクスポート機能の性能試験などに使用した経験あり</t>
@@ -3648,14 +3631,14 @@
     <rPh sb="42" eb="44">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>業種</t>
     <rPh sb="0" eb="2">
       <t>ギョウシュ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>製造系</t>
@@ -3665,7 +3648,7 @@
     <rPh sb="2" eb="3">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>非エンジニア時代に自動車部品製造(3年)をやっており、製造工程の機械が人に与える影響を理解しております。
@@ -3740,21 +3723,21 @@
     <rPh sb="126" eb="128">
       <t>イシキ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>銀行系</t>
     <rPh sb="0" eb="3">
       <t>ギンコウケイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ロジスティクス系</t>
     <rPh sb="7" eb="8">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ロジスティクス向けアプリのテスト経験があり、
@@ -3883,7 +3866,7 @@
     <rPh sb="193" eb="195">
       <t>シヨウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>人事系</t>
@@ -3893,14 +3876,14 @@
     <rPh sb="2" eb="3">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ファッション系</t>
     <rPh sb="6" eb="7">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>特別専門に勉強したレベルではありませんが、開発を通じファッション系の通販サイトなどのメニューや新商品追加、セールなどの業務背景に触れた経験はあります。</t>
@@ -3943,7 +3926,7 @@
     <rPh sb="67" eb="69">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>大手通信業界でのお客様環境でサードパーティアプリのインストールや開発アプリ資源のデプロイ、および総合試験の実施を行った経験があります。業務知識については特別専門に勉強したレベルではありません。</t>
@@ -3989,15 +3972,15 @@
     <rPh sb="69" eb="71">
       <t>チシキ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>仕事の進め方や考え方などについて</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>以下、現場のミスマッチを防ぐために私の考えや求めていることを記載いたします。</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>私の強みはプログラミング関係です。</t>
@@ -4010,7 +3993,7 @@
     <rPh sb="12" eb="14">
       <t>カンケイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>キャリアビジョン</t>
@@ -4035,7 +4018,7 @@
     <rPh sb="37" eb="38">
       <t>カンガ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>言語について</t>
@@ -4054,7 +4037,7 @@
     <rPh sb="28" eb="30">
       <t>エンカツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>その次に言語としては将来性のありそうな言語や伝統のある言語であるほうが良いと考えております。</t>
@@ -4070,7 +4053,7 @@
     <rPh sb="38" eb="39">
       <t>カンガ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>自身の性格について</t>
@@ -4086,7 +4069,7 @@
     <rPh sb="9" eb="11">
       <t>セイカク</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>実装について</t>
@@ -4099,7 +4082,7 @@
     <rPh sb="17" eb="19">
       <t>キボウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>その他</t>
@@ -4121,7 +4104,7 @@
     <rPh sb="20" eb="22">
       <t>ジッセキ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>2017年1月からの趣味です。</t>
@@ -4134,7 +4117,7 @@
     <rPh sb="10" eb="12">
       <t>シュミ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>一人称、自走</t>
@@ -4144,7 +4127,7 @@
     <rPh sb="4" eb="6">
       <t>ジソウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>健康面</t>
@@ -4154,7 +4137,7 @@
     <rPh sb="2" eb="3">
       <t>メン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>IT技術ではなく業務仕様の深い理解が必要だと考えています。</t>
@@ -4179,7 +4162,7 @@
     <rPh sb="22" eb="23">
       <t>カンガ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>長期的な観点で自走するためにも現場の有識者への質問が必要不可欠だと考えております。</t>
@@ -4210,7 +4193,7 @@
     <rPh sb="33" eb="34">
       <t>カンガ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>以下は計測した内容の一例
@@ -4276,7 +4259,7 @@
     <rPh sb="70" eb="72">
       <t>ケイソク</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>特に慢性的な持病があるというわけではありません。</t>
@@ -4289,7 +4272,7 @@
     <rPh sb="6" eb="8">
       <t>ジビョウ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>基本的に良好です。</t>
@@ -4299,14 +4282,14 @@
     <rPh sb="4" eb="6">
       <t>リョウコウ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>小分類</t>
     <rPh sb="0" eb="3">
       <t>ショウブンルイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Java Silver白本。SE8とSE11のどちらか迷ったため、購入。取得には至らなかったが、var（型推論）やモジュールなどが追加されたことは概念として理解しております。</t>
@@ -4343,7 +4326,7 @@
     <rPh sb="78" eb="80">
       <t>リカイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>開発者ツールのFirebugの使用経験などあり</t>
@@ -4356,7 +4339,7 @@
     <rPh sb="17" eb="19">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>障害発生時の事象の報告など経験あり(10～20件)。
@@ -4412,7 +4395,7 @@
     <rPh sb="59" eb="61">
       <t>イシキ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>銀行システム利用者が使用するための銀行業務用IME辞書を現新比較、および設定した経験があります。</t>
@@ -4452,7 +4435,7 @@
     <rPh sb="40" eb="42">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>システム利用者向けの可搬媒体を使用した手順書の作成経験がありますので、高速スタートアップ設定時にUSBの動作不良が起きやすいことを認識しております。
@@ -4526,7 +4509,7 @@
     <rPh sb="117" eb="119">
       <t>ココロエ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>設計書を編集する際なども元の状態に戻せるようにバックアップしておく作法を心得ております。
@@ -4555,7 +4538,7 @@
     <rPh sb="36" eb="38">
       <t>ココロエ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>InternetExplorer終了中に別プロセスのInternetExplorerが立ち上がらないシステム障害の原因の調査を経験しているので、コマンドライン列などからプロセスがどのファイルから起動され、どのパラメータを受け取っているか特定できます。</t>
@@ -4601,7 +4584,7 @@
     <rPh sb="118" eb="120">
       <t>トクテイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>営業日、非営業日などを想定した運用試験で使用していたため、ジョブグループの概念を理解しており、即時実行や保留などの操作などの経験があります。接続時に別試験環境に接続しないように留意しておりました。</t>
@@ -4674,14 +4657,14 @@
     <rPh sb="88" eb="90">
       <t>リュウイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>イメージ管理</t>
     <rPh sb="4" eb="6">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>端末構築手順にそって設定・デプロイなどした試験用端末のイメージをバックアップ・リストアした経験があります。ほかチームも利用する端末のリストアも含めるため、1回のリストア依頼で２６件規模の対応の実績あり。プロジェクト完了後の運用チーム、および次回更改プロジェクトメンバー宛てにバックアップ・リストアのフローチャート付き手順書を作成。</t>
@@ -4763,7 +4746,7 @@
     <rPh sb="162" eb="164">
       <t>サクセイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>IEのプロセス終了40秒以内に他IEが起動された場合のシステム障害について調査経験あり。(Loosely-Coupled IE)
@@ -4820,19 +4803,19 @@
     <rPh sb="103" eb="105">
       <t>ケイケンシンライズセッテイカクセッテイチシリョウカケイケン</t>
     </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>DataCloningWizard（データクローニングウィザード）</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>Acrobat Reader 2020</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>PDF</t>
     <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>DataCloningWizard（データクローニングウィザード）</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>Acrobat Reader 2020</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>PDF</t>
-    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>実務を通して以下の経験があります。
@@ -4859,7 +4842,7 @@
     <rPh sb="80" eb="82">
       <t>チョウサ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>業務ではタブレット側からPCに送られるXMLデータの代わりのドライバとして使用していました。ただし、単発的な使い方に限り、負荷テスト経験などはありません。
@@ -4921,7 +4904,7 @@
     <rPh sb="122" eb="123">
       <t>オコナ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>過去３世代（次期・現行・旧環境）のシステムの設定値をドキュメント化し、現行の設定値と同じになるように次期業務システムの設定を行った経験があります。次期環境で非推奨(非サポート)となっていないかなど調査した経験があります。</t>
@@ -4982,11 +4965,11 @@
     <rPh sb="102" eb="104">
       <t>ケイケン</t>
     </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>Oracle Certified Java Programmer, Gold SE 8</t>
     <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>Oracle Certified Java Programmer, Gold SE 8</t>
-    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>・スリープ解除時のWM_PAINT受信時のエディットコントロール描画障害調査(1件)
@@ -5024,7 +5007,7 @@
     <rPh sb="67" eb="69">
       <t>サギョウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ほぼ解析専門。
@@ -5080,7 +5063,7 @@
     <rPh sb="99" eb="101">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>・修正箇所の関連機能や類似機能の確認
@@ -5142,7 +5125,7 @@
     <rPh sb="53" eb="55">
       <t>カクニン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>・ネットワークと共有センター有効無効切替スクリプトの解析、および設計書作成
@@ -5189,7 +5172,7 @@
     <rPh sb="67" eb="69">
       <t>タイオウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>・シーケンス図や表などを用いたプログラムデザイン設計書の作成経験あり(約20件)
@@ -5245,7 +5228,7 @@
     <rPh sb="80" eb="81">
       <t>ケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>時刻指定保存機能やプリントスクリーン長押し機能を使用してスリープ中のアプリの画面状態を撮影して障害の発生条件を特定した実績があります。</t>
@@ -5297,7 +5280,7 @@
     <rPh sb="59" eb="61">
       <t>ジッセキ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ほぼ解析専門。
@@ -5366,7 +5349,7 @@
     <rPh sb="135" eb="136">
       <t>ケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>外部とのメールのやり取りが多い時期に勉強しました。
@@ -5410,7 +5393,7 @@
     <rPh sb="77" eb="79">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>言語ごとに技術レベルのムラがあるので現場で必要なスキルを直接保有しているか面談の際に確認していただければ幸いです。</t>
@@ -5444,7 +5427,7 @@
     <rPh sb="52" eb="53">
       <t>サイワ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>クライアントからの機能追加要望に対し、対応可否や対応工数など回答経験あり(約10件前後)</t>
@@ -5487,7 +5470,7 @@
     <rPh sb="41" eb="43">
       <t>ゼンゴ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>マルウェア対策のためマクロ自動実行オフのまま閲覧する作法を心得ております。
@@ -5535,7 +5518,7 @@
     <rPh sb="115" eb="117">
       <t>シヨウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>固定長電文やログの16進数やパック10進数を解析した経験があります。</t>
@@ -5557,7 +5540,7 @@
     <rPh sb="26" eb="28">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>業務システムの基本的な機能</t>
@@ -5570,11 +5553,11 @@
     <rPh sb="11" eb="13">
       <t>キノウ</t>
     </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>－</t>
     <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>－</t>
-    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>業務内容について</t>
@@ -5584,7 +5567,7 @@
     <rPh sb="2" eb="4">
       <t>ナイヨウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ファイル共有システム
@@ -5608,21 +5591,21 @@
     <rPh sb="50" eb="52">
       <t>セイギョ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>C言語</t>
     <rPh sb="1" eb="3">
       <t>ゲンゴ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>年月</t>
     <rPh sb="0" eb="2">
       <t>ネンゲツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>5年6か月</t>
@@ -5632,7 +5615,7 @@
     <rPh sb="4" eb="5">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>3年1か月</t>
@@ -5642,38 +5625,38 @@
     <rPh sb="4" eb="5">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>9か月</t>
     <rPh sb="2" eb="3">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>3か月</t>
     <rPh sb="2" eb="3">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>4か月</t>
     <rPh sb="2" eb="3">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>Perl
 HTML</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>Java
 (Spring)</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>以下は開発を通じ触れた業務の内容や業務システムの経験です。ただし、機能実装経験のみではなく、システム利用者側の観点でテストを行ったことがある経験を含みます。</t>
@@ -5701,7 +5684,7 @@
     <rPh sb="24" eb="26">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>在庫管理システム
@@ -5739,24 +5722,24 @@
     <rPh sb="54" eb="56">
       <t>キノウ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>JQuery</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>win32API</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>Microsoft Foundation Class</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>CGI.pm
 DBI</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>使用ライブラリ例</t>
@@ -5766,12 +5749,12 @@
     <rPh sb="7" eb="8">
       <t>レイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>CSS
 Bootstrap</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>・通販サイトの期間限定セールCGI修正（2BUY価格や消費税など）
@@ -5861,7 +5844,7 @@
     <rPh sb="165" eb="167">
       <t>サクセイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>以下は項目作成・実施した項目の一例
@@ -6002,7 +5985,7 @@
     <rPh sb="185" eb="187">
       <t>カクニン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>「なぜ」と聞かない質問術</t>
@@ -6015,7 +5998,7 @@
     <rPh sb="11" eb="12">
       <t>ジュツ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>独習 JSP&amp;サーブレット第3版</t>
@@ -6028,7 +6011,7 @@
     <rPh sb="15" eb="16">
       <t>ハン</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>Java Gold白本。４周程度実施。</t>
@@ -6044,7 +6027,7 @@
     <rPh sb="16" eb="18">
       <t>ジッシ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>以下のことを理解しました。
@@ -6092,7 +6075,7 @@
     <rPh sb="70" eb="71">
       <t>ウ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>以下は学んだことの一例です。
@@ -6154,15 +6137,15 @@
     <rPh sb="151" eb="153">
       <t>カンリ</t>
     </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>ポートフォリオ</t>
     <phoneticPr fontId="14"/>
   </si>
   <si>
-    <t>ポートフォリオ</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>https://github.com/Test-Information/portfolio</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>JQueryの実装やWordPressへの対応など行い実務外でのポートフォリオ作品を作成した経験があります。2016年に学んでから最新技術にアップデートできていないので、保有技術はレガシー寄りになってるかもしれません。</t>
@@ -6211,7 +6194,7 @@
     <rPh sb="94" eb="95">
       <t>ヨ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>預金業務～為替など、大枠は理解しています。顧客登録、口座作成、入金、出金、為替など。口座の登録～口座の解約までのシナリオを想像し、総合試験項目を作成した経験があります。通帳への書き込みやページめくり、新通帳発行など利用したビジネスロジックの修正の経験もあります。</t>
@@ -6305,7 +6288,7 @@
     <rPh sb="123" eb="125">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>以下の内容を理解しました。
@@ -6335,7 +6318,7 @@
     <rPh sb="39" eb="41">
       <t>シヨウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>本資料は案件別のスキルシートとは別の経験やスキルの詳細を伝えるために作成しました。</t>
@@ -6357,7 +6340,7 @@
     <rPh sb="18" eb="20">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>資料に記載してある内容でも遠慮なく質問していただければと思います。</t>
@@ -6379,7 +6362,7 @@
     <rPh sb="28" eb="29">
       <t>オモ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>面談の際に、セルの塗りつぶしやフィルタリングなどを行っていただいても問題ございません。</t>
@@ -6398,7 +6381,7 @@
     <rPh sb="34" eb="36">
       <t>モンダイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>以下の手順を学びました。
@@ -6432,7 +6415,7 @@
     <rPh sb="64" eb="66">
       <t>ホウホウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ポインタがアドレスを指し示す概念であることなど理解しました。</t>
@@ -6445,7 +6428,7 @@
     <rPh sb="23" eb="25">
       <t>リカイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>CDBやPDB、トランザクションの開始、終了条件に付いては学びましたが、知らない機能のほうが多いです。</t>
@@ -6473,7 +6456,7 @@
     <rPh sb="46" eb="47">
       <t>オオ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Pingを使用した別の階の端末の起動状態の確認やARPテーブルを使用した端末の特定などができるようになりました。</t>
@@ -6507,7 +6490,7 @@
     <rPh sb="39" eb="41">
       <t>トクテイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>VLANやDNS・HOSTS、MACアドレスなどネットワーク以外の実務を行う上でも知識が水面下で生きている実感があります。</t>
@@ -6532,49 +6515,7 @@
     <rPh sb="53" eb="55">
       <t>ジッカン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>以下の内容を理解しました。
-・JSPがTomcatによりclassファイルにコンパイルされていること
-・サーブレットにはinitやdestroyなどライフサイクルがあること
-・サーブレット処理前後にフィルター処理を行うことができること
-・初回作成時のシングルトンのインスタンスを共有し、マルチスレッドで受け付けていること
-・Httpリクエスト時のインスタンス変数の取り扱いは危険であること</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>リカイ</t>
-    </rPh>
-    <rPh sb="94" eb="96">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="96" eb="98">
-      <t>ゼンゴ</t>
-    </rPh>
-    <rPh sb="104" eb="106">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="107" eb="108">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="179" eb="181">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="182" eb="183">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="184" eb="185">
-      <t>アツカ</t>
-    </rPh>
-    <rPh sb="187" eb="189">
-      <t>キケン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>以下に習得技術や経験を記述します。
@@ -6619,7 +6560,7 @@
     <rPh sb="128" eb="130">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Where条件をCase条件に置き換えることができることに感銘を受けました。</t>
@@ -6641,7 +6582,7 @@
     <rPh sb="32" eb="33">
       <t>ウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>以下の内容を理解しました
@@ -6662,7 +6603,7 @@
     <rPh sb="92" eb="94">
       <t>サクセイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>コメント（スキルや経験、作法など）</t>
@@ -6672,7 +6613,7 @@
     <rPh sb="12" eb="14">
       <t>サホウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>以下に習得技術や経験を記述します。
@@ -6748,7 +6689,7 @@
     <rPh sb="183" eb="186">
       <t>セイゴウセイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>応用情報資格取得のため3週ほど実施。
@@ -6830,7 +6771,7 @@
     <rPh sb="131" eb="133">
       <t>シク</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t xml:space="preserve">
@@ -6838,7 +6779,7 @@
     <rPh sb="1" eb="3">
       <t>ソウゴウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>・シートの値を引数とした正規表現の作成およびクリップボードへの格納処理
@@ -6882,7 +6823,7 @@
     <rPh sb="73" eb="75">
       <t>ジッソウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>・ネットワークドライブの取得、加工処理
@@ -6922,7 +6863,7 @@
     <rPh sb="95" eb="97">
       <t>ジョウタイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>DBの接続からクエリーの使用経験があります。試験で使用するテーブルやレコードの作成などの経験があります。(5テーブル以上)
@@ -6957,11 +6898,11 @@
     <rPh sb="91" eb="92">
       <t>ココロ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>DB GUIツール</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>JP1で運用試験を担当したときに知識がなかったため補強していました。即時実行や保留などの操作は行えるが、設定面に関する知識は保有していません。</t>
@@ -7010,7 +6951,7 @@
     <rPh sb="62" eb="64">
       <t>ホユウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>以下の内容を理解しました。
@@ -7065,7 +7006,7 @@
     <rPh sb="182" eb="184">
       <t>セッテイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>デベロッパーツールのElementsやConsole、スマホシミュレータ等の使用経験あり</t>
@@ -7078,7 +7019,7 @@
     <rPh sb="40" eb="42">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>・Q&amp;Aページの新規実装
@@ -7150,7 +7091,7 @@
     <rPh sb="118" eb="119">
       <t>カ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>コレクションやジェネリクス、JDBCなどについて学びました。Stream APIやラムダ式はデバッグ効率が下がる可能性があるため現場を選ぶと考えております。</t>
@@ -7178,11 +7119,11 @@
     <rPh sb="70" eb="71">
       <t>カンガ</t>
     </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>Oracle Certified Java Programmer, Silver SE 8</t>
     <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>Oracle Certified Java Programmer, Silver SE 8</t>
-    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>Linux関係の現場に参画した際に必要だと感じたため、6割程度実施。
@@ -7238,7 +7179,7 @@
     <rPh sb="92" eb="94">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>以下に習得技術や経験を記述します。
@@ -7257,7 +7198,7 @@
     <rPh sb="163" eb="165">
       <t>コウブンレンケイシヨウソウサ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>・外部ライブラリを使用しないJSONデータの作成や構文チェックおよび、制御文字のエスケープ対応(1件)
@@ -7378,7 +7319,7 @@
     <rPh sb="247" eb="249">
       <t>ジッソウケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>C言語は他多くの言語と違いエラーが出ずにクラッシュしてしまう言語です。</t>
@@ -7403,7 +7344,7 @@
     <rPh sb="30" eb="32">
       <t>ゲンゴ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>Gitなどもない環境でコーディングすることが多かったので、デグレ防止の意識が高まったと感じております。</t>
@@ -7425,7 +7366,7 @@
     <rPh sb="43" eb="44">
       <t>カン</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>繰り返しの中でメモリ生成を避けたコーディングができ、内部ツールなどの作成経験もあります。</t>
@@ -7444,14 +7385,14 @@
     <rPh sb="13" eb="14">
       <t>サ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>強みと弱み</t>
     <rPh sb="3" eb="4">
       <t>ヨワ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>通信系2</t>
@@ -7461,7 +7402,7 @@
     <rPh sb="2" eb="3">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>通信系1</t>
@@ -7471,19 +7412,19 @@
     <rPh sb="2" eb="3">
       <t>ケイ</t>
     </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>Java</t>
     <phoneticPr fontId="14"/>
   </si>
   <si>
-    <t>Java</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>VSCODE</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>テキストエディタ</t>
     <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>テキストエディタ</t>
-    <phoneticPr fontId="13"/>
   </si>
   <si>
     <r>
@@ -7534,14 +7475,14 @@
     <rPh sb="31" eb="33">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>更新日：</t>
     <rPh sb="0" eb="3">
       <t>コウシンビ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>手順書に従ったZabbixエージェントのお客様環境端末へのインストール経験あり</t>
@@ -7563,22 +7504,22 @@
     <rPh sb="35" eb="37">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Google Workspace</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>グループウェア</t>
   </si>
   <si>
     <t>グループウェア</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Proself</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>月次定例作業の手順書にインポート作業の経験あり。
@@ -7610,14 +7551,14 @@
     <rPh sb="43" eb="45">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>1か月</t>
     <rPh sb="2" eb="3">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>プロビジョニングシステム
@@ -7634,7 +7575,7 @@
     <rPh sb="35" eb="37">
       <t>カイシュウ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>銀行向け取引システム
@@ -7690,7 +7631,7 @@
     <rPh sb="72" eb="74">
       <t>キノウ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>人事イベント管理システム
@@ -7717,7 +7658,7 @@
     <rPh sb="33" eb="35">
       <t>セッテイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t xml:space="preserve">ファッション系ECサイト
@@ -7759,7 +7700,7 @@
     <rPh sb="83" eb="85">
       <t>キノウ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>スマホ購入時の新規契約時の回線開通時の処理工程内で使用されるプロビジョニングシステムの電文受入処理の緊急リリース対応を担当。対抗システムへのレスポンス返却個所の調査、およびRFC 9112に準拠し、Httpレスポンスヘッダ内の改行コードのLFをCRLFに統一する処理の実装、テストを担当。</t>
@@ -7847,7 +7788,7 @@
     <rPh sb="141" eb="143">
       <t>タントウ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>人事イベント（入社、異動、昇進、結婚、出産、退職等）を管理しているシステムのテスト経験がありました。前回の更改プロジェクトの残したテストデータを使用し、更改予定のDBのカラム定義に合わせSQLを修正し試験を行った経験があります。</t>
@@ -7899,7 +7840,7 @@
     <rPh sb="113" eb="114">
       <t>オコナケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>・Google Meetでの画面共有経験
@@ -7932,15 +7873,15 @@
     <rPh sb="50" eb="52">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Cisco AnyConnect</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>VPN</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>以下のような内容を想定した試験項目の作成、実施経験あり
@@ -7991,7 +7932,7 @@
     <rPh sb="88" eb="90">
       <t>ツイカ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>条件網羅などの試験項目の作成、実施経験あり。
@@ -8056,7 +7997,7 @@
     <rPh sb="72" eb="74">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>JMeterやCurlコマンドをドライバとした試験の経験あり</t>
@@ -8066,7 +8007,7 @@
     <rPh sb="26" eb="28">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>タブレットチーム開発資源を開発環境に配置し、試験を行った実績あり。</t>
@@ -8094,99 +8035,7 @@
     <rPh sb="28" eb="30">
       <t>ジッセキ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>・Httpレスポンスヘッダの改行コードの調査・改修（RFC9112準拠対応）
-・設計書レイアウト確認テスト後のパンくずリストの文言修正
-・コントローラーのマッピングやモデル値の修正
-・DBの命名規則変更に伴うDTOのフィールド名のリファクタリング
-・ログイン時の入力チェック(メールアドレスの@の有無や記号の有無のチェック）
-・JDBC接続ロジックの追加
-・Singletonパターンの実装
-・将来的な障害発生を懸念したlog4jによる実装担当処理のログ取得処理の追加</t>
-    <rPh sb="14" eb="16">
-      <t>カイギョウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>チョウサ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>カイシュウ</t>
-    </rPh>
-    <rPh sb="40" eb="43">
-      <t>セッケイショ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="53" eb="54">
-      <t>ゴ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>モンゴン</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="86" eb="87">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="88" eb="90">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="99" eb="101">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="102" eb="103">
-      <t>トモナ</t>
-    </rPh>
-    <rPh sb="113" eb="114">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="129" eb="130">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="131" eb="133">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="148" eb="150">
-      <t>ウム</t>
-    </rPh>
-    <rPh sb="151" eb="153">
-      <t>キゴウ</t>
-    </rPh>
-    <rPh sb="154" eb="156">
-      <t>ウム</t>
-    </rPh>
-    <rPh sb="168" eb="170">
-      <t>セツゾク</t>
-    </rPh>
-    <rPh sb="175" eb="177">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="193" eb="195">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="197" eb="200">
-      <t>ショウライテキ</t>
-    </rPh>
-    <rPh sb="201" eb="203">
-      <t>ショウガイ</t>
-    </rPh>
-    <rPh sb="203" eb="205">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="206" eb="208">
-      <t>ケネン</t>
-    </rPh>
-    <rPh sb="218" eb="220">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="222" eb="224">
-      <t>ショリ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ログイン時のメールアドレス入力規則チェックなど、Httpリクエスト、レスポンス時の処理の実装経験があります。
@@ -8327,7 +8176,7 @@
     <rPh sb="304" eb="306">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>C言語プログラム(PC)とJavaプログラム(タブレット)の連携の際に使用していた経験があります。</t>
@@ -8346,7 +8195,7 @@
     <rPh sb="41" eb="43">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>・Xpathによる孫要素や複数同名タグ存在時の要素指定の経験あり
@@ -8378,20 +8227,20 @@
     <rPh sb="51" eb="53">
       <t>イハン</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>JSON</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>XML</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>Linux
 シェル</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>・JSONキー名に"や\が含まれていた場合の試験経験あり
@@ -8426,7 +8275,7 @@
     <rPh sb="59" eb="61">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>C言語プログラム(PC)とJavaプログラム(タブレット)の連携の際に使用していた経験があります。テストで定例的に使用するタグなどはExcelのフラッシュフィル機能を使用し、タグの生成などを行い試験データを作成したことがあります。</t>
@@ -8460,7 +8309,7 @@
     <rPh sb="90" eb="92">
       <t>セイセイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>レコードの更新が他開発者のタスクに影響を与えることを理解しているので、
@@ -8521,15 +8370,15 @@
     <rPh sb="131" eb="133">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ant</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>ビルドツール</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>SpringBoot
@@ -8538,7 +8387,7 @@
 Lombok
 log4j
 Mockito</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>リフレクションやMockitoを使用したJUnitコードの作成経験あり。</t>
@@ -8551,7 +8400,7 @@
     <rPh sb="31" eb="33">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>だまし絵を描かないための－－要件定義のセオリー</t>
@@ -8567,7 +8416,7 @@
     <rPh sb="16" eb="18">
       <t>テイギ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>はじめよう！要件定義～ビギナーからベテランまで</t>
@@ -8577,15 +8426,15 @@
     <rPh sb="8" eb="10">
       <t>テイギ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>未読了</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>未読</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>Q&amp;A資料の作成経験</t>
@@ -8598,58 +8447,7 @@
     <rPh sb="8" eb="10">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>・踏み台サーバへの接続経験
-・ウィンドウの複製を利用した二窓以上での作業経験
-・操作ログ出力設定の経験</t>
-    <rPh sb="1" eb="2">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>セツゾク</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>フクセイ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>ニ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>マド</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>サギョウ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ケイケン</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>・本番環境へのファイルのアップロード経験あり
@@ -8661,11 +8459,11 @@
     <rPh sb="82" eb="84">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>TortoiseGit</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>・.gitignore等、ローカル資源を考慮したコミット経験
@@ -8683,7 +8481,7 @@
     <rPh sb="28" eb="30">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>コンパイル環境でのビルド経験や、実行環境でのログの確認経験があります。</t>
@@ -8705,7 +8503,7 @@
     <rPh sb="27" eb="29">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>マークアップ</t>
@@ -8715,125 +8513,22 @@
   </si>
   <si>
     <t>コンパイル</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>インタプリタ</t>
   </si>
   <si>
     <t>インタプリタ</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>OSシェル</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>データ記述言語</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・makeコマンドを使用したビルド作業
-・find . -nameを使用したビルドログの特定
-・grep -B によるビルドログのエラー箇所以前の出力
-・sedコマンドを使用した標準出力の改行コード（LF/CRLF）の可視化
-・tail -nを使用したアプリケーションログの監視
-・headコマンドをパイプ併用した最新ログファイル出力
-・grep -rnコマンドを使用したログからの警告やfailなどの文言抽出
-・curlコマンドを使用したhttpリクエスト/レスポンス処理の動作確認
-・reset&amp;&amp;を使用したクリア状態での証跡の取得
-・java起動シェルの環境変数等の解析経験</t>
-    <rPh sb="10" eb="12">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>サギョウ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>トクテイ</t>
-    </rPh>
-    <rPh sb="68" eb="70">
-      <t>カショ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>イゼン</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="89" eb="91">
-      <t>ヒョウジュン</t>
-    </rPh>
-    <rPh sb="91" eb="93">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="94" eb="96">
-      <t>カイギョウ</t>
-    </rPh>
-    <rPh sb="109" eb="112">
-      <t>カシカ</t>
-    </rPh>
-    <rPh sb="122" eb="124">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="153" eb="155">
-      <t>ヘイヨウ</t>
-    </rPh>
-    <rPh sb="157" eb="159">
-      <t>サイシン</t>
-    </rPh>
-    <rPh sb="165" eb="167">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="182" eb="184">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="191" eb="193">
-      <t>ケイコク</t>
-    </rPh>
-    <rPh sb="201" eb="203">
-      <t>モンゴン</t>
-    </rPh>
-    <rPh sb="203" eb="205">
-      <t>チュウシュツ</t>
-    </rPh>
-    <rPh sb="216" eb="218">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="235" eb="237">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="238" eb="240">
-      <t>ドウサ</t>
-    </rPh>
-    <rPh sb="240" eb="242">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="274" eb="276">
-      <t>キドウ</t>
-    </rPh>
-    <rPh sb="280" eb="282">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="282" eb="284">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="284" eb="285">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="286" eb="288">
-      <t>カイセキ</t>
-    </rPh>
-    <rPh sb="288" eb="290">
-      <t>ケイケン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>・build.xmlへの外部 jarのクラスパスの設定経験</t>
@@ -8846,7 +8541,7 @@
     <rPh sb="27" eb="29">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>・リモートワーク使用用途でのVPNの接続経験あり</t>
@@ -8862,113 +8557,18 @@
     <rPh sb="20" eb="22">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>・編集時の排他制御設定経験
-・保存時の自動バックアップ設定経験
-・文言置換用秀丸マクロの作成経験</t>
-    <rPh sb="1" eb="3">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ハイタ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>セイギョ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>モンゴン</t>
-    </rPh>
-    <rPh sb="35" eb="38">
-      <t>チカンヨウ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ヒデマル</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>ケイケン</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>・除外拡張子などを考慮した関数の呼び出し元や環境変数等のGrep経験
-・アウトラインを使用したソースコードの解析経験</t>
-    <rPh sb="1" eb="3">
-      <t>ジョガイ</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>カクチョウシ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>コウリョ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>カンスウ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>カイセキ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ケイケン</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>CentOS6のインストール経験</t>
     <rPh sb="14" eb="16">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>デザイン</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>次期試験端末へのインストール、およびウイルス定義ファイルの最新化作業など</t>
@@ -8993,7 +8593,7 @@
     <rPh sb="32" eb="34">
       <t>サギョウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>Linuxを用いた案件は経験していますが、開発案件ではなかったためLinux上での開発経験に少し難があるかもしれません。</t>
@@ -9027,76 +8627,14 @@
     <rPh sb="48" eb="49">
       <t>ナン</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>JavaSilver資格 PDF</t>
     <rPh sb="10" eb="12">
       <t>シカク</t>
     </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>JavaGold資格 PDF</t>
-    <rPh sb="8" eb="10">
-      <t>シカク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>HTML Lv1合格レポート</t>
-    <rPh sb="8" eb="10">
-      <t>ゴウカク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応用情報午後　勉強状況</t>
-    <rPh sb="0" eb="2">
-      <t>オウヨウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ゴゴ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ベンキョウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応用情報午前　勉強状況</t>
-    <rPh sb="0" eb="2">
-      <t>オウヨウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ゴゼン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ベンキョウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>購入したKindle本</t>
-    <rPh sb="0" eb="2">
-      <t>コウニュウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ホン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>・WHEREコマンドによるファイル名の検索
@@ -9130,7 +8668,7 @@
     <rPh sb="109" eb="111">
       <t>シュトク</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>stdio.h
@@ -9142,7 +8680,7 @@
     <rPh sb="38" eb="40">
       <t>ザガク</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>標準ライブラリでのプログラミング経験が豊富。メモリ領域初期化漏れや他変数の領域破壊などがないように意識しながら実装する作法を心得ております。別プロセスやタブレットから呼び出されるインターフェースの修正を主に担当し、パラメータに応じたデータの加工処理のロジックの実装経験あり。30年運用されているシステムでの実装だったので完全新規での仕様追加は少なく、既存仕様に対応する関数を流用し、機能拡張していくという業務が中心。ビルド時の警告は全て対応する作法を心得ております。
@@ -9333,29 +8871,525 @@
     <rPh sb="346" eb="348">
       <t>ケイケン</t>
     </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・アプリログ時刻補正 秀丸マクロの作成経験
+・編集時の排他制御設定経験
+・保存時の自動バックアップ設定経験</t>
+    <rPh sb="23" eb="25">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ハイタ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・除外拡張子などを考慮した関数の呼び出し元や環境変数等のGrep経験
+・アウトラインを使用したソースコードの解析経験
+・改行コード、文字コードを意識したファイルの保存</t>
+    <rPh sb="1" eb="3">
+      <t>ジョガイ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>カクチョウシ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウリョ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>カイセキ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>カイギョウ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>イシキ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・Git add
+・Git status
+・Git commit(Amend)
+・Git push(Force)
+・featureブランチの作成
+・署名付きコミットの設定</t>
+    <rPh sb="69" eb="71">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・Httpレスポンスヘッダの改行コードの調査・改修（RFC9112準拠対応）
+・クラスパスの追加やgetPropertyによる実行時チェック
+・将来的な障害発生を備えたlog4jによる実装担当処理のログ取得処理の追加
+・設計書レイアウト確認テスト後のパンくずリストの文言修正
+・コントローラーのマッピングやモデル値の修正
+・DBの命名規則変更に伴うDTOのフィールド名のリファクタリング
+・ログイン時の入力チェック(メールアドレスの@の有無や記号の有無のチェック）
+・JDBC接続ロジックの追加
+・Singletonパターンの実装</t>
+    <rPh sb="14" eb="16">
+      <t>カイギョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カイシュウ</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>ソナ</t>
+    </rPh>
+    <rPh sb="110" eb="113">
+      <t>セッケイショ</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>モンゴン</t>
+    </rPh>
+    <rPh sb="135" eb="137">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="157" eb="158">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="159" eb="161">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="170" eb="172">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="173" eb="174">
+      <t>トモナ</t>
+    </rPh>
+    <rPh sb="184" eb="185">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="200" eb="201">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="202" eb="204">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="219" eb="221">
+      <t>ウム</t>
+    </rPh>
+    <rPh sb="222" eb="224">
+      <t>キゴウ</t>
+    </rPh>
+    <rPh sb="225" eb="227">
+      <t>ウム</t>
+    </rPh>
+    <rPh sb="239" eb="241">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="246" eb="248">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>以下の内容を理解しました。
+・JSPがTomcatによりclassファイルにコンパイルされていること
+・サーブレットにはinitやdestroyなどライフサイクルがあること
+・サーブレット処理前後にフィルター処理を行うことができること
+・初回作成時のシングルトンのインスタンスを共有し、マルチスレッドで受け付けていること
+・Httpリクエスト時のインスタンス変数の取り扱いは危険であること
+・DB接続はコネクションプールを使いまわすこと</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>ゼンゴ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="107" eb="108">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="179" eb="181">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="182" eb="183">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="184" eb="185">
+      <t>アツカ</t>
+    </rPh>
+    <rPh sb="187" eb="189">
+      <t>キケン</t>
+    </rPh>
+    <rPh sb="198" eb="200">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="211" eb="212">
+      <t>ツカ</t>
+    </rPh>
     <phoneticPr fontId="14"/>
   </si>
   <si>
-    <t>画面証跡</t>
+    <t>　　　HTML Lv1合格レポート</t>
+    <rPh sb="11" eb="13">
+      <t>ゴウカク</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>合格資格や学習状況などの画面証跡</t>
     <rPh sb="0" eb="2">
+      <t>ゴウカク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シカク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
       <t>ガメン</t>
     </rPh>
+    <rPh sb="14" eb="16">
+      <t>ショウセキ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  JavaGold資格 PDF</t>
+    <rPh sb="10" eb="12">
+      <t>シカク</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> SQL系の基礎知識証明</t>
+    <rPh sb="4" eb="5">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>チシキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ショウメイ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> ネットワーク系の基礎知識証明</t>
+    <rPh sb="7" eb="8">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>チシキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ショウメイ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 応用情報</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 午前 勉強状況</t>
+    <rPh sb="1" eb="3">
+      <t>ゴゼン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>午後 勉強状況</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  購入したKindle本</t>
     <rPh sb="2" eb="4">
-      <t>ショウセキ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>・ログ監視専用ttlファイル作成(TeraTermマクロ)
+・踏み台サーバへの接続経験
+・ウィンドウの複製を利用した二窓以上での作業経験
+・操作ログ出力設定の経験</t>
+    <rPh sb="3" eb="5">
+      <t>カンシ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>フクセイ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ニ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>マド</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・makeビルド結果表示シェルにビルド詳細表示処理の追加
+・find . -nameを使用したビルドログの特定
+・grep -B によるビルドログのエラー箇所以前の出力
+・sedコマンドを使用した標準出力の改行コード（LF/CRLF）の可視化
+・tail -n -fを使用したアプリケーションログの監視
+・headコマンドをパイプ併用した最新ログファイル出力
+・grep -rnコマンドを使用したログからの警告やエラーなどの文言抽出
+・curlコマンドを使用したhttpリクエスト/レスポンス処理の動作確認
+・reset&amp;&amp;を使用したクリア状態での証跡の取得
+・java起動シェルの環境変数等の解析経験</t>
+    <rPh sb="8" eb="10">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>カショ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>イゼン</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>ヒョウジュン</t>
+    </rPh>
+    <rPh sb="100" eb="102">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>カイギョウ</t>
+    </rPh>
+    <rPh sb="118" eb="121">
+      <t>カシカ</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="165" eb="167">
+      <t>ヘイヨウ</t>
+    </rPh>
+    <rPh sb="169" eb="171">
+      <t>サイシン</t>
+    </rPh>
+    <rPh sb="177" eb="179">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="194" eb="196">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="203" eb="205">
+      <t>ケイコク</t>
+    </rPh>
+    <rPh sb="212" eb="214">
+      <t>モンゴン</t>
+    </rPh>
+    <rPh sb="214" eb="216">
+      <t>チュウシュツ</t>
+    </rPh>
+    <rPh sb="227" eb="229">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="246" eb="248">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="249" eb="251">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="251" eb="253">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="285" eb="287">
+      <t>キドウ</t>
+    </rPh>
+    <rPh sb="291" eb="293">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="293" eb="295">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="295" eb="296">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="297" eb="299">
+      <t>カイセキ</t>
+    </rPh>
+    <rPh sb="299" eb="301">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -9656,89 +9690,92 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1">
@@ -9747,10 +9784,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1">
@@ -9762,53 +9799,44 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -9834,23 +9862,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>120195</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>470206</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>234567</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>237607</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>148418</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="23" name="図 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB6A8C15-92B4-4033-4C01-119F80461219}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7270BDE4-AB0F-994A-1089-0B6F9FD4D6B3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9866,28 +9894,35 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688731" y="6770077"/>
-          <a:ext cx="4133667" cy="5312125"/>
+          <a:off x="120195" y="13036827"/>
+          <a:ext cx="7207325" cy="5913113"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>140804</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>223630</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>331208</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>204296</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>324266</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>221559</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -9910,8 +9945,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688731" y="725365"/>
-          <a:ext cx="3994669" cy="5523642"/>
+          <a:off x="140804" y="26231021"/>
+          <a:ext cx="3836092" cy="5282234"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9922,16 +9957,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>35719</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>115512</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>206036</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>135973</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>241755</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>13359</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -9954,8 +9989,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688731" y="13298365"/>
-          <a:ext cx="3869497" cy="861338"/>
+          <a:off x="35719" y="39093469"/>
+          <a:ext cx="3858666" cy="858630"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9966,16 +10001,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>35719</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>115513</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>640280</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>88885</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>676000</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>206469</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -9998,8 +10033,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688731" y="14265519"/>
-          <a:ext cx="3615011" cy="1781404"/>
+          <a:off x="35719" y="40054252"/>
+          <a:ext cx="3605455" cy="1772325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10010,23 +10045,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>115956</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>211857</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>681726</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>168519</xdr:rowOff>
+      <xdr:colOff>441243</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>173934</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
+        <xdr:cNvPr id="9" name="図 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7724C2EC-7D30-89C1-8EA4-5E9D7E49DF85}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95EDFA44-5E45-F8A6-FF18-6141682DB8FD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10042,8 +10077,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688732" y="19343077"/>
-          <a:ext cx="4345186" cy="3311769"/>
+          <a:off x="115956" y="39189814"/>
+          <a:ext cx="4665374" cy="3805207"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10054,23 +10089,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>91108</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>239752</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>325287</xdr:colOff>
-      <xdr:row>122</xdr:row>
-      <xdr:rowOff>200201</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>364988</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>38263</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
+        <xdr:cNvPr id="12" name="図 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95EDFA44-5E45-F8A6-FF18-6141682DB8FD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A52CB2F2-AFA8-941C-E7A6-7E09D3AF7A71}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10086,35 +10121,42 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688731" y="25871365"/>
-          <a:ext cx="4677479" cy="3827028"/>
+          <a:off x="91108" y="7271687"/>
+          <a:ext cx="3926510" cy="3161250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>199725</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>35719</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>115513</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>443170</xdr:colOff>
-      <xdr:row>130</xdr:row>
-      <xdr:rowOff>241788</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>277508</xdr:colOff>
+      <xdr:row>150</xdr:row>
+      <xdr:rowOff>168222</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71123FA8-35FA-D954-29D8-1367BC075C8A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9046DC8F-B0DC-446F-BD81-E22FABC96CF8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10130,8 +10172,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688731" y="29939706"/>
-          <a:ext cx="4795362" cy="1734582"/>
+          <a:off x="35719" y="41975817"/>
+          <a:ext cx="3894419" cy="773296"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10142,23 +10184,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>135</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>235470</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>273880</xdr:colOff>
-      <xdr:row>148</xdr:row>
-      <xdr:rowOff>36635</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1283</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>231912</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
+        <xdr:cNvPr id="18" name="図 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A52CB2F2-AFA8-941C-E7A6-7E09D3AF7A71}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35C6A767-EB20-4E34-A112-0C392EDE789D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10174,8 +10216,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688731" y="32641442"/>
-          <a:ext cx="3937341" cy="3179885"/>
+          <a:off x="4340087" y="26242861"/>
+          <a:ext cx="4126022" cy="5280747"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10186,23 +10228,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>162</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>35719</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>115512</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>505558</xdr:colOff>
-      <xdr:row>183</xdr:row>
-      <xdr:rowOff>11989</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>248521</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>45906</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="図 12">
+        <xdr:cNvPr id="19" name="図 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC972B1D-EDE7-A445-A531-CEC57E078200}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDAD37A7-2D70-49AC-874D-E1AAD2493CDB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10218,8 +10260,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688731" y="39169731"/>
-          <a:ext cx="5546481" cy="5089547"/>
+          <a:off x="4375806" y="39093469"/>
+          <a:ext cx="4337541" cy="3293133"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10230,23 +10272,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>192</xdr:row>
-      <xdr:rowOff>234766</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>314739</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>183160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>207063</xdr:colOff>
-      <xdr:row>205</xdr:row>
-      <xdr:rowOff>168520</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>285800</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>223629</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
+        <xdr:cNvPr id="20" name="図 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{201FDF3B-3323-55D8-E3C2-064EB0B10050}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2ED7A0C1-8DA0-4216-A087-CB5DCC277025}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10262,8 +10304,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688731" y="46899939"/>
-          <a:ext cx="3181794" cy="3077004"/>
+          <a:off x="3967369" y="42523856"/>
+          <a:ext cx="4783257" cy="1721839"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10274,23 +10316,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>189</xdr:row>
-      <xdr:rowOff>74621</xdr:rowOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>16566</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>188010</xdr:colOff>
-      <xdr:row>192</xdr:row>
-      <xdr:rowOff>168520</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>275185</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>194484</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="図 14">
+        <xdr:cNvPr id="21" name="図 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14F65800-465C-AB66-2CE7-CE8874813249}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D7CAAA6-0AD9-445B-8B35-806AD71BE1F4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10306,35 +10348,42 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688731" y="46014429"/>
-          <a:ext cx="3162741" cy="819264"/>
+          <a:off x="4340087" y="7288696"/>
+          <a:ext cx="4399924" cy="4021049"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>40628</xdr:colOff>
-      <xdr:row>214</xdr:row>
-      <xdr:rowOff>227135</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>119463</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>16565</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>224</xdr:row>
-      <xdr:rowOff>57109</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>378412</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>156175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="図 15">
+        <xdr:cNvPr id="13" name="図 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10C54494-90C7-0664-5958-5091FC9354A9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D31707F2-0F78-2BFF-3C3D-52BDA89507B9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10350,35 +10399,42 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="729359" y="52211654"/>
-          <a:ext cx="5689026" cy="2247859"/>
+          <a:off x="119463" y="19538674"/>
+          <a:ext cx="8036319" cy="5183718"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>7327</xdr:colOff>
-      <xdr:row>227</xdr:row>
-      <xdr:rowOff>125390</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>137302</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>236</xdr:row>
-      <xdr:rowOff>80597</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>82727</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="図 16">
+        <xdr:cNvPr id="35" name="図 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46F4023D-7A26-38CE-5AF5-8D273D221C53}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3291B87E-F1CC-8B2D-4D4F-DC973F02E716}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10394,35 +10450,42 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="696058" y="55253159"/>
-          <a:ext cx="5722327" cy="2131303"/>
+          <a:off x="137302" y="29129935"/>
+          <a:ext cx="5577698" cy="2004293"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>135816</xdr:colOff>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>241789</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>50637</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>662609</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>193690</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="36" name="図 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9046DC8F-B0DC-446F-BD81-E22FABC96CF8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F09A95E-B1D8-F402-9B48-F11DAA3EB68A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10438,12 +10501,163 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688731" y="16199827"/>
-          <a:ext cx="3905250" cy="776003"/>
+          <a:off x="135816" y="26247587"/>
+          <a:ext cx="5554336" cy="2115256"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>455544</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>16565</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>176494</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>165653</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="10" name="グループ化 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E3087EA-862E-D795-7587-1A8E53B38F99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="4108174" y="13293587"/>
+          <a:ext cx="3158233" cy="629479"/>
+          <a:chOff x="5242891" y="14121848"/>
+          <a:chExt cx="6903017" cy="1375866"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="5" name="図 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDDFAFF3-3123-D6A7-31B6-AA106F39781A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5242891" y="14602239"/>
+            <a:ext cx="6868484" cy="895475"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="8" name="図 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B3D65C4-C712-C004-5BCF-5968E0D43C6A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5267740" y="14121848"/>
+            <a:ext cx="6878168" cy="486663"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>422413</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>231913</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>539710</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>41413</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C24460B-9006-456E-80B5-711610C432FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6137413" y="1018761"/>
+          <a:ext cx="2867123" cy="3892826"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -10732,7 +10946,7 @@
     </row>
     <row r="3" spans="2:10">
       <c r="B3" s="30" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="2:10">
@@ -10742,7 +10956,7 @@
     </row>
     <row r="5" spans="2:10">
       <c r="B5" s="31" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="19.5" thickBot="1"/>
@@ -10906,14 +11120,14 @@
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="13"/>
+  <phoneticPr fontId="14"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -10927,7 +11141,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C227"/>
+  <dimension ref="A2:J129"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -10935,129 +11149,101 @@
     <col min="3" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="24">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:10" ht="24">
+      <c r="A2" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="J4" s="39" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="38" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="39" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="39" t="s">
+        <v>485</v>
+      </c>
+      <c r="H30" s="39" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
-      <c r="B3" s="48" t="s">
+    <row r="54" spans="1:2">
+      <c r="A54" s="39" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="6" spans="2:3">
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-    </row>
-    <row r="8" spans="2:3">
-      <c r="C8" s="32"/>
-    </row>
-    <row r="9" spans="2:3">
-      <c r="C9" s="32"/>
-    </row>
-    <row r="10" spans="2:3">
-      <c r="C10" s="32"/>
-    </row>
-    <row r="11" spans="2:3">
-      <c r="C11" s="33"/>
-    </row>
-    <row r="12" spans="2:3">
-      <c r="C12" s="32"/>
-    </row>
-    <row r="14" spans="2:3">
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-    </row>
-    <row r="21" spans="2:3">
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-    </row>
-    <row r="26" spans="2:3">
-      <c r="C26" s="26"/>
-    </row>
-    <row r="27" spans="2:3">
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-    </row>
-    <row r="28" spans="2:3">
-      <c r="C28" s="26"/>
-    </row>
-    <row r="29" spans="2:3">
-      <c r="C29" s="26"/>
-    </row>
-    <row r="31" spans="2:3">
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-    </row>
-    <row r="32" spans="2:3">
-      <c r="C32" s="26"/>
-    </row>
-    <row r="33" spans="2:3">
-      <c r="C33" s="26"/>
-    </row>
-    <row r="34" spans="2:3">
-      <c r="C34" s="26"/>
-    </row>
-    <row r="35" spans="2:3">
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-    </row>
-    <row r="36" spans="2:3">
-      <c r="C36" s="29"/>
-    </row>
-    <row r="38" spans="2:3">
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-    </row>
-    <row r="135" spans="2:2">
-      <c r="B135" s="48" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="162" spans="2:2">
-      <c r="B162" s="48" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="189" spans="2:2">
-      <c r="B189" s="48" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="215" spans="2:2">
-      <c r="B215" s="48" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="227" spans="2:2">
-      <c r="B227" s="48" t="s">
-        <v>477</v>
-      </c>
+    <row r="59" spans="1:2">
+      <c r="B59" s="38"/>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="39" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="39" t="s">
+        <v>487</v>
+      </c>
+      <c r="B109" s="25"/>
+      <c r="C109" s="25"/>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="C111" s="32"/>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="C112" s="32"/>
+    </row>
+    <row r="113" spans="2:3">
+      <c r="C113" s="32"/>
+    </row>
+    <row r="114" spans="2:3">
+      <c r="C114" s="33"/>
+    </row>
+    <row r="115" spans="2:3">
+      <c r="C115" s="32"/>
+    </row>
+    <row r="117" spans="2:3">
+      <c r="B117" s="25"/>
+      <c r="C117" s="25"/>
+    </row>
+    <row r="120" spans="2:3">
+      <c r="B120" s="25"/>
+      <c r="C120" s="25"/>
+    </row>
+    <row r="124" spans="2:3">
+      <c r="B124" s="25"/>
+      <c r="C124" s="25"/>
+    </row>
+    <row r="127" spans="2:3">
+      <c r="B127" s="25"/>
+      <c r="C127" s="25"/>
+    </row>
+    <row r="129" spans="3:3">
+      <c r="C129" s="26"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="13"/>
+  <phoneticPr fontId="14"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;P / &amp;N ページ</oddFooter>
   </headerFooter>
-  <rowBreaks count="8" manualBreakCount="8">
-    <brk id="26" max="14" man="1"/>
-    <brk id="53" max="14" man="1"/>
-    <brk id="79" max="14" man="1"/>
-    <brk id="105" max="14" man="1"/>
-    <brk id="132" max="14" man="1"/>
-    <brk id="157" max="14" man="1"/>
-    <brk id="210" max="14" man="1"/>
-    <brk id="237" max="14" man="1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="52" max="13" man="1"/>
+    <brk id="79" max="13" man="1"/>
   </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -11141,10 +11327,10 @@
     </row>
     <row r="6" spans="1:7" ht="73.5" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>37</v>
@@ -11164,7 +11350,7 @@
     </row>
     <row r="7" spans="1:7" ht="43.5" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>40</v>
@@ -11212,7 +11398,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:G4" xr:uid="{21FFF12F-B684-4050-9B34-306B03FBB89B}"/>
-  <phoneticPr fontId="13"/>
+  <phoneticPr fontId="14"/>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" xr:uid="{27A4E6AC-D535-4917-9A75-E6F6C321D2F1}"/>
     <hyperlink ref="C7" r:id="rId2" xr:uid="{30F668CC-9B59-46FD-807B-98AF09EED418}"/>
@@ -11258,7 +11444,7 @@
         <v>48</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>49</v>
@@ -11268,7 +11454,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="19.5" customHeight="1" thickTop="1">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="46" t="s">
         <v>51</v>
       </c>
       <c r="B5" s="16" t="s">
@@ -11285,7 +11471,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="41"/>
+      <c r="A6" s="44"/>
       <c r="B6" s="16" t="s">
         <v>55</v>
       </c>
@@ -11300,7 +11486,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="41"/>
+      <c r="A7" s="44"/>
       <c r="B7" s="16" t="s">
         <v>56</v>
       </c>
@@ -11315,7 +11501,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="41"/>
+      <c r="A8" s="44"/>
       <c r="B8" s="16" t="s">
         <v>58</v>
       </c>
@@ -11330,8 +11516,8 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="41"/>
-      <c r="B9" s="37" t="s">
+      <c r="A9" s="44"/>
+      <c r="B9" s="40" t="s">
         <v>60</v>
       </c>
       <c r="C9" s="16" t="s">
@@ -11345,90 +11531,90 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="56.25">
-      <c r="A10" s="41"/>
-      <c r="B10" s="38"/>
+      <c r="A10" s="44"/>
+      <c r="B10" s="41"/>
       <c r="C10" s="16" t="s">
         <v>63</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E10" s="21">
         <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="41"/>
-      <c r="B11" s="39"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="42"/>
       <c r="C11" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="44" t="s">
-        <v>450</v>
+      <c r="D11" s="13" t="s">
+        <v>447</v>
       </c>
       <c r="E11" s="21">
         <v>0.2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="41"/>
-      <c r="B12" s="37" t="s">
+      <c r="A12" s="44"/>
+      <c r="B12" s="40" t="s">
         <v>65</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>66</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E12" s="21">
         <v>0.9</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="41"/>
-      <c r="B13" s="39"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="42"/>
       <c r="C13" s="16" t="s">
         <v>67</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E13" s="21">
         <v>0.9</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="112.5">
-      <c r="A14" s="41"/>
-      <c r="B14" s="40" t="s">
-        <v>392</v>
+      <c r="A14" s="44"/>
+      <c r="B14" s="43" t="s">
+        <v>390</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E14" s="21">
         <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="56.25">
-      <c r="A15" s="41"/>
-      <c r="B15" s="41"/>
+      <c r="A15" s="44"/>
+      <c r="B15" s="44"/>
       <c r="C15" s="16" t="s">
         <v>69</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E15" s="21">
         <v>0.8</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="57" customHeight="1">
-      <c r="A16" s="41"/>
-      <c r="B16" s="41"/>
+      <c r="A16" s="44"/>
+      <c r="B16" s="44"/>
       <c r="C16" s="16" t="s">
         <v>70</v>
       </c>
@@ -11440,33 +11626,33 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="168.75">
-      <c r="A17" s="41"/>
-      <c r="B17" s="41"/>
+      <c r="A17" s="44"/>
+      <c r="B17" s="44"/>
       <c r="C17" s="16" t="s">
         <v>72</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E17" s="21">
         <v>0.9</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="57" customHeight="1">
-      <c r="A18" s="41"/>
-      <c r="B18" s="42"/>
+      <c r="A18" s="44"/>
+      <c r="B18" s="45"/>
       <c r="C18" s="16" t="s">
         <v>73</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E18" s="21">
         <v>0.8</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="41"/>
+      <c r="A19" s="44"/>
       <c r="B19" s="22" t="s">
         <v>74</v>
       </c>
@@ -11481,7 +11667,7 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="41"/>
+      <c r="A20" s="44"/>
       <c r="B20" s="22" t="s">
         <v>76</v>
       </c>
@@ -11496,7 +11682,7 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="42"/>
+      <c r="A21" s="45"/>
       <c r="B21" s="22" t="s">
         <v>79</v>
       </c>
@@ -11559,7 +11745,7 @@
     <mergeCell ref="B14:B18"/>
     <mergeCell ref="A5:A21"/>
   </mergeCells>
-  <phoneticPr fontId="13"/>
+  <phoneticPr fontId="14"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -11595,7 +11781,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="27" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B2" s="27"/>
     </row>
@@ -11618,7 +11804,7 @@
         <v>89</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>90</v>
@@ -11632,19 +11818,19 @@
     </row>
     <row r="5" spans="1:8" ht="225.75" thickTop="1">
       <c r="A5" s="23" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>92</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="F5" s="23">
         <v>2026</v>
@@ -11658,22 +11844,22 @@
     </row>
     <row r="6" spans="1:8" ht="206.25">
       <c r="A6" s="23" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>93</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>437</v>
+        <v>477</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F6" s="23">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="G6" s="24">
         <v>0.6</v>
@@ -11684,19 +11870,19 @@
     </row>
     <row r="7" spans="1:8" ht="93.75">
       <c r="A7" s="23" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B7" s="23" t="s">
         <v>107</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F7" s="23" t="s">
         <v>77</v>
@@ -11708,7 +11894,7 @@
     </row>
     <row r="8" spans="1:8" ht="75">
       <c r="A8" s="16" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>98</v>
@@ -11717,7 +11903,7 @@
         <v>99</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="E8" s="16"/>
       <c r="F8" s="16">
@@ -11729,17 +11915,17 @@
       <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:8" ht="187.5">
-      <c r="A9" s="46" t="s">
-        <v>466</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>443</v>
+      <c r="A9" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>440</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="23" t="s">
@@ -11752,7 +11938,7 @@
     </row>
     <row r="10" spans="1:8" ht="75">
       <c r="A10" s="16" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>94</v>
@@ -11761,10 +11947,10 @@
         <v>95</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F10" s="23">
         <v>2026</v>
@@ -11776,7 +11962,7 @@
     </row>
     <row r="11" spans="1:8" ht="56.25">
       <c r="A11" s="16" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>96</v>
@@ -11785,7 +11971,7 @@
         <v>97</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="23">
@@ -11798,7 +11984,7 @@
     </row>
     <row r="12" spans="1:8" ht="75">
       <c r="A12" s="23" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B12" s="23" t="s">
         <v>101</v>
@@ -11810,7 +11996,7 @@
         <v>103</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F12" s="23">
         <v>2026</v>
@@ -11822,7 +12008,7 @@
     </row>
     <row r="13" spans="1:8" ht="131.25">
       <c r="A13" s="23" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B13" s="23" t="s">
         <v>104</v>
@@ -11831,10 +12017,10 @@
         <v>105</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F13" s="23">
         <v>2018</v>
@@ -11846,16 +12032,16 @@
     </row>
     <row r="14" spans="1:8" ht="75">
       <c r="A14" s="16" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>106</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E14" s="23"/>
       <c r="F14" s="23">
@@ -11868,16 +12054,16 @@
     </row>
     <row r="15" spans="1:8" ht="37.5">
       <c r="A15" s="23" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B15" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="D15" s="20" t="s">
         <v>441</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>439</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>444</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23" t="s">
@@ -11890,19 +12076,19 @@
     </row>
     <row r="16" spans="1:8" ht="112.5">
       <c r="A16" s="23" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>100</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F16" s="23">
         <v>2026</v>
@@ -11914,16 +12100,16 @@
     </row>
     <row r="17" spans="1:8" ht="56.25">
       <c r="A17" s="23" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B17" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="C17" s="20" t="s">
         <v>442</v>
       </c>
-      <c r="C17" s="20" t="s">
-        <v>445</v>
-      </c>
       <c r="D17" s="20" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E17" s="23"/>
       <c r="F17" s="23" t="s">
@@ -11961,7 +12147,7 @@
     <sortCondition descending="1" ref="G8:G17"/>
     <sortCondition descending="1" ref="F8:F17"/>
   </sortState>
-  <phoneticPr fontId="13"/>
+  <phoneticPr fontId="14"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -12010,7 +12196,7 @@
         <v>110</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>111</v>
@@ -12030,7 +12216,7 @@
         <v>118</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16">
@@ -12064,7 +12250,7 @@
         <v>123</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>115</v>
@@ -12102,7 +12288,7 @@
         <v>117</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="23">
@@ -12136,7 +12322,7 @@
         <v>114</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>115</v>
@@ -12174,7 +12360,7 @@
         <v>128</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D13" s="23" t="s">
         <v>129</v>
@@ -12194,7 +12380,7 @@
         <v>131</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>129</v>
@@ -12214,7 +12400,7 @@
         <v>121</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23">
@@ -12232,7 +12418,7 @@
         <v>125</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="23">
@@ -12250,7 +12436,7 @@
         <v>116</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="23">
@@ -12268,7 +12454,7 @@
         <v>130</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="23">
@@ -12278,15 +12464,15 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="112.5">
+    <row r="19" spans="1:6" ht="131.25">
       <c r="A19" s="23" t="s">
         <v>113</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>385</v>
+        <v>478</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="23">
@@ -12301,10 +12487,10 @@
         <v>113</v>
       </c>
       <c r="B20" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="C20" s="20" t="s">
         <v>451</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>454</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="23">
@@ -12319,10 +12505,10 @@
         <v>113</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="23">
@@ -12340,7 +12526,7 @@
         <v>141</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="23">
@@ -12390,7 +12576,7 @@
         <v>139</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>115</v>
@@ -12430,7 +12616,7 @@
         <v>138</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D27" s="23" t="s">
         <v>115</v>
@@ -12488,7 +12674,7 @@
         <v>137</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D30" s="23"/>
       <c r="E30" s="23">
@@ -12506,7 +12692,7 @@
         <v>140</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D31" s="23" t="s">
         <v>129</v>
@@ -12544,7 +12730,7 @@
         <v>143</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>129</v>
@@ -12615,10 +12801,10 @@
         <v>151</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D37" s="23"/>
       <c r="E37" s="23">
@@ -12654,7 +12840,7 @@
     <sortCondition ref="A5:A37"/>
     <sortCondition ref="E5:E37"/>
   </sortState>
-  <phoneticPr fontId="13"/>
+  <phoneticPr fontId="14"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="77" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -12704,7 +12890,7 @@
         <v>157</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>158</v>
@@ -12730,7 +12916,7 @@
         <v>161</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16" t="s">
@@ -12754,7 +12940,7 @@
         <v>161</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>162</v>
@@ -12780,7 +12966,7 @@
         <v>165</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>162</v>
@@ -12806,7 +12992,7 @@
         <v>167</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>162</v>
@@ -12853,7 +13039,7 @@
         <v>180</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>181</v>
@@ -12880,7 +13066,7 @@
         <v>172</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>162</v>
@@ -12904,7 +13090,7 @@
         <v>174</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D12" s="23" t="s">
         <v>162</v>
@@ -12952,7 +13138,7 @@
         <v>178</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>162</v>
@@ -12978,7 +13164,7 @@
         <v>178</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>162</v>
@@ -13018,7 +13204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="37.5">
+    <row r="17" spans="1:8" ht="112.5">
       <c r="A17" s="13" t="s">
         <v>185</v>
       </c>
@@ -13026,7 +13212,7 @@
         <v>183</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>186</v>
+        <v>476</v>
       </c>
       <c r="D17" s="23" t="s">
         <v>162</v>
@@ -13045,14 +13231,14 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="56.25">
-      <c r="A18" s="47" t="s">
-        <v>458</v>
+      <c r="A18" s="20" t="s">
+        <v>454</v>
       </c>
       <c r="B18" s="20" t="s">
         <v>183</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D18" s="23" t="s">
         <v>162</v>
@@ -13070,18 +13256,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="56.25">
-      <c r="A19" s="47" t="s">
+    <row r="19" spans="1:8" ht="75">
+      <c r="A19" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>188</v>
-      </c>
       <c r="C19" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
+        <v>488</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>162</v>
+      </c>
       <c r="F19" s="23">
         <v>2018</v>
       </c>
@@ -13094,13 +13284,13 @@
     </row>
     <row r="20" spans="1:8" ht="75">
       <c r="A20" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D20" s="23" t="s">
         <v>162</v>
@@ -13120,13 +13310,13 @@
     </row>
     <row r="21" spans="1:8" ht="37.5">
       <c r="A21" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" s="20" t="s">
         <v>192</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>193</v>
       </c>
       <c r="D21" s="23" t="s">
         <v>162</v>
@@ -13146,13 +13336,13 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="B22" s="20" t="s">
-        <v>190</v>
-      </c>
       <c r="C22" s="20" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D22" s="23" t="s">
         <v>162</v>
@@ -13170,13 +13360,13 @@
     </row>
     <row r="23" spans="1:8" ht="37.5">
       <c r="A23" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B23" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>195</v>
-      </c>
       <c r="C23" s="20" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>162</v>
@@ -13194,15 +13384,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="37.5">
+    <row r="24" spans="1:8" ht="56.25">
       <c r="A24" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="B24" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="B24" s="20" t="s">
-        <v>197</v>
-      </c>
       <c r="C24" s="20" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D24" s="23" t="s">
         <v>162</v>
@@ -13222,13 +13412,13 @@
     </row>
     <row r="25" spans="1:8" ht="56.25">
       <c r="A25" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>162</v>
@@ -13248,13 +13438,13 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="B26" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>200</v>
-      </c>
       <c r="C26" s="20" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D26" s="23" t="s">
         <v>162</v>
@@ -13274,13 +13464,13 @@
     </row>
     <row r="27" spans="1:8" ht="37.5">
       <c r="A27" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="B27" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="C27" s="20" t="s">
         <v>202</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>203</v>
       </c>
       <c r="D27" s="23" t="s">
         <v>162</v>
@@ -13300,13 +13490,13 @@
     </row>
     <row r="28" spans="1:8" ht="56.25">
       <c r="A28" s="20" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D28" s="23" t="s">
         <v>162</v>
@@ -13322,10 +13512,10 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="23" t="s">
@@ -13342,10 +13532,10 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="23"/>
@@ -13362,13 +13552,13 @@
     </row>
     <row r="31" spans="1:8" ht="56.25">
       <c r="A31" s="20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D31" s="23" t="s">
         <v>162</v>
@@ -13384,13 +13574,13 @@
     </row>
     <row r="32" spans="1:8" ht="37.5">
       <c r="A32" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B32" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="C32" s="20" t="s">
         <v>208</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>209</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="23" t="s">
@@ -13406,13 +13596,13 @@
     </row>
     <row r="33" spans="1:8" ht="37.5">
       <c r="A33" s="20" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>162</v>
@@ -13430,13 +13620,13 @@
     </row>
     <row r="34" spans="1:8" ht="37.5">
       <c r="A34" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="B34" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="B34" s="20" t="s">
-        <v>212</v>
-      </c>
       <c r="C34" s="36" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D34" s="23" t="s">
         <v>162</v>
@@ -13452,13 +13642,13 @@
     </row>
     <row r="35" spans="1:8" ht="56.25">
       <c r="A35" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="B35" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="C35" s="20" t="s">
         <v>327</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>328</v>
       </c>
       <c r="D35" s="23" t="s">
         <v>162</v>
@@ -13474,13 +13664,13 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="B36" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="B36" s="20" t="s">
-        <v>215</v>
-      </c>
       <c r="C36" s="20" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="D36" s="23" t="s">
         <v>162</v>
@@ -13498,13 +13688,13 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="20" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D37" s="23" t="s">
         <v>162</v>
@@ -13520,13 +13710,13 @@
     </row>
     <row r="38" spans="1:8" ht="37.5">
       <c r="A38" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B38" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="B38" s="20" t="s">
-        <v>217</v>
-      </c>
       <c r="C38" s="20" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="D38" s="23" t="s">
         <v>162</v>
@@ -13542,13 +13732,13 @@
     </row>
     <row r="39" spans="1:8" ht="37.5">
       <c r="A39" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="C39" s="20" t="s">
         <v>220</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>221</v>
       </c>
       <c r="D39" s="23"/>
       <c r="E39" s="23" t="s">
@@ -13564,13 +13754,13 @@
     </row>
     <row r="40" spans="1:8" ht="37.5">
       <c r="A40" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="C40" s="20" t="s">
         <v>218</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>219</v>
       </c>
       <c r="D40" s="23" t="s">
         <v>162</v>
@@ -13586,13 +13776,13 @@
     </row>
     <row r="41" spans="1:8" ht="93.75">
       <c r="A41" s="20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B41" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="C41" s="20" t="s">
         <v>322</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>323</v>
       </c>
       <c r="D41" s="23" t="s">
         <v>162</v>
@@ -13608,13 +13798,13 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="B42" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="B42" s="20" t="s">
-        <v>223</v>
-      </c>
       <c r="C42" s="36" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D42" s="23" t="s">
         <v>162</v>
@@ -13630,13 +13820,13 @@
     </row>
     <row r="43" spans="1:8" ht="37.5">
       <c r="A43" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="C43" s="20" t="s">
         <v>240</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>419</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>241</v>
       </c>
       <c r="D43" s="23" t="s">
         <v>162</v>
@@ -13652,13 +13842,13 @@
     </row>
     <row r="44" spans="1:8" ht="37.5">
       <c r="A44" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="C44" s="37" t="s">
         <v>227</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>419</v>
-      </c>
-      <c r="C44" s="45" t="s">
-        <v>228</v>
       </c>
       <c r="D44" s="23" t="s">
         <v>162</v>
@@ -13674,10 +13864,10 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="23" t="s">
@@ -13694,13 +13884,13 @@
     </row>
     <row r="46" spans="1:8" ht="56.25">
       <c r="A46" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B46" s="20" t="s">
         <v>418</v>
       </c>
-      <c r="B46" s="20" t="s">
-        <v>420</v>
-      </c>
       <c r="C46" s="20" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D46" s="23" t="s">
         <v>162</v>
@@ -13716,13 +13906,13 @@
     </row>
     <row r="47" spans="1:8" ht="37.5">
       <c r="A47" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B47" s="20" t="s">
         <v>178</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D47" s="23" t="s">
         <v>162</v>
@@ -13738,13 +13928,13 @@
     </row>
     <row r="48" spans="1:8" ht="37.5">
       <c r="A48" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="C48" s="20" t="s">
         <v>413</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>414</v>
-      </c>
-      <c r="C48" s="20" t="s">
-        <v>415</v>
       </c>
       <c r="D48" s="23" t="s">
         <v>162</v>
@@ -13760,13 +13950,13 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>467</v>
+      </c>
+      <c r="C49" s="20" t="s">
         <v>238</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>474</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>239</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>162</v>
@@ -13782,13 +13972,13 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B50" s="20" t="s">
         <v>183</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>162</v>
@@ -13806,13 +13996,13 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="B51" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="B51" s="20" t="s">
-        <v>232</v>
-      </c>
       <c r="C51" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D51" s="23" t="s">
         <v>162</v>
@@ -13829,14 +14019,14 @@
       <c r="H51" s="23"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="47" t="s">
-        <v>447</v>
+      <c r="A52" s="20" t="s">
+        <v>444</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>162</v>
@@ -13852,13 +14042,13 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="B53" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="B53" s="20" t="s">
+      <c r="C53" s="20" t="s">
         <v>234</v>
-      </c>
-      <c r="C53" s="20" t="s">
-        <v>235</v>
       </c>
       <c r="D53" s="23" t="s">
         <v>162</v>
@@ -13874,10 +14064,10 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="20" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C54" s="20"/>
       <c r="D54" s="23" t="s">
@@ -13894,13 +14084,13 @@
     </row>
     <row r="55" spans="1:8" ht="93.75">
       <c r="A55" s="20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D55" s="23" t="s">
         <v>162</v>
@@ -13918,13 +14108,13 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D56" s="23" t="s">
         <v>162</v>
@@ -13968,7 +14158,7 @@
     <sortCondition descending="1" ref="G5:G60"/>
     <sortCondition ref="F5:F60"/>
   </sortState>
-  <phoneticPr fontId="14"/>
+  <phoneticPr fontId="15"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="88" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -13994,7 +14184,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30">
       <c r="A1" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -14004,10 +14194,10 @@
     </row>
     <row r="4" spans="1:4" ht="19.5" thickBot="1">
       <c r="A4" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>50</v>
@@ -14018,10 +14208,10 @@
     </row>
     <row r="5" spans="1:4" ht="19.5" thickTop="1">
       <c r="A5" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>244</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>245</v>
       </c>
       <c r="C5" s="21">
         <v>0.7</v>
@@ -14032,10 +14222,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="B6" s="20" t="s">
         <v>246</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>247</v>
       </c>
       <c r="C6" s="21">
         <v>0.7</v>
@@ -14046,10 +14236,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="B7" s="20" t="s">
         <v>248</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>249</v>
       </c>
       <c r="C7" s="24">
         <v>0.9</v>
@@ -14060,10 +14250,10 @@
     </row>
     <row r="8" spans="1:4" ht="37.5">
       <c r="A8" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" s="20" t="s">
         <v>250</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>251</v>
       </c>
       <c r="C8" s="21">
         <v>0.8</v>
@@ -14074,10 +14264,10 @@
     </row>
     <row r="9" spans="1:4" ht="56.25">
       <c r="A9" s="20" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C9" s="21">
         <v>0.4</v>
@@ -14088,10 +14278,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>253</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>254</v>
       </c>
       <c r="C10" s="21">
         <v>0.2</v>
@@ -14102,10 +14292,10 @@
     </row>
     <row r="11" spans="1:4" ht="37.5">
       <c r="A11" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="B11" s="20" t="s">
         <v>255</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>256</v>
       </c>
       <c r="C11" s="21">
         <v>0.1</v>
@@ -14116,10 +14306,10 @@
     </row>
     <row r="12" spans="1:4" ht="56.25">
       <c r="A12" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C12" s="21">
         <v>0.8</v>
@@ -14130,10 +14320,10 @@
     </row>
     <row r="13" spans="1:4" ht="56.25">
       <c r="A13" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="B13" s="20" t="s">
         <v>258</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>259</v>
       </c>
       <c r="C13" s="24">
         <v>0.8</v>
@@ -14144,10 +14334,10 @@
     </row>
     <row r="14" spans="1:4" ht="56.25">
       <c r="A14" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C14" s="24">
         <v>0.8</v>
@@ -14158,10 +14348,10 @@
     </row>
     <row r="15" spans="1:4" ht="37.5">
       <c r="A15" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="B15" s="20" t="s">
         <v>261</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>262</v>
       </c>
       <c r="C15" s="24">
         <v>0.3</v>
@@ -14172,10 +14362,10 @@
     </row>
     <row r="16" spans="1:4" ht="75">
       <c r="A16" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="B16" s="20" t="s">
         <v>263</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>264</v>
       </c>
       <c r="C16" s="24">
         <v>0.95</v>
@@ -14184,10 +14374,10 @@
     </row>
     <row r="17" spans="1:4" ht="37.5">
       <c r="A17" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="B17" s="20" t="s">
         <v>265</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>266</v>
       </c>
       <c r="C17" s="24">
         <v>0.95</v>
@@ -14196,10 +14386,10 @@
     </row>
     <row r="18" spans="1:4" ht="37.5">
       <c r="A18" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="B18" s="20" t="s">
         <v>267</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>268</v>
       </c>
       <c r="C18" s="24">
         <v>0.8</v>
@@ -14208,10 +14398,10 @@
     </row>
     <row r="19" spans="1:4" ht="56.25">
       <c r="A19" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="B19" s="20" t="s">
         <v>269</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>270</v>
       </c>
       <c r="C19" s="24">
         <v>0.6</v>
@@ -14220,7 +14410,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="24">
@@ -14230,7 +14420,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="24">
@@ -14240,10 +14430,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="20" t="s">
+        <v>272</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>273</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>274</v>
       </c>
       <c r="C22" s="24">
         <v>0.5</v>
@@ -14252,10 +14442,10 @@
     </row>
     <row r="23" spans="1:4" ht="37.5">
       <c r="A23" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C23" s="24">
         <v>0.3</v>
@@ -14264,10 +14454,10 @@
     </row>
     <row r="24" spans="1:4" ht="37.5">
       <c r="A24" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="B24" s="20" t="s">
         <v>276</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>277</v>
       </c>
       <c r="C24" s="24">
         <v>0.3</v>
@@ -14276,10 +14466,10 @@
     </row>
     <row r="25" spans="1:4" ht="75">
       <c r="A25" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C25" s="24">
         <v>0.3</v>
@@ -14288,10 +14478,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="B26" s="20" t="s">
         <v>279</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>280</v>
       </c>
       <c r="C26" s="24">
         <v>0.1</v>
@@ -14326,7 +14516,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:D4" xr:uid="{BA60F202-06F6-4430-911F-CE81B59CEF26}"/>
-  <phoneticPr fontId="14"/>
+  <phoneticPr fontId="15"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -14359,7 +14549,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="28" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -14367,16 +14557,16 @@
     </row>
     <row r="4" spans="1:6" ht="19.5" thickBot="1">
       <c r="A4" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>88</v>
@@ -14387,16 +14577,16 @@
     </row>
     <row r="5" spans="1:6" ht="94.5" thickTop="1">
       <c r="A5" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>283</v>
-      </c>
       <c r="D5" s="16" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E5" s="21"/>
       <c r="F5" s="21">
@@ -14405,19 +14595,19 @@
     </row>
     <row r="6" spans="1:6" ht="93.75">
       <c r="A6" s="23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F6" s="24">
         <v>0.7</v>
@@ -14425,16 +14615,16 @@
     </row>
     <row r="7" spans="1:6" ht="112.5">
       <c r="A7" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>286</v>
-      </c>
       <c r="D7" s="23" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="24">
@@ -14443,19 +14633,19 @@
     </row>
     <row r="8" spans="1:6" ht="56.25">
       <c r="A8" s="23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F8" s="24">
         <v>0.05</v>
@@ -14463,19 +14653,19 @@
     </row>
     <row r="9" spans="1:6" ht="112.5">
       <c r="A9" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>427</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>289</v>
-      </c>
       <c r="D9" s="23" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F9" s="24">
         <v>0.05</v>
@@ -14483,16 +14673,16 @@
     </row>
     <row r="10" spans="1:6" ht="56.25">
       <c r="A10" s="23" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E10" s="24"/>
       <c r="F10" s="24">
@@ -14501,19 +14691,19 @@
     </row>
     <row r="11" spans="1:6" ht="75">
       <c r="A11" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>422</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="E11" s="24" t="s">
         <v>410</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>424</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>428</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>423</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>412</v>
       </c>
       <c r="F11" s="24">
         <v>0.05</v>
@@ -14545,7 +14735,7 @@
       <sortCondition descending="1" ref="F4"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="13"/>
+  <phoneticPr fontId="14"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -14574,12 +14764,12 @@
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="25" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="2:3">
@@ -14587,32 +14777,32 @@
         <v>1</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="C8" s="32" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" spans="2:3">
-      <c r="C9" s="48" t="s">
-        <v>407</v>
+      <c r="C9" s="38" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" s="32" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="2:3">
-      <c r="C11" s="48" t="s">
-        <v>476</v>
+      <c r="C11" s="38" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="12" spans="2:3">
@@ -14623,12 +14813,12 @@
         <v>2</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="2:3">
@@ -14636,17 +14826,17 @@
         <v>3</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="C18" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="C19" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="2:3">
@@ -14654,12 +14844,12 @@
         <v>4</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="C22" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="24" spans="2:3">
@@ -14667,12 +14857,12 @@
         <v>5</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="C25" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="26" spans="2:3">
@@ -14683,17 +14873,17 @@
         <v>6</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="28" spans="2:3">
       <c r="C28" s="26" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="C29" s="26" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="31" spans="2:3">
@@ -14701,17 +14891,17 @@
         <v>7</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="32" spans="2:3">
       <c r="C32" s="26" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="33" spans="2:12">
       <c r="C33" s="26" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -14722,12 +14912,12 @@
         <v>8</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="36" spans="2:12">
       <c r="C36" s="29" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="38" spans="2:12">
@@ -14735,30 +14925,30 @@
         <v>9</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="2:12">
       <c r="C39" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="2:12">
       <c r="C40" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="2:12">
       <c r="K41" s="35" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="L41" s="34">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46105</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13"/>
+  <phoneticPr fontId="14"/>
   <hyperlinks>
     <hyperlink ref="C36" r:id="rId1" xr:uid="{02BDDA31-576A-4688-8EFA-472077AEE200}"/>
   </hyperlinks>

--- a/99_Others/Supplement.xlsx
+++ b/99_Others/Supplement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\portfolio\99_Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF72773-8BBD-4C02-A808-208BA11E0ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD2E7EA-6D96-4F3F-BB36-7B6721E0F39C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">工程別!$A$4:$E$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">資格別!$A$4:$G$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Windows機能別!$A$1:$D$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">ツール別!$A$1:$H$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">ツール別!$A$1:$H$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">画面証跡!$A$1:$N$186</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">教材別!$A$1:$F$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">業務別!$A$1:$F$11</definedName>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="499">
   <si>
     <t>説明</t>
     <rPh sb="0" eb="2">
@@ -2246,16 +2246,6 @@
     <phoneticPr fontId="15"/>
   </si>
   <si>
-    <t>サードパーティ製アプリ名</t>
-    <rPh sb="7" eb="8">
-      <t>セイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
     <t>区分</t>
     <rPh sb="0" eb="2">
       <t>クブン</t>
@@ -2320,61 +2310,10 @@
     <phoneticPr fontId="15"/>
   </si>
   <si>
-    <t>DB</t>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
     <t>WinMerge</t>
   </si>
   <si>
     <t>Diff</t>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>開発案件別のソースコードに差分を移植する作業を行っていた経験があるため、
-フォルダ比較や自動バックアップ、同期ポイントを意識した使い方ができます。</t>
-    <rPh sb="0" eb="2">
-      <t>カイハツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>アンケン</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>サブン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>イショク</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>サギョウ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ヒカク</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>ドウキ</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>イシキ</t>
-    </rPh>
-    <rPh sb="64" eb="65">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="66" eb="67">
-      <t>カタ</t>
-    </rPh>
     <phoneticPr fontId="15"/>
   </si>
   <si>
@@ -2404,76 +2343,6 @@
     <phoneticPr fontId="15"/>
   </si>
   <si>
-    <t>システムの本番リリース直後の約１か月、夜間監視のため使用していた経験があります。障害発生を検知してエスカレーションする立ち位置ではありましたが、万が一に備え自力でのジョブ停止やスキップなどの操作を学んだうえでの監視業務を担当していました。</t>
-    <rPh sb="5" eb="7">
-      <t>ホンバン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>チョクゴ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ヤク</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ゲツ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ヤカン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>カンシ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>ショウガイ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ケンチ</t>
-    </rPh>
-    <rPh sb="59" eb="63">
-      <t>タチイチ</t>
-    </rPh>
-    <rPh sb="72" eb="73">
-      <t>マン</t>
-    </rPh>
-    <rPh sb="74" eb="75">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="76" eb="77">
-      <t>ソナ</t>
-    </rPh>
-    <rPh sb="78" eb="80">
-      <t>ジリキ</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>テイシ</t>
-    </rPh>
-    <rPh sb="95" eb="97">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="98" eb="99">
-      <t>マナ</t>
-    </rPh>
-    <rPh sb="105" eb="107">
-      <t>カンシ</t>
-    </rPh>
-    <rPh sb="107" eb="109">
-      <t>ギョウム</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>タントウ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
     <t>Jira Service Desk</t>
     <phoneticPr fontId="15"/>
   </si>
@@ -2493,55 +2362,6 @@
     <phoneticPr fontId="15"/>
   </si>
   <si>
-    <t>システム障害の調査の時など事象再現できない場合、画面共有などでエスカレーションするなどした経験があります。また通信障害などに備えスマホなどでも参加できるように準備をしておくなど工夫していました。</t>
-    <rPh sb="4" eb="6">
-      <t>ショウガイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>チョウサ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ジショウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>サイゲン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>キョウユウ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>ツウシン</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>ショウガイ</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>ソナ</t>
-    </rPh>
-    <rPh sb="71" eb="73">
-      <t>サンカ</t>
-    </rPh>
-    <rPh sb="79" eb="81">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="88" eb="90">
-      <t>クフウ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
     <t>Source Tree</t>
     <phoneticPr fontId="15"/>
   </si>
@@ -2606,29 +2426,6 @@
     <phoneticPr fontId="15"/>
   </si>
   <si>
-    <t>スケジュールの設定やメールサーバの接続ができます。
-検索フォルダなどではシステムエラーの識別子を設定するなどの工夫をしていました。</t>
-    <rPh sb="7" eb="9">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>セツゾク</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="44" eb="47">
-      <t>シキベツシ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>クフウ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
     <t>WinShot</t>
     <phoneticPr fontId="15"/>
   </si>
@@ -2665,56 +2462,10 @@
     <phoneticPr fontId="15"/>
   </si>
   <si>
-    <t>thunderbird固有の技術ではないですが、怪しいメールのマクロを実行しない作法を心得ており、万が一のウイルス感染時のLAN抜き、報告対応ができます。</t>
-    <rPh sb="11" eb="13">
-      <t>コユウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ギジュツ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>アヤ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>サホウ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ココロエ</t>
-    </rPh>
-    <rPh sb="49" eb="50">
-      <t>マン</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>カンセン</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="64" eb="65">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>ホウコク</t>
-    </rPh>
-    <rPh sb="69" eb="71">
-      <t>タイオウ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
     <t>Oracle SQL Developer</t>
     <phoneticPr fontId="15"/>
   </si>
   <si>
-    <t>MySQL Workbench</t>
-  </si>
-  <si>
     <t>H2</t>
   </si>
   <si>
@@ -2723,25 +2474,6 @@
   </si>
   <si>
     <t>FTP</t>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>Mac端末を使用していた時期があるため、レンタルサーバへのHTML、JSなどを用いたポートフォリオのアップロード経験があります。</t>
-    <rPh sb="3" eb="5">
-      <t>タンマツ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ジキ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>モチ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ケイケン</t>
-    </rPh>
     <phoneticPr fontId="15"/>
   </si>
   <si>
@@ -2825,16 +2557,6 @@
   </si>
   <si>
     <t>Redmine</t>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>チケットの作成経験あり</t>
-    <rPh sb="5" eb="7">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ケイケン</t>
-    </rPh>
     <phoneticPr fontId="15"/>
   </si>
   <si>
@@ -2966,34 +2688,6 @@
   </si>
   <si>
     <t>IP Messenger</t>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>ネットワーク使用不可の現場の経験があるため、メッセージの送信やログの設定など基本的な使用ができます。</t>
-    <rPh sb="6" eb="8">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>フカ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ゲンバ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ソウシン</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="38" eb="41">
-      <t>キホンテキ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>シヨウ</t>
-    </rPh>
     <phoneticPr fontId="15"/>
   </si>
   <si>
@@ -4587,79 +4281,6 @@
     <phoneticPr fontId="15"/>
   </si>
   <si>
-    <t>営業日、非営業日などを想定した運用試験で使用していたため、ジョブグループの概念を理解しており、即時実行や保留などの操作などの経験があります。接続時に別試験環境に接続しないように留意しておりました。</t>
-    <rPh sb="0" eb="2">
-      <t>エイギョウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ビ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>エイギョウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ビ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ソウテイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ウンヨウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>シケン</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ガイネン</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>リカイ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>ソクジ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ホリュウ</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>セツゾク</t>
-    </rPh>
-    <rPh sb="72" eb="73">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="74" eb="75">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="75" eb="77">
-      <t>シケン</t>
-    </rPh>
-    <rPh sb="77" eb="79">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="80" eb="82">
-      <t>セツゾク</t>
-    </rPh>
-    <rPh sb="88" eb="90">
-      <t>リュウイ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
     <t>イメージ管理</t>
     <rPh sb="4" eb="6">
       <t>カンリ</t>
@@ -4747,63 +4368,6 @@
       <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>IEのプロセス終了40秒以内に他IEが起動された場合のシステム障害について調査経験あり。(Loosely-Coupled IE)
-また、証明書有効期間中に「信頼されていないサイトです」と表示される障害の調査経験あり。(398日ルール)
-ほか、信頼済みサイト設定など各設定値の資料化経験あり。</t>
-    <rPh sb="7" eb="9">
-      <t>シュウリョウ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>イナイ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ホカ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>キドウ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ショウガイ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>チョウサ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="68" eb="71">
-      <t>ショウメイショ</t>
-    </rPh>
-    <rPh sb="71" eb="73">
-      <t>ユウコウ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>キカン</t>
-    </rPh>
-    <rPh sb="75" eb="76">
-      <t>チュウ</t>
-    </rPh>
-    <rPh sb="93" eb="95">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="98" eb="100">
-      <t>ショウガイ</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>チョウサ</t>
-    </rPh>
-    <rPh sb="103" eb="105">
-      <t>ケイケンシンライズセッテイカクセッテイチシリョウカケイケン</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>DataCloningWizard（データクローニングウィザード）</t>
@@ -4845,68 +4409,6 @@
     <phoneticPr fontId="14"/>
   </si>
   <si>
-    <t>業務ではタブレット側からPCに送られるXMLデータの代わりのドライバとして使用していました。ただし、単発的な使い方に限り、負荷テスト経験などはありません。
-イベントIDとXMLデータを送信するツールとして利用し、ユーザー定義環境変数の設定なども行っていました。。</t>
-    <rPh sb="0" eb="2">
-      <t>ギョウム</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ガワ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>オク</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>タンパツ</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="56" eb="57">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>カギ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>フカ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="92" eb="94">
-      <t>ソウシン</t>
-    </rPh>
-    <rPh sb="102" eb="104">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>テイギ</t>
-    </rPh>
-    <rPh sb="112" eb="114">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="114" eb="116">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="117" eb="119">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="122" eb="123">
-      <t>オコナ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
     <t>過去３世代（次期・現行・旧環境）のシステムの設定値をドキュメント化し、現行の設定値と同じになるように次期業務システムの設定を行った経験があります。次期環境で非推奨(非サポート)となっていないかなど調査した経験があります。</t>
     <rPh sb="0" eb="2">
       <t>カコ</t>
@@ -5469,54 +4971,6 @@
     </rPh>
     <rPh sb="41" eb="43">
       <t>ゼンゴ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>マルウェア対策のためマクロ自動実行オフのまま閲覧する作法を心得ております。
-また、Excelファイルは「新規」や「読み取り専用」で開く作法を心得ております。
-ほか、8割ほどの操作はキーボード操作のみで完結でき、VLOOKなど関数が使用できます。</t>
-    <rPh sb="22" eb="24">
-      <t>エツラン</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>シンキ</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>センヨウ</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>サホウ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>ココロエ</t>
-    </rPh>
-    <rPh sb="83" eb="84">
-      <t>ワリ</t>
-    </rPh>
-    <rPh sb="87" eb="89">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="95" eb="97">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="100" eb="102">
-      <t>カンケツ</t>
-    </rPh>
-    <rPh sb="112" eb="114">
-      <t>カンスウ</t>
-    </rPh>
-    <rPh sb="115" eb="117">
-      <t>シヨウ</t>
     </rPh>
     <phoneticPr fontId="15"/>
   </si>
@@ -6778,125 +6232,6 @@
 総合テスト</t>
     <rPh sb="1" eb="3">
       <t>ソウゴウ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>・シートの値を引数とした正規表現の作成およびクリップボードへの格納処理
-・フォームコントロールを契機としたPDF出力や外部ブック保存、自動フィルタ実装</t>
-    <rPh sb="5" eb="6">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ヒキスウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>セイキ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ヒョウゲン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>カクノウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ケイキ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ガイブ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>・ネットワークドライブの取得、加工処理
-・JSONを設定ファイルとしたiniファイル情報取得処理実装
-・Get-AppxPackageを用いたストアアプリのバージョンチェック
-・サービス実行状態のチェック</t>
-    <rPh sb="12" eb="14">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カコウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="68" eb="69">
-      <t>モチ</t>
-    </rPh>
-    <rPh sb="93" eb="95">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="95" eb="97">
-      <t>ジョウタイ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>DBの接続からクエリーの使用経験があります。試験で使用するテーブルやレコードの作成などの経験があります。(5テーブル以上)
-また、ヒューマンミスに備え、CTASによるバックアップなど心がけておりました。</t>
-    <rPh sb="3" eb="5">
-      <t>セツゾク</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>シケン</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="73" eb="74">
-      <t>ソナ</t>
-    </rPh>
-    <rPh sb="91" eb="92">
-      <t>ココロ</t>
     </rPh>
     <phoneticPr fontId="15"/>
   </si>
@@ -8312,67 +7647,6 @@
     <phoneticPr fontId="14"/>
   </si>
   <si>
-    <t>レコードの更新が他開発者のタスクに影響を与えることを理解しているので、
-テキストエディタに実行するSQLのシナリオを書いてから、実行する作法を身に着けております。
-例)Savepoint→Select→Delete→(RollBack)
-※環境構築や効率化設定の経験なし</t>
-    <rPh sb="5" eb="7">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ホカ</t>
-    </rPh>
-    <rPh sb="9" eb="12">
-      <t>カイハツシャ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>エイキョウ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>リカイ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="68" eb="70">
-      <t>サホウ</t>
-    </rPh>
-    <rPh sb="71" eb="72">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="73" eb="74">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="82" eb="83">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="120" eb="122">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="122" eb="124">
-      <t>コウチク</t>
-    </rPh>
-    <rPh sb="125" eb="128">
-      <t>コウリツカ</t>
-    </rPh>
-    <rPh sb="128" eb="130">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="131" eb="133">
-      <t>ケイケン</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
     <t>ant</t>
     <phoneticPr fontId="15"/>
   </si>
@@ -8635,40 +7909,6 @@
       <t>シカク</t>
     </rPh>
     <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>・WHEREコマンドによるファイル名の検索
-・RENコマンドやCOPYコマンドによるjpg証跡ファイルのリネーム
-・指定ディレクトリからのログのコピー
-・cls&amp;&amp;や/?や%date%%time%等を使用した画面証跡の取得</t>
-    <rPh sb="17" eb="18">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ショウセキ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="98" eb="99">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="100" eb="102">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="104" eb="106">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="106" eb="108">
-      <t>ショウセキ</t>
-    </rPh>
-    <rPh sb="109" eb="111">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>stdio.h
@@ -8874,39 +8114,6 @@
     <phoneticPr fontId="15"/>
   </si>
   <si>
-    <t>・アプリログ時刻補正 秀丸マクロの作成経験
-・編集時の排他制御設定経験
-・保存時の自動バックアップ設定経験</t>
-    <rPh sb="23" eb="25">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ハイタ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>セイギョ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>セッテイ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
     <t>・除外拡張子などを考慮した関数の呼び出し元や環境変数等のGrep経験
 ・アウトラインを使用したソースコードの解析経験
 ・改行コード、文字コードを意識したファイルの保存</t>
@@ -8963,18 +8170,6 @@
     </rPh>
     <rPh sb="81" eb="83">
       <t>ホゾン</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>・Git add
-・Git status
-・Git commit(Amend)
-・Git push(Force)
-・featureブランチの作成
-・署名付きコミットの設定</t>
-    <rPh sb="69" eb="71">
-      <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="15"/>
   </si>
@@ -9196,8 +8391,475 @@
     <phoneticPr fontId="14"/>
   </si>
   <si>
+    <t>・ファイル名検索バッチの新規作成(約150ステップ)【ポートフォリオ掲載作品】
+・shell:startup使用不可環境でのスタートアップ代替バッチの作成(約20ステップ)
+・ドラッグ＆ドロップしたファイルのリネームバッチ（5ステップ）</t>
+    <rPh sb="54" eb="56">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ダイタイ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>ヤク</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・勤務表自動入力マクロ【ポートフォリオ掲載作品】
+・シートの値を引数とした正規表現の作成およびクリップボードへの格納処理
+・フォームコントロールを契機としたPDF出力や外部ブック保存、自動フィルタ実装</t>
+    <rPh sb="1" eb="3">
+      <t>キンム</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ケイサイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>サクヒン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>セイキ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>カクノウ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ケイキ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・端末ステータス確認スクリプト【モックアップのみ掲載】(約50×8ステップ)
+・開発資源タイムスタンプ確認スクリプト(約10ステップ)
+・Windows音量変更スクリプト(自宅用)</t>
+    <rPh sb="1" eb="3">
+      <t>タンマツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ケイサイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>シゲン</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>オンリョウ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="86" eb="89">
+      <t>ジタクヨウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・最終リクエストのログ抽出shの新規作成(約50ステップ)
+・クラスパス抽出shの新規作成(約50ステップ)
+・antビルド結果表示cshにビルド結果(エラー/警告/注意)表示処理の追加
+・curl送信試験用ドライバshの作成(約50ステップ)</t>
+    <rPh sb="62" eb="64">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ケイコク</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>チュウイ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="101" eb="104">
+      <t>シケンヨウ</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>https://ma.educo-j.or.jp/h/EID900059008/ngxv3stpqf</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>・試験で使用するテーブルやレコードの作成などの経験
+・CTAS構文によるテーブルのバックアップの経験</t>
+    <rPh sb="1" eb="3">
+      <t>シケン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>コウブン</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・Send Later（指定時刻メール送信機能）の使用経験</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>レコードの更新が他開発者のタスクに影響を与えることを理解しているので、
+テキストエディタに実行するSQLのシナリオを書いてから、実行する作法を身に着けております。
+例)Savepoint→Select→Delete→(RollBack)</t>
+    <rPh sb="5" eb="7">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>カイハツシャ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>サホウ</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="82" eb="83">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・営業、非営業日を考慮したジョブの即時実行、保留の経験(運用テスト)</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・JSON(XML)送信ツールとして単発的な使い方での使用経験あり
+・試験用スレッドグループの作成経験
+・試験用ユーザー定義環境変数の設定経験</t>
+    <rPh sb="10" eb="12">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>タンパツテキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="53" eb="56">
+      <t>シケンヨウ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・レンタルサーバへの接続経験
+・HTML、JSなどを用いたポートフォリオのアップロード経験</t>
+    <rPh sb="10" eb="12">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・フォルダ単位での環境資源の比較経験
+・同期ポイントの使用
+・保存時の自動バックアップ設定経験</t>
+    <rPh sb="5" eb="7">
+      <t>タンイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シゲン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ドウキ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・システムの本番リリース直後の約１か月、夜間監視の経験
+・ジョブ停止、スキップの経験</t>
+    <rPh sb="6" eb="8">
+      <t>ホンバン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>チョクゴ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ゲツ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヤカン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カンシ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>テイシ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・システム障害調査経験あり。(Loosely-Coupled IEや398日ルール等)
+・信頼済みサイト設定など各設定値の資料化経験あり。</t>
+    <rPh sb="5" eb="7">
+      <t>ショウガイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>トウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・SQLワークシートの使用
+・SQL履歴ビューの使用</t>
+    <rPh sb="18" eb="20">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>DB GUIツール</t>
+  </si>
+  <si>
+    <t>phpMyAdmin</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・環境構築の経験
+・GUI上でのDB作成経験</t>
+    <rPh sb="1" eb="3">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>MySQL Workbench</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・環境構築の経験</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・チケットの作成経験や小規模な仕様の変更管理等</t>
+    <rPh sb="6" eb="8">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ショウキボ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>トウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・featureブランチの作成
+・署名付きコミットの設定
+・Git add
+・Git status
+・Git commit(Amend)
+・Git push(Force)</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
     <t>・ログ監視専用ttlファイル作成(TeraTermマクロ)
-・踏み台サーバへの接続経験
+・踏み台サーバへの接続経験(SSHポートフォワード)
 ・ウィンドウの複製を利用した二窓以上での作業経験
 ・操作ログ出力設定の経験</t>
     <rPh sb="3" eb="5">
@@ -9221,155 +8883,252 @@
     <rPh sb="41" eb="43">
       <t>ケイケン</t>
     </rPh>
-    <rPh sb="51" eb="53">
+    <rPh sb="64" eb="66">
       <t>フクセイ</t>
     </rPh>
-    <rPh sb="54" eb="56">
+    <rPh sb="67" eb="69">
       <t>リヨウ</t>
     </rPh>
-    <rPh sb="58" eb="59">
+    <rPh sb="71" eb="72">
       <t>ニ</t>
     </rPh>
-    <rPh sb="59" eb="60">
+    <rPh sb="72" eb="73">
       <t>マド</t>
     </rPh>
-    <rPh sb="60" eb="62">
+    <rPh sb="73" eb="75">
       <t>イジョウ</t>
     </rPh>
-    <rPh sb="64" eb="66">
+    <rPh sb="77" eb="79">
       <t>サギョウ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>セッテイ</t>
     </rPh>
     <rPh sb="79" eb="81">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>・makeビルド結果表示シェルにビルド詳細表示処理の追加
-・find . -nameを使用したビルドログの特定
-・grep -B によるビルドログのエラー箇所以前の出力
-・sedコマンドを使用した標準出力の改行コード（LF/CRLF）の可視化
-・tail -n -fを使用したアプリケーションログの監視
-・headコマンドをパイプ併用した最新ログファイル出力
-・grep -rnコマンドを使用したログからの警告やエラーなどの文言抽出
-・curlコマンドを使用したhttpリクエスト/レスポンス処理の動作確認
-・reset&amp;&amp;を使用したクリア状態での証跡の取得
-・java起動シェルの環境変数等の解析経験</t>
+    <rPh sb="83" eb="85">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・アプリログ時刻補正 秀丸マクロの作成経験
+・ソース修正履歴記載用の定型文出力マクロの作成経験
+・編集時の排他制御設定経験
+・保存時の自動バックアップ設定経験</t>
+    <rPh sb="26" eb="28">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>テイケイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ハイタ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・検索フォルダを使用した開発アプリのエラーメッセージの抽出経験
+・会議の設定やグループスケジュールの使用経験</t>
+    <rPh sb="1" eb="3">
+      <t>ケンサク</t>
+    </rPh>
     <rPh sb="8" eb="10">
-      <t>ケッカ</t>
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>チュウシュツ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>時限ファイルの使用経験</t>
+    <rPh sb="0" eb="2">
+      <t>ジゲン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>サードパーティ製
+アプリ名</t>
+    <rPh sb="7" eb="8">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・複数人への送信の際、To、CCを明示的に記載して送信した経験
+・メッセージログの設定経験</t>
+    <rPh sb="1" eb="3">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>メイジテキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・画面共有を使用した制作物の説明経験</t>
+    <rPh sb="1" eb="3">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シヨウ</t>
     </rPh>
     <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>トクテイ</t>
-    </rPh>
-    <rPh sb="77" eb="79">
-      <t>カショ</t>
-    </rPh>
-    <rPh sb="79" eb="81">
-      <t>イゼン</t>
-    </rPh>
-    <rPh sb="82" eb="84">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="94" eb="96">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="98" eb="100">
-      <t>ヒョウジュン</t>
-    </rPh>
-    <rPh sb="100" eb="102">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="103" eb="105">
-      <t>カイギョウ</t>
-    </rPh>
-    <rPh sb="118" eb="121">
-      <t>カシカ</t>
-    </rPh>
-    <rPh sb="134" eb="136">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="165" eb="167">
-      <t>ヘイヨウ</t>
-    </rPh>
-    <rPh sb="169" eb="171">
-      <t>サイシン</t>
-    </rPh>
-    <rPh sb="177" eb="179">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="194" eb="196">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="203" eb="205">
-      <t>ケイコク</t>
-    </rPh>
-    <rPh sb="212" eb="214">
-      <t>モンゴン</t>
-    </rPh>
-    <rPh sb="214" eb="216">
-      <t>チュウシュツ</t>
-    </rPh>
-    <rPh sb="227" eb="229">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="246" eb="248">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="249" eb="251">
-      <t>ドウサ</t>
-    </rPh>
-    <rPh sb="251" eb="253">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="285" eb="287">
-      <t>キドウ</t>
-    </rPh>
-    <rPh sb="291" eb="293">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="293" eb="295">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="295" eb="296">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="297" eb="299">
-      <t>カイセキ</t>
-    </rPh>
-    <rPh sb="299" eb="301">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ブツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・マルウェア対策のためマクロ自動実行ブロックのまま閲覧する習慣あり
+・多人数で共有を考慮して「新規」や「読み取り専用」で開く習慣あり</t>
+    <rPh sb="29" eb="31">
+      <t>シュウカン</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>タニンズウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>コウリョ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>シュウカン</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>WebLogic</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>サーバ</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>・手順書を参考としたコマンドによる再起動経験</t>
+    <rPh sb="1" eb="4">
+      <t>テジュンショ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サンコウ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>サイキドウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
   </si>
 </sst>
 </file>
@@ -9698,7 +9457,7 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
@@ -9816,6 +9575,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10518,99 +10280,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>455544</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>16565</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>176494</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>165653</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="10" name="グループ化 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E3087EA-862E-D795-7587-1A8E53B38F99}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="4108174" y="13293587"/>
-          <a:ext cx="3158233" cy="629479"/>
-          <a:chOff x="5242891" y="14121848"/>
-          <a:chExt cx="6903017" cy="1375866"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="5" name="図 4">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDDFAFF3-3123-D6A7-31B6-AA106F39781A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5242891" y="14602239"/>
-            <a:ext cx="6868484" cy="895475"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="8" name="図 7">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B3D65C4-C712-C004-5BCF-5968E0D43C6A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5267740" y="14121848"/>
-            <a:ext cx="6878168" cy="486663"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
@@ -10638,7 +10307,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10658,6 +10327,50 @@
             </a:schemeClr>
           </a:solidFill>
         </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>332016</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>112378</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>151718</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>168728</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{037793DD-B1E4-EF18-4826-C9DDFCEA721E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4664530" y="13109921"/>
+          <a:ext cx="2562902" cy="1014293"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -10946,7 +10659,7 @@
     </row>
     <row r="3" spans="2:10">
       <c r="B3" s="30" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="2:10">
@@ -10956,7 +10669,7 @@
     </row>
     <row r="5" spans="2:10">
       <c r="B5" s="31" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="19.5" thickBot="1"/>
@@ -11120,7 +10833,7 @@
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="10" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
     </row>
     <row r="23" spans="2:2">
@@ -11151,38 +10864,38 @@
   <sheetData>
     <row r="2" spans="1:10" ht="24">
       <c r="A2" s="1" t="s">
-        <v>480</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="39" t="s">
-        <v>481</v>
+        <v>459</v>
       </c>
       <c r="J4" s="39" t="s">
-        <v>479</v>
+        <v>457</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="38" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="39" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="39" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="H30" s="39" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="39" t="s">
-        <v>482</v>
+        <v>460</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -11190,12 +10903,12 @@
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="39" t="s">
-        <v>483</v>
+        <v>461</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="39" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
       <c r="B109" s="25"/>
       <c r="C109" s="25"/>
@@ -11304,14 +11017,16 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="38.25" thickTop="1">
+    <row r="5" spans="1:7" ht="57" thickTop="1">
       <c r="A5" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="13"/>
+      <c r="C5" s="40" t="s">
+        <v>470</v>
+      </c>
       <c r="D5" s="15" t="s">
         <v>35</v>
       </c>
@@ -11327,10 +11042,10 @@
     </row>
     <row r="6" spans="1:7" ht="73.5" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>37</v>
@@ -11350,7 +11065,7 @@
     </row>
     <row r="7" spans="1:7" ht="43.5" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>40</v>
@@ -11402,9 +11117,10 @@
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" xr:uid="{27A4E6AC-D535-4917-9A75-E6F6C321D2F1}"/>
     <hyperlink ref="C7" r:id="rId2" xr:uid="{30F668CC-9B59-46FD-807B-98AF09EED418}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{32A79625-C4AE-442D-8202-0214BE5E6252}"/>
   </hyperlinks>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="92" fitToHeight="0" orientation="landscape" r:id="rId3"/>
+  <pageSetup paperSize="9" scale="92" fitToHeight="0" orientation="landscape" r:id="rId4"/>
   <headerFooter>
     <oddFooter>&amp;P / &amp;N ページ</oddFooter>
   </headerFooter>
@@ -11444,7 +11160,7 @@
         <v>48</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>49</v>
@@ -11454,7 +11170,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="19.5" customHeight="1" thickTop="1">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="47" t="s">
         <v>51</v>
       </c>
       <c r="B5" s="16" t="s">
@@ -11471,7 +11187,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="44"/>
+      <c r="A6" s="45"/>
       <c r="B6" s="16" t="s">
         <v>55</v>
       </c>
@@ -11486,7 +11202,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="44"/>
+      <c r="A7" s="45"/>
       <c r="B7" s="16" t="s">
         <v>56</v>
       </c>
@@ -11501,7 +11217,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="44"/>
+      <c r="A8" s="45"/>
       <c r="B8" s="16" t="s">
         <v>58</v>
       </c>
@@ -11516,8 +11232,8 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="44"/>
-      <c r="B9" s="40" t="s">
+      <c r="A9" s="45"/>
+      <c r="B9" s="41" t="s">
         <v>60</v>
       </c>
       <c r="C9" s="16" t="s">
@@ -11531,90 +11247,90 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="56.25">
-      <c r="A10" s="44"/>
-      <c r="B10" s="41"/>
+      <c r="A10" s="45"/>
+      <c r="B10" s="42"/>
       <c r="C10" s="16" t="s">
         <v>63</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="E10" s="21">
         <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="44"/>
-      <c r="B11" s="42"/>
+      <c r="A11" s="45"/>
+      <c r="B11" s="43"/>
       <c r="C11" s="16" t="s">
         <v>64</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="E11" s="21">
         <v>0.2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="44"/>
-      <c r="B12" s="40" t="s">
+      <c r="A12" s="45"/>
+      <c r="B12" s="41" t="s">
         <v>65</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>66</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="E12" s="21">
         <v>0.9</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="44"/>
-      <c r="B13" s="42"/>
+      <c r="A13" s="45"/>
+      <c r="B13" s="43"/>
       <c r="C13" s="16" t="s">
         <v>67</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="E13" s="21">
         <v>0.9</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="112.5">
-      <c r="A14" s="44"/>
-      <c r="B14" s="43" t="s">
-        <v>390</v>
+      <c r="A14" s="45"/>
+      <c r="B14" s="44" t="s">
+        <v>375</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="E14" s="21">
         <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="56.25">
-      <c r="A15" s="44"/>
-      <c r="B15" s="44"/>
+      <c r="A15" s="45"/>
+      <c r="B15" s="45"/>
       <c r="C15" s="16" t="s">
         <v>69</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="E15" s="21">
         <v>0.8</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="57" customHeight="1">
-      <c r="A16" s="44"/>
-      <c r="B16" s="44"/>
+      <c r="A16" s="45"/>
+      <c r="B16" s="45"/>
       <c r="C16" s="16" t="s">
         <v>70</v>
       </c>
@@ -11626,33 +11342,33 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="168.75">
-      <c r="A17" s="44"/>
-      <c r="B17" s="44"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="45"/>
       <c r="C17" s="16" t="s">
         <v>72</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="E17" s="21">
         <v>0.9</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="57" customHeight="1">
-      <c r="A18" s="44"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="45"/>
+      <c r="B18" s="46"/>
       <c r="C18" s="16" t="s">
         <v>73</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="E18" s="21">
         <v>0.8</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="44"/>
+      <c r="A19" s="45"/>
       <c r="B19" s="22" t="s">
         <v>74</v>
       </c>
@@ -11667,7 +11383,7 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="44"/>
+      <c r="A20" s="45"/>
       <c r="B20" s="22" t="s">
         <v>76</v>
       </c>
@@ -11682,7 +11398,7 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="45"/>
+      <c r="A21" s="46"/>
       <c r="B21" s="22" t="s">
         <v>79</v>
       </c>
@@ -11781,7 +11497,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="27" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="B2" s="27"/>
     </row>
@@ -11804,7 +11520,7 @@
         <v>89</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>90</v>
@@ -11818,19 +11534,19 @@
     </row>
     <row r="5" spans="1:8" ht="225.75" thickTop="1">
       <c r="A5" s="23" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>92</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="F5" s="23">
         <v>2026</v>
@@ -11844,19 +11560,19 @@
     </row>
     <row r="6" spans="1:8" ht="206.25">
       <c r="A6" s="23" t="s">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>93</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>477</v>
+        <v>455</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="F6" s="23">
         <v>2026</v>
@@ -11870,19 +11586,19 @@
     </row>
     <row r="7" spans="1:8" ht="93.75">
       <c r="A7" s="23" t="s">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="B7" s="23" t="s">
         <v>107</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="F7" s="23" t="s">
         <v>77</v>
@@ -11892,9 +11608,9 @@
       </c>
       <c r="H7" s="23"/>
     </row>
-    <row r="8" spans="1:8" ht="75">
+    <row r="8" spans="1:8" ht="56.25">
       <c r="A8" s="16" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>98</v>
@@ -11903,7 +11619,7 @@
         <v>99</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="E8" s="16"/>
       <c r="F8" s="16">
@@ -11914,18 +11630,18 @@
       </c>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:8" ht="187.5">
+    <row r="9" spans="1:8" ht="75">
       <c r="A9" s="23" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>489</v>
+        <v>469</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="23" t="s">
@@ -11936,9 +11652,9 @@
       </c>
       <c r="H9" s="23"/>
     </row>
-    <row r="10" spans="1:8" ht="75">
+    <row r="10" spans="1:8" ht="56.25">
       <c r="A10" s="16" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>94</v>
@@ -11947,10 +11663,10 @@
         <v>95</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>392</v>
+        <v>468</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="F10" s="23">
         <v>2026</v>
@@ -11960,9 +11676,9 @@
       </c>
       <c r="H10" s="23"/>
     </row>
-    <row r="11" spans="1:8" ht="56.25">
+    <row r="11" spans="1:8" ht="75">
       <c r="A11" s="16" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>96</v>
@@ -11971,7 +11687,7 @@
         <v>97</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>391</v>
+        <v>467</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="23">
@@ -11984,7 +11700,7 @@
     </row>
     <row r="12" spans="1:8" ht="75">
       <c r="A12" s="23" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="B12" s="23" t="s">
         <v>101</v>
@@ -11996,7 +11712,7 @@
         <v>103</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F12" s="23">
         <v>2026</v>
@@ -12008,7 +11724,7 @@
     </row>
     <row r="13" spans="1:8" ht="131.25">
       <c r="A13" s="23" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="B13" s="23" t="s">
         <v>104</v>
@@ -12017,10 +11733,10 @@
         <v>105</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="F13" s="23">
         <v>2018</v>
@@ -12032,16 +11748,16 @@
     </row>
     <row r="14" spans="1:8" ht="75">
       <c r="A14" s="16" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>106</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="E14" s="23"/>
       <c r="F14" s="23">
@@ -12054,16 +11770,16 @@
     </row>
     <row r="15" spans="1:8" ht="37.5">
       <c r="A15" s="23" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23" t="s">
@@ -12076,19 +11792,19 @@
     </row>
     <row r="16" spans="1:8" ht="112.5">
       <c r="A16" s="23" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>100</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="F16" s="23">
         <v>2026</v>
@@ -12100,16 +11816,16 @@
     </row>
     <row r="17" spans="1:8" ht="56.25">
       <c r="A17" s="23" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="E17" s="23"/>
       <c r="F17" s="23" t="s">
@@ -12196,7 +11912,7 @@
         <v>110</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>111</v>
@@ -12216,7 +11932,7 @@
         <v>118</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16">
@@ -12250,7 +11966,7 @@
         <v>123</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>115</v>
@@ -12288,7 +12004,7 @@
         <v>117</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="23">
@@ -12322,7 +12038,7 @@
         <v>114</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>115</v>
@@ -12360,7 +12076,7 @@
         <v>128</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="D13" s="23" t="s">
         <v>129</v>
@@ -12380,7 +12096,7 @@
         <v>131</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>129</v>
@@ -12400,7 +12116,7 @@
         <v>121</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23">
@@ -12418,7 +12134,7 @@
         <v>125</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="23">
@@ -12436,7 +12152,7 @@
         <v>116</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="23">
@@ -12454,7 +12170,7 @@
         <v>130</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="23">
@@ -12469,10 +12185,10 @@
         <v>113</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>478</v>
+        <v>456</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="23">
@@ -12487,10 +12203,10 @@
         <v>113</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="23">
@@ -12505,10 +12221,10 @@
         <v>113</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="23">
@@ -12526,7 +12242,7 @@
         <v>141</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="23">
@@ -12576,7 +12292,7 @@
         <v>139</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>115</v>
@@ -12616,7 +12332,7 @@
         <v>138</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="D27" s="23" t="s">
         <v>115</v>
@@ -12674,7 +12390,7 @@
         <v>137</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="D30" s="23"/>
       <c r="E30" s="23">
@@ -12692,7 +12408,7 @@
         <v>140</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="D31" s="23" t="s">
         <v>129</v>
@@ -12730,7 +12446,7 @@
         <v>143</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>129</v>
@@ -12801,10 +12517,10 @@
         <v>151</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="D37" s="23"/>
       <c r="E37" s="23">
@@ -12854,7 +12570,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="20.875" style="2" customWidth="1"/>
@@ -12884,19 +12600,19 @@
     </row>
     <row r="4" spans="1:8" ht="54.75" thickBot="1">
       <c r="A4" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="C4" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="D4" s="12" t="s">
+      <c r="E4" s="12" t="s">
         <v>158</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>159</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>112</v>
@@ -12910,17 +12626,17 @@
     </row>
     <row r="5" spans="1:8" ht="113.25" thickTop="1">
       <c r="A5" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>161</v>
-      </c>
       <c r="C5" s="13" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F5" s="16">
         <v>2023</v>
@@ -12934,19 +12650,19 @@
     </row>
     <row r="6" spans="1:8" ht="131.25">
       <c r="A6" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B6" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="D6" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>162</v>
-      </c>
       <c r="E6" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F6" s="23">
         <v>2025</v>
@@ -12960,19 +12676,19 @@
     </row>
     <row r="7" spans="1:8" ht="131.25">
       <c r="A7" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>165</v>
-      </c>
       <c r="C7" s="20" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F7" s="23">
         <v>2026</v>
@@ -12984,18 +12700,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="93.75">
+    <row r="8" spans="1:8" ht="75">
       <c r="A8" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>167</v>
+        <v>481</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23">
@@ -13008,21 +12724,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="37.5">
+    <row r="9" spans="1:8" ht="56.25">
       <c r="A9" s="20" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>170</v>
+        <v>477</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F9" s="23">
         <v>2025</v>
@@ -13034,18 +12750,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="56.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="20" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>181</v>
+        <v>494</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="23">
@@ -13058,18 +12774,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="75">
+    <row r="11" spans="1:8" ht="56.25">
       <c r="A11" s="20" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>328</v>
+        <v>475</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="23">
@@ -13082,18 +12798,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="56.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="20" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>320</v>
+        <v>474</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="23">
@@ -13106,18 +12822,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="75">
+    <row r="13" spans="1:8" ht="37.5">
       <c r="A13" s="20" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>176</v>
+        <v>478</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="23">
@@ -13132,19 +12848,19 @@
     </row>
     <row r="14" spans="1:8" ht="37.5">
       <c r="A14" s="13" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F14" s="23">
         <v>2018</v>
@@ -13158,16 +12874,16 @@
     </row>
     <row r="15" spans="1:8" ht="56.25">
       <c r="A15" s="13" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23">
@@ -13182,16 +12898,16 @@
     </row>
     <row r="16" spans="1:8" ht="37.5">
       <c r="A16" s="13" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E16" s="23"/>
       <c r="F16" s="23">
@@ -13206,19 +12922,19 @@
     </row>
     <row r="17" spans="1:8" ht="112.5">
       <c r="A17" s="13" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F17" s="23">
         <v>2025</v>
@@ -13232,19 +12948,19 @@
     </row>
     <row r="18" spans="1:8" ht="56.25">
       <c r="A18" s="20" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F18" s="23">
         <v>2026</v>
@@ -13258,19 +12974,19 @@
     </row>
     <row r="19" spans="1:8" ht="75">
       <c r="A19" s="20" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>488</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F19" s="23">
         <v>2018</v>
@@ -13282,21 +12998,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="75">
+    <row r="20" spans="1:8" ht="37.5">
       <c r="A20" s="13" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>341</v>
+        <v>495</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F20" s="23">
         <v>2025</v>
@@ -13310,19 +13026,19 @@
     </row>
     <row r="21" spans="1:8" ht="37.5">
       <c r="A21" s="13" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>192</v>
+        <v>490</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F21" s="23">
         <v>2025</v>
@@ -13336,16 +13052,16 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="13" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E22" s="23"/>
       <c r="F22" s="23">
@@ -13360,19 +13076,19 @@
     </row>
     <row r="23" spans="1:8" ht="37.5">
       <c r="A23" s="13" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F23" s="23">
         <v>2025</v>
@@ -13386,19 +13102,19 @@
     </row>
     <row r="24" spans="1:8" ht="56.25">
       <c r="A24" s="20" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>475</v>
+        <v>454</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F24" s="23">
         <v>2025</v>
@@ -13410,21 +13126,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="56.25">
+    <row r="25" spans="1:8" ht="75">
       <c r="A25" s="20" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F25" s="23">
         <v>2025</v>
@@ -13438,19 +13154,19 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="20" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F26" s="23">
         <v>2025</v>
@@ -13462,21 +13178,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="37.5">
+    <row r="27" spans="1:8">
       <c r="A27" s="20" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>202</v>
+        <v>472</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F27" s="23">
         <v>2025</v>
@@ -13488,264 +13204,270 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="56.25">
+    <row r="28" spans="1:8" ht="37.5">
       <c r="A28" s="20" t="s">
-        <v>205</v>
+        <v>482</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>393</v>
+        <v>483</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E28" s="23"/>
+        <v>161</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>161</v>
+      </c>
       <c r="F28" s="23">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="G28" s="24">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H28" s="23"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" ht="37.5">
       <c r="A29" s="20" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>394</v>
-      </c>
-      <c r="C29" s="20"/>
+        <v>376</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>471</v>
+      </c>
       <c r="D29" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E29" s="23"/>
       <c r="F29" s="23">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="G29" s="24">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H29" s="23"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="20" t="s">
-        <v>203</v>
+        <v>484</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>394</v>
-      </c>
-      <c r="C30" s="20"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23" t="s">
-        <v>162</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>485</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E30" s="23"/>
       <c r="F30" s="23">
+        <v>2018</v>
+      </c>
+      <c r="G30" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="H30" s="23"/>
+    </row>
+    <row r="31" spans="1:8" ht="37.5">
+      <c r="A31" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>480</v>
+      </c>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" s="23">
         <v>2025</v>
       </c>
-      <c r="G30" s="24">
+      <c r="G31" s="24">
         <v>0.2</v>
       </c>
-      <c r="H30" s="23"/>
-    </row>
-    <row r="31" spans="1:8" ht="56.25">
-      <c r="A31" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>453</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23">
-        <v>2018</v>
-      </c>
-      <c r="G31" s="24">
-        <v>0.3</v>
-      </c>
       <c r="H31" s="23"/>
     </row>
-    <row r="32" spans="1:8" ht="37.5">
+    <row r="32" spans="1:8" ht="56.25">
       <c r="A32" s="20" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23" t="s">
-        <v>162</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E32" s="23"/>
       <c r="F32" s="23">
         <v>2018</v>
       </c>
       <c r="G32" s="24">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="H32" s="23"/>
     </row>
     <row r="33" spans="1:8" ht="37.5">
       <c r="A33" s="20" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>162</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="D33" s="23"/>
       <c r="E33" s="23" t="s">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="F33" s="23">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="G33" s="24">
-        <v>0.6</v>
+        <v>0.05</v>
       </c>
       <c r="H33" s="23"/>
     </row>
     <row r="34" spans="1:8" ht="37.5">
       <c r="A34" s="20" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>420</v>
+        <v>202</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>321</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E34" s="23"/>
+        <v>161</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>77</v>
+      </c>
       <c r="F34" s="23">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="G34" s="24">
-        <v>0.05</v>
+        <v>0.6</v>
       </c>
       <c r="H34" s="23"/>
     </row>
-    <row r="35" spans="1:8" ht="56.25">
+    <row r="35" spans="1:8" ht="37.5">
       <c r="A35" s="20" t="s">
-        <v>325</v>
+        <v>201</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>326</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>327</v>
+        <v>202</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>402</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E35" s="23"/>
       <c r="F35" s="23">
+        <v>2018</v>
+      </c>
+      <c r="G35" s="24">
+        <v>0.05</v>
+      </c>
+      <c r="H35" s="23"/>
+    </row>
+    <row r="36" spans="1:8" ht="56.25">
+      <c r="A36" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23">
         <v>2020</v>
       </c>
-      <c r="G35" s="24">
+      <c r="G36" s="24">
         <v>0.4</v>
-      </c>
-      <c r="H35" s="23"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>466</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="F36" s="23">
-        <v>2019</v>
-      </c>
-      <c r="G36" s="24">
-        <v>0.1</v>
       </c>
       <c r="H36" s="23"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="20" t="s">
-        <v>429</v>
+        <v>204</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>430</v>
+        <v>205</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E37" s="23"/>
+        <v>161</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>161</v>
+      </c>
       <c r="F37" s="23">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="G37" s="24">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H37" s="23"/>
     </row>
-    <row r="38" spans="1:8" ht="37.5">
+    <row r="38" spans="1:8">
       <c r="A38" s="20" t="s">
-        <v>215</v>
+        <v>411</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>216</v>
+        <v>412</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>468</v>
+        <v>446</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E38" s="23"/>
       <c r="F38" s="23">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="G38" s="24">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H38" s="23"/>
     </row>
     <row r="39" spans="1:8" ht="37.5">
       <c r="A39" s="20" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23" t="s">
-        <v>162</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E39" s="23"/>
       <c r="F39" s="23">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="G39" s="24">
         <v>0.1</v>
@@ -13754,409 +13476,455 @@
     </row>
     <row r="40" spans="1:8" ht="37.5">
       <c r="A40" s="20" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E40" s="23"/>
+        <v>211</v>
+      </c>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23" t="s">
+        <v>161</v>
+      </c>
       <c r="F40" s="23">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="G40" s="24">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H40" s="23"/>
     </row>
-    <row r="41" spans="1:8" ht="93.75">
+    <row r="41" spans="1:8" ht="37.5">
       <c r="A41" s="20" t="s">
-        <v>324</v>
+        <v>208</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>321</v>
+        <v>207</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>322</v>
+        <v>209</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E41" s="23"/>
       <c r="F41" s="23">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="G41" s="24">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="H41" s="23"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" ht="93.75">
       <c r="A42" s="20" t="s">
-        <v>221</v>
+        <v>311</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="C42" s="36" t="s">
-        <v>415</v>
+        <v>309</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>310</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E42" s="23"/>
       <c r="F42" s="23">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="G42" s="24">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="H42" s="23"/>
     </row>
-    <row r="43" spans="1:8" ht="37.5">
+    <row r="43" spans="1:8">
       <c r="A43" s="20" t="s">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>417</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>240</v>
+        <v>213</v>
+      </c>
+      <c r="C43" s="36" t="s">
+        <v>397</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E43" s="23"/>
       <c r="F43" s="23">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="G43" s="24">
-        <v>0.6</v>
+        <v>0.05</v>
       </c>
       <c r="H43" s="23"/>
     </row>
     <row r="44" spans="1:8" ht="37.5">
       <c r="A44" s="20" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>417</v>
-      </c>
-      <c r="C44" s="37" t="s">
-        <v>227</v>
+        <v>399</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>493</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E44" s="23"/>
       <c r="F44" s="23">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="G44" s="24">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="H44" s="23"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" ht="37.5">
       <c r="A45" s="20" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>417</v>
-      </c>
-      <c r="C45" s="20"/>
+        <v>399</v>
+      </c>
+      <c r="C45" s="37" t="s">
+        <v>217</v>
+      </c>
       <c r="D45" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E45" s="23"/>
       <c r="F45" s="23">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="G45" s="24">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H45" s="23"/>
     </row>
-    <row r="46" spans="1:8" ht="56.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="20" t="s">
-        <v>416</v>
+        <v>215</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>418</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>428</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="C46" s="20"/>
       <c r="D46" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E46" s="23"/>
       <c r="F46" s="23">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="G46" s="24">
         <v>0.05</v>
       </c>
       <c r="H46" s="23"/>
     </row>
-    <row r="47" spans="1:8" ht="37.5">
+    <row r="47" spans="1:8" ht="56.25">
       <c r="A47" s="20" t="s">
-        <v>223</v>
+        <v>398</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>178</v>
+        <v>400</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>224</v>
+        <v>410</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E47" s="23"/>
       <c r="F47" s="23">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="G47" s="24">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H47" s="23"/>
     </row>
     <row r="48" spans="1:8" ht="37.5">
       <c r="A48" s="20" t="s">
-        <v>411</v>
+        <v>214</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>412</v>
+        <v>174</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>413</v>
+        <v>486</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E48" s="23"/>
       <c r="F48" s="23">
-        <v>2026</v>
+        <v>2018</v>
       </c>
       <c r="G48" s="24">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H48" s="23"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" ht="37.5">
       <c r="A49" s="20" t="s">
-        <v>237</v>
+        <v>393</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>467</v>
+        <v>394</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>238</v>
+        <v>395</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E49" s="23"/>
       <c r="F49" s="23">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="G49" s="24">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H49" s="23"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="C50" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="B50" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>229</v>
-      </c>
       <c r="D50" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>162</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="E50" s="23"/>
       <c r="F50" s="23">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="G50" s="24">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H50" s="23"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="20" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>231</v>
+        <v>178</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>342</v>
+        <v>219</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F51" s="23">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="G51" s="24">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="H51" s="23"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="20" t="s">
-        <v>444</v>
+        <v>220</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>445</v>
+        <v>221</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>464</v>
+        <v>327</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E52" s="23"/>
+        <v>161</v>
+      </c>
+      <c r="E52" s="23" t="s">
+        <v>161</v>
+      </c>
       <c r="F52" s="23">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G52" s="24">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="H52" s="23"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="20" t="s">
-        <v>232</v>
+        <v>425</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>233</v>
+        <v>426</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>234</v>
+        <v>445</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E53" s="23"/>
       <c r="F53" s="23">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="G53" s="24">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="23"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="20" t="s">
-        <v>419</v>
+        <v>222</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="C54" s="20"/>
+        <v>223</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>224</v>
+      </c>
       <c r="D54" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E54" s="23"/>
       <c r="F54" s="23">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="G54" s="24">
         <v>0.05</v>
       </c>
       <c r="H54" s="23"/>
     </row>
-    <row r="55" spans="1:8" ht="93.75">
+    <row r="55" spans="1:8">
       <c r="A55" s="20" t="s">
-        <v>236</v>
+        <v>401</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>323</v>
+        <v>491</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E55" s="23" t="s">
-        <v>162</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="E55" s="23"/>
       <c r="F55" s="23">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G55" s="24">
-        <v>0.95</v>
+        <v>0.05</v>
       </c>
       <c r="H55" s="23"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" ht="37.5">
       <c r="A56" s="20" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>314</v>
+        <v>479</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F56" s="23">
         <v>2025</v>
       </c>
       <c r="G56" s="24">
+        <v>0.95</v>
+      </c>
+      <c r="H56" s="23"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C57" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="D57" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E57" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="F57" s="23">
+        <v>2025</v>
+      </c>
+      <c r="G57" s="24">
         <v>0.5</v>
       </c>
-      <c r="H56" s="23"/>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="2" t="s">
-        <v>83</v>
-      </c>
+      <c r="H57" s="23"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="A58" s="20" t="s">
+        <v>496</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>497</v>
+      </c>
+      <c r="C58" s="20" t="s">
+        <v>498</v>
+      </c>
+      <c r="D58" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23">
+        <v>2018</v>
+      </c>
+      <c r="G58" s="24">
+        <v>0.05</v>
+      </c>
+      <c r="H58" s="23"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="2" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:H4" xr:uid="{21FFF12F-B684-4050-9B34-306B03FBB89B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:H60">
-    <sortCondition ref="H5:H60"/>
-    <sortCondition ref="B5:B60"/>
-    <sortCondition descending="1" ref="G5:G60"/>
-    <sortCondition ref="F5:F60"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:H62">
+    <sortCondition ref="H5:H62"/>
+    <sortCondition ref="B5:B62"/>
+    <sortCondition descending="1" ref="G5:G62"/>
+    <sortCondition ref="F5:F62"/>
   </sortState>
   <phoneticPr fontId="15"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
@@ -14184,7 +13952,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30">
       <c r="A1" s="11" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -14194,10 +13962,10 @@
     </row>
     <row r="4" spans="1:4" ht="19.5" thickBot="1">
       <c r="A4" s="12" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>50</v>
@@ -14208,10 +13976,10 @@
     </row>
     <row r="5" spans="1:4" ht="19.5" thickTop="1">
       <c r="A5" s="13" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C5" s="21">
         <v>0.7</v>
@@ -14222,10 +13990,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="20" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C6" s="21">
         <v>0.7</v>
@@ -14236,10 +14004,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="20" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C7" s="24">
         <v>0.9</v>
@@ -14250,10 +14018,10 @@
     </row>
     <row r="8" spans="1:4" ht="37.5">
       <c r="A8" s="20" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="C8" s="21">
         <v>0.8</v>
@@ -14264,10 +14032,10 @@
     </row>
     <row r="9" spans="1:4" ht="56.25">
       <c r="A9" s="20" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="C9" s="21">
         <v>0.4</v>
@@ -14278,10 +14046,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="20" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="C10" s="21">
         <v>0.2</v>
@@ -14292,10 +14060,10 @@
     </row>
     <row r="11" spans="1:4" ht="37.5">
       <c r="A11" s="20" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C11" s="21">
         <v>0.1</v>
@@ -14306,10 +14074,10 @@
     </row>
     <row r="12" spans="1:4" ht="56.25">
       <c r="A12" s="13" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C12" s="21">
         <v>0.8</v>
@@ -14320,10 +14088,10 @@
     </row>
     <row r="13" spans="1:4" ht="56.25">
       <c r="A13" s="20" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="C13" s="24">
         <v>0.8</v>
@@ -14334,10 +14102,10 @@
     </row>
     <row r="14" spans="1:4" ht="56.25">
       <c r="A14" s="20" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C14" s="24">
         <v>0.8</v>
@@ -14348,10 +14116,10 @@
     </row>
     <row r="15" spans="1:4" ht="37.5">
       <c r="A15" s="20" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="C15" s="24">
         <v>0.3</v>
@@ -14362,10 +14130,10 @@
     </row>
     <row r="16" spans="1:4" ht="75">
       <c r="A16" s="13" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="C16" s="24">
         <v>0.95</v>
@@ -14374,10 +14142,10 @@
     </row>
     <row r="17" spans="1:4" ht="37.5">
       <c r="A17" s="20" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C17" s="24">
         <v>0.95</v>
@@ -14386,10 +14154,10 @@
     </row>
     <row r="18" spans="1:4" ht="37.5">
       <c r="A18" s="20" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="C18" s="24">
         <v>0.8</v>
@@ -14398,10 +14166,10 @@
     </row>
     <row r="19" spans="1:4" ht="56.25">
       <c r="A19" s="20" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="C19" s="24">
         <v>0.6</v>
@@ -14410,7 +14178,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="20" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="24">
@@ -14420,7 +14188,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="20" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="24">
@@ -14430,10 +14198,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="20" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C22" s="24">
         <v>0.5</v>
@@ -14442,10 +14210,10 @@
     </row>
     <row r="23" spans="1:4" ht="37.5">
       <c r="A23" s="20" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C23" s="24">
         <v>0.3</v>
@@ -14454,10 +14222,10 @@
     </row>
     <row r="24" spans="1:4" ht="37.5">
       <c r="A24" s="20" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="C24" s="24">
         <v>0.3</v>
@@ -14466,10 +14234,10 @@
     </row>
     <row r="25" spans="1:4" ht="75">
       <c r="A25" s="20" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="C25" s="24">
         <v>0.3</v>
@@ -14478,10 +14246,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="20" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C26" s="24">
         <v>0.1</v>
@@ -14549,7 +14317,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="28" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -14557,16 +14325,16 @@
     </row>
     <row r="4" spans="1:6" ht="19.5" thickBot="1">
       <c r="A4" s="12" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>88</v>
@@ -14577,16 +14345,16 @@
     </row>
     <row r="5" spans="1:6" ht="94.5" thickTop="1">
       <c r="A5" s="16" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="E5" s="21"/>
       <c r="F5" s="21">
@@ -14595,19 +14363,19 @@
     </row>
     <row r="6" spans="1:6" ht="93.75">
       <c r="A6" s="23" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="F6" s="24">
         <v>0.7</v>
@@ -14615,16 +14383,16 @@
     </row>
     <row r="7" spans="1:6" ht="112.5">
       <c r="A7" s="23" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="24">
@@ -14633,19 +14401,19 @@
     </row>
     <row r="8" spans="1:6" ht="56.25">
       <c r="A8" s="23" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="F8" s="24">
         <v>0.05</v>
@@ -14653,19 +14421,19 @@
     </row>
     <row r="9" spans="1:6" ht="112.5">
       <c r="A9" s="23" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="F9" s="24">
         <v>0.05</v>
@@ -14673,16 +14441,16 @@
     </row>
     <row r="10" spans="1:6" ht="56.25">
       <c r="A10" s="23" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="E10" s="24"/>
       <c r="F10" s="24">
@@ -14691,19 +14459,19 @@
     </row>
     <row r="11" spans="1:6" ht="75">
       <c r="A11" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>408</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>422</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>426</v>
-      </c>
       <c r="D11" s="23" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="F11" s="24">
         <v>0.05</v>
@@ -14764,12 +14532,12 @@
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="25" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="2" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="2:3">
@@ -14777,32 +14545,32 @@
         <v>1</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" s="2" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="C8" s="32" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="C9" s="38" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" s="32" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" s="38" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" spans="2:3">
@@ -14813,12 +14581,12 @@
         <v>2</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" s="2" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="2:3">
@@ -14826,17 +14594,17 @@
         <v>3</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="C18" s="2" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="C19" s="2" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="2:3">
@@ -14844,12 +14612,12 @@
         <v>4</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="C22" s="2" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="2:3">
@@ -14857,12 +14625,12 @@
         <v>5</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="C25" s="2" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="2:3">
@@ -14873,17 +14641,17 @@
         <v>6</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="2:3">
       <c r="C28" s="26" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="C29" s="26" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="2:3">
@@ -14891,17 +14659,17 @@
         <v>7</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="2:3">
       <c r="C32" s="26" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="2:12">
       <c r="C33" s="26" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -14912,12 +14680,12 @@
         <v>8</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
     </row>
     <row r="36" spans="2:12">
       <c r="C36" s="29" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38" spans="2:12">
@@ -14925,26 +14693,26 @@
         <v>9</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="2:12">
       <c r="C39" s="2" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40" spans="2:12">
       <c r="C40" s="2" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
     </row>
     <row r="41" spans="2:12">
       <c r="K41" s="35" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="L41" s="34">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46126</v>
       </c>
     </row>
   </sheetData>

--- a/99_Others/Supplement.xlsx
+++ b/99_Others/Supplement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\portfolio\99_Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD2E7EA-6D96-4F3F-BB36-7B6721E0F39C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC4FA4B-AE6D-4855-8D3A-444BA7080C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,14 +33,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">工程別!$A$4:$E$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">資格別!$A$4:$G$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Windows機能別!$A$1:$D$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">ツール別!$A$1:$H$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">ツール別!$A$1:$H$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">画面証跡!$A$1:$N$186</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">教材別!$A$1:$F$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">教材別!$A$1:$F$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">業務別!$A$1:$F$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">言語別!$A$1:$H$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">言語別!$A$1:$H$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">工程別!$A$1:$E$27</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">仕事の進め方や考え方!$A$1:$O$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">資格別!$A$1:$G$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">仕事の進め方や考え方!$A$1:$O$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">資格別!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">目次!$A$1:$K$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">Windows機能別!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">ツール別!$1:$4</definedName>
@@ -71,13 +71,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="505">
   <si>
     <t>説明</t>
     <rPh sb="0" eb="2">
       <t>セツメイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <r>
@@ -118,14 +118,14 @@
     <rPh sb="33" eb="34">
       <t>サイワ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>目次</t>
     <rPh sb="0" eb="2">
       <t>モクジ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>資格別</t>
@@ -135,7 +135,7 @@
     <rPh sb="2" eb="3">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>客観的なスキル指標</t>
@@ -145,11 +145,11 @@
     <rPh sb="7" eb="9">
       <t>シヒョウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>工程別</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ウォーターフォールやアジャイルでの工程、役割での観点</t>
@@ -162,7 +162,7 @@
     <rPh sb="24" eb="26">
       <t>カンテン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>言語別</t>
@@ -172,7 +172,7 @@
     <rPh sb="2" eb="3">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>経験してきたプログラミング・マークアップ言語</t>
@@ -182,7 +182,7 @@
     <rPh sb="20" eb="22">
       <t>ゲンゴ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>教材別</t>
@@ -192,7 +192,7 @@
     <rPh sb="2" eb="3">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>業務時間外の勉強してきた本の内容</t>
@@ -214,14 +214,14 @@
     <rPh sb="14" eb="16">
       <t>ナイヨウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ツール別</t>
     <rPh sb="3" eb="4">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>業界標準のツール別の理解度やツールを通して経験した業務など</t>
@@ -246,7 +246,7 @@
     <rPh sb="25" eb="27">
       <t>ギョウム</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Windows機能別</t>
@@ -256,7 +256,7 @@
     <rPh sb="9" eb="10">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>実務で使用する頻度の高い機能の経験</t>
@@ -278,7 +278,7 @@
     <rPh sb="15" eb="17">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>業務別</t>
@@ -288,7 +288,7 @@
     <rPh sb="2" eb="3">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>システム開発の際、付随して必要になったIT以外の業務知識について</t>
@@ -313,7 +313,7 @@
     <rPh sb="26" eb="28">
       <t>チシキ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>仕事の進め方や考え方</t>
@@ -332,7 +332,7 @@
     <rPh sb="9" eb="10">
       <t>カタ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>個人の仕事の考え方などのご説明</t>
@@ -351,7 +351,7 @@
     <rPh sb="13" eb="15">
       <t>セツメイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>■面談前の留意点</t>
@@ -364,7 +364,7 @@
     <rPh sb="5" eb="8">
       <t>リュウイテン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>誤字脱字など十分注意したつもりではありますが、</t>
@@ -380,11 +380,11 @@
     <rPh sb="8" eb="10">
       <t>チュウイトクジュウヨウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>本書は頻繁に書き換えるため「理解度」列など、うっかり記載を間違えてしまう場合を懸念しております。</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>特に重要なスキルについては、よりミスマッチが発生しないように面談などで、</t>
@@ -394,11 +394,11 @@
     <rPh sb="30" eb="32">
       <t>メンダン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>事前にご確認していただければと思います。</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>観点別のスキル感や工夫した点、お作法などを記述します。メインはスキルシートやポートフォリオ成果物をご確認ください。</t>
@@ -429,7 +429,7 @@
     <rPh sb="50" eb="52">
       <t>カクニン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>※合格したものに限り記載し、受験中の資格は省きます。</t>
@@ -451,7 +451,7 @@
     <rPh sb="21" eb="22">
       <t>ハブ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>資格名</t>
@@ -461,15 +461,15 @@
     <rPh sb="2" eb="3">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>コメント</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>デジタルバッジ</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>合格点数</t>
@@ -479,7 +479,7 @@
     <rPh sb="3" eb="4">
       <t>スウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>受験回数</t>
@@ -489,7 +489,7 @@
     <rPh sb="2" eb="4">
       <t>カイスウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>学習期間</t>
@@ -499,7 +499,7 @@
     <rPh sb="2" eb="4">
       <t>キカン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>取得日付</t>
@@ -509,7 +509,7 @@
     <rPh sb="2" eb="4">
       <t>ヒヅケ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>HTML5プロフェッショナル認定試験 レベル1</t>
@@ -534,7 +534,7 @@
     <rPh sb="22" eb="23">
       <t>フカ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>約70点</t>
@@ -544,32 +544,32 @@
     <rPh sb="3" eb="4">
       <t>テン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>1か月</t>
     <rPh sb="2" eb="3">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>https://catalog-education.oracle.com/pls/certview/sharebadge?id=1B95E9A663D35A568BF9D4E2A771FE0D11ABCC4B3C5B1CA8B5BDFF58028CC4FE</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>約60点</t>
     <rPh sb="0" eb="1">
       <t>ヤク</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>1年</t>
     <rPh sb="1" eb="2">
       <t>ネン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>カプセル化や例外処理、継承、ポリモーフィズムなど基本的な文法などを学びました。</t>
@@ -594,18 +594,18 @@
     <rPh sb="33" eb="34">
       <t>マナ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>https://catalog-education.oracle.com/pls/certview/sharebadge?id=53530D71C1F9D80C808FB90F92AA21C7099A92F2E5180E51AD2F324C39097648</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>約90点</t>
     <rPh sb="0" eb="1">
       <t>ヤク</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>タイピング技能検定 イータイピング・マスター 1級</t>
@@ -618,7 +618,7 @@
     <rPh sb="24" eb="25">
       <t>キュウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>使用頻度の高い単語と苦手な単語を専門的に練習した経験あり。標準運指を崩し最適化適用済。実務では緩急や静音を意識しております。</t>
@@ -679,14 +679,14 @@
     <rPh sb="53" eb="55">
       <t>イシキ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>2年</t>
     <rPh sb="1" eb="2">
       <t>ネン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>工程別</t>
@@ -696,21 +696,21 @@
     <rPh sb="2" eb="3">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>大分類</t>
     <rPh sb="0" eb="3">
       <t>ダイブンルイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>中分類</t>
     <rPh sb="0" eb="3">
       <t>チュウブンルイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>作業内容や工夫した点など</t>
@@ -726,18 +726,18 @@
     <rPh sb="9" eb="10">
       <t>テン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>理解度 ※１</t>
     <rPh sb="0" eb="3">
       <t>リカイド</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ウォーターフォール</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>要件定義</t>
@@ -747,7 +747,7 @@
     <rPh sb="2" eb="4">
       <t>テイギ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>－</t>
@@ -766,7 +766,7 @@
     <rPh sb="13" eb="15">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>基本設計</t>
@@ -776,7 +776,7 @@
     <rPh sb="2" eb="4">
       <t>セッケイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>詳細設計</t>
@@ -786,7 +786,7 @@
     <rPh sb="2" eb="4">
       <t>セッケイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>プログラムデザイン設計書にて他プロセス連携時のシーケンス図の記載実績あり。</t>
@@ -811,14 +811,14 @@
     <rPh sb="32" eb="34">
       <t>ジッセキ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>実装</t>
     <rPh sb="0" eb="2">
       <t>ジッソウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>※言語別シート参照</t>
@@ -831,46 +831,46 @@
     <rPh sb="7" eb="9">
       <t>サンショウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>単体テスト</t>
     <rPh sb="0" eb="2">
       <t>タンタイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>机上</t>
     <rPh sb="0" eb="2">
       <t>キジョウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ソースコードを画面証跡とした机上デバッグの実績あり</t>
     <rPh sb="21" eb="23">
       <t>ジッセキ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>実機</t>
     <rPh sb="0" eb="2">
       <t>ジッキ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>テストコード</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>結合テスト</t>
     <rPh sb="0" eb="2">
       <t>ケツゴウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>内部結合</t>
@@ -880,7 +880,7 @@
     <rPh sb="2" eb="4">
       <t>ケツゴウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>外部結合</t>
@@ -890,22 +890,22 @@
     <rPh sb="2" eb="4">
       <t>ケツゴウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>運用</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>性能</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>負荷</t>
     <rPh sb="0" eb="2">
       <t>フカ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>以下は消化した内容の一例
@@ -931,15 +931,15 @@
     <rPh sb="24" eb="26">
       <t>シケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>イレギュラー</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>デグレード</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>運用・保守</t>
@@ -949,7 +949,7 @@
     <rPh sb="3" eb="5">
       <t>ホシュ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>夜間バッチ監視経験あり　※スキルシート参照</t>
@@ -965,15 +965,15 @@
     <rPh sb="19" eb="21">
       <t>サンショウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ヘルプデスク</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>－</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>問い合わせ回答の経験あり　※スキルシート参照</t>
@@ -992,11 +992,11 @@
     <rPh sb="20" eb="22">
       <t>サンショウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>PMO</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>進捗管理の経験あり　※スキルシート参照</t>
@@ -1012,11 +1012,11 @@
     <rPh sb="17" eb="19">
       <t>サンショウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>アジャイル</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>実務経験なし。スクラムやスプリントなどの用語は応用情報の学習で知っているくらいのレベル感です。</t>
@@ -1044,7 +1044,7 @@
     <rPh sb="43" eb="44">
       <t>カン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>※１　理解度についての値の定義を以下に示す。</t>
@@ -1063,7 +1063,7 @@
     <rPh sb="19" eb="20">
       <t>シメ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>70%～100%：一人で実践できる</t>
@@ -1073,7 +1073,7 @@
     <rPh sb="12" eb="14">
       <t>ジッセン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>40%～69%：一人で実践できるが細かいところを指摘される不安がある</t>
@@ -1092,7 +1092,7 @@
     <rPh sb="29" eb="31">
       <t>フアン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>0%～ 39%：忘れてしまっている可能性があるが経験がある</t>
@@ -1105,7 +1105,7 @@
     <rPh sb="24" eb="26">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>※構文だけ勉強した言語は除き、実務上、成果物を作成した言語のみの記載とします。</t>
@@ -1139,14 +1139,14 @@
     <rPh sb="32" eb="34">
       <t>キサイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>言語</t>
     <rPh sb="0" eb="2">
       <t>ゲンゴ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>実装経験や取扱経験</t>
@@ -1162,7 +1162,7 @@
     <rPh sb="7" eb="9">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>最終実装年</t>
@@ -1175,29 +1175,29 @@
     <rPh sb="4" eb="5">
       <t>ネン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>優先度</t>
     <rPh sb="0" eb="3">
       <t>ユウセンド</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>C言語</t>
     <rPh sb="0" eb="3">
       <t>ｃ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Java</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>PowerShell</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>内部向けの業務改善ツールを作成した経験があります。(50ステップ×10ファイル程度)</t>
@@ -1222,11 +1222,11 @@
     <rPh sb="39" eb="41">
       <t>テイド</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Excel VBA</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>500行規模のログ取得ツール作成経験あり(1件)</t>
@@ -1248,11 +1248,11 @@
     <rPh sb="22" eb="23">
       <t>ケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Batch</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>コマンドプロンプト単体のコマンドも含めるとコピーやリネーム、検索などできます。</t>
@@ -1265,15 +1265,15 @@
     <rPh sb="30" eb="32">
       <t>ケンサク</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>HTML</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>JavaScript</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>デベロッパーツールからデバッグなどができます。
@@ -1312,7 +1312,7 @@
     <rPh sb="115" eb="117">
       <t>キョウミ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・RegExpを使用したXML閉じタグ後やJSON波括弧後の改行挿入処理
@@ -1381,11 +1381,11 @@
     <rPh sb="85" eb="87">
       <t>ショリ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Perl</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ファッション系サイトのフロント、バックエンドの実装など担当しました。
@@ -1487,15 +1487,15 @@
     <rPh sb="207" eb="208">
       <t>オコナ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>VBScript</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>C++</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>※実際に購入したものとし、Kindle Unlimitedでのレンタル読書は除きます。</t>
@@ -1511,14 +1511,14 @@
     <rPh sb="38" eb="39">
       <t>ノゾ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>分類</t>
     <rPh sb="0" eb="2">
       <t>ブンルイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>学習した書籍</t>
@@ -1528,7 +1528,7 @@
     <rPh sb="4" eb="6">
       <t>ショセキ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>実務へのプラスな影響</t>
@@ -1538,7 +1538,7 @@
     <rPh sb="8" eb="10">
       <t>エイキョウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>学習時期（年）</t>
@@ -1551,14 +1551,14 @@
     <rPh sb="5" eb="6">
       <t>ネン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>IT系</t>
     <rPh sb="2" eb="3">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>C言語ポインタ完全制覇</t>
@@ -1571,11 +1571,11 @@
     <rPh sb="9" eb="11">
       <t>セイハ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>〇</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Git入門コマンドライン演習８０</t>
@@ -1585,11 +1585,11 @@
     <rPh sb="12" eb="14">
       <t>エンシュウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>JavaエンジニアのためのEclipseパーフェクトガイド</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>JP1認定エンジニア V12対応</t>
@@ -1599,11 +1599,11 @@
     <rPh sb="14" eb="16">
       <t>タイオウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Linuxシェルスクリプト ショートガイダンス</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>実務でシェルスクリプトを解析する機会があったため学習したが、スクリプト作成までは至らなかった。Linuxコマンドはパイプラインを使用した当日日付とエラー識別子の含まれるGrepコマンドの作成経験がありました。知らないコマンドは、いきなり本番環境でコマンドで試さず、試験環境で試す作法を心得ております。</t>
@@ -1673,7 +1673,7 @@
     <rPh sb="142" eb="144">
       <t>ココロエ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Oracleデータベースの基本と仕組み(第6版)</t>
@@ -1689,7 +1689,7 @@
     <rPh sb="22" eb="23">
       <t>ハン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Subversion実践入門</t>
@@ -1699,7 +1699,7 @@
     <rPh sb="12" eb="14">
       <t>ニュウモン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>アウトルック最速仕事術</t>
@@ -1712,7 +1712,7 @@
     <rPh sb="10" eb="11">
       <t>ジュツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>即戦力のDB2管理術</t>
@@ -1725,7 +1725,7 @@
     <rPh sb="9" eb="10">
       <t>ジュツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>達人に学ぶSQL徹底指南書(第2版)</t>
@@ -1750,14 +1750,14 @@
     <rPh sb="16" eb="17">
       <t>ハン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>独習アセンブラ</t>
     <rPh sb="0" eb="2">
       <t>ドクシュウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>一応勉強してみたかったため学習したが、実務に生かす場面もなく、プラスになったものはなかった。</t>
@@ -1779,14 +1779,14 @@
     <rPh sb="25" eb="27">
       <t>バメン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ネットワークはなぜ繋がるのか</t>
     <rPh sb="9" eb="10">
       <t>ツナ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>〇</t>
@@ -1796,11 +1796,11 @@
     <rPh sb="14" eb="16">
       <t>ニュウモン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>マスタリング TCP/IP</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>資格系</t>
@@ -1810,7 +1810,7 @@
     <rPh sb="2" eb="3">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>JavaGold SE8 オラクル認定資格教科書</t>
@@ -1823,7 +1823,7 @@
     <rPh sb="21" eb="24">
       <t>キョウカショ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Java Gold紫本。約３周</t>
@@ -1839,7 +1839,7 @@
     <rPh sb="14" eb="15">
       <t>シュウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>JavaSilver SE8 オラクル認定資格教科書</t>
@@ -1852,7 +1852,7 @@
     <rPh sb="23" eb="26">
       <t>キョウカショ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Java Silver紫本。約３周</t>
@@ -1868,28 +1868,28 @@
     <rPh sb="16" eb="17">
       <t>シュウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Javaプログラマ Gold SE8 スピードマスター問題集</t>
     <rPh sb="27" eb="30">
       <t>モンダイシュウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Javaプログラマ Silver SE11 スピードマスター問題集</t>
     <rPh sb="30" eb="33">
       <t>モンダイシュウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>LPIC レベル1 スピードマスター問題集</t>
     <rPh sb="18" eb="21">
       <t>モンダイシュウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>応用情報技術者2024 午後問題の重点対策</t>
@@ -1914,18 +1914,18 @@
     <rPh sb="19" eb="21">
       <t>タイサク</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ORACLE MASTER Bronze 12c SQL基礎 スタディガイド</t>
     <rPh sb="28" eb="30">
       <t>キソ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t xml:space="preserve">ORACLE MASTER Bronze DBA11g スタディガイド </t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>キタミ式応用情報技術者</t>
@@ -1941,7 +1941,7 @@
     <rPh sb="8" eb="11">
       <t>ギジュツシャ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>徹底攻略 Java SE8 Gold 問題集</t>
@@ -1954,14 +1954,14 @@
     <rPh sb="19" eb="22">
       <t>モンダイシュウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Java Gold黒本。約３周</t>
     <rPh sb="9" eb="10">
       <t>クロ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>徹底攻略 Java SE8 Silver 問題集</t>
@@ -1974,7 +1974,7 @@
     <rPh sb="21" eb="24">
       <t>モンダイシュウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Java Silver黒本。約３周しました。ループ文を読み取る力やデータ型を考慮する基本的な能力が身についたと振り返っています。</t>
@@ -2014,7 +2014,7 @@
     <rPh sb="57" eb="58">
       <t>カエ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>徹底攻略 OracleMasterBronze 12c基礎 問題集</t>
@@ -2033,11 +2033,11 @@
     <rPh sb="32" eb="33">
       <t>シュウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ネスペR4</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>一応勉強してみたかったため、模擬試験を1周半解きました。
@@ -2084,7 +2084,7 @@
     <rPh sb="62" eb="63">
       <t>カン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>非IT系</t>
@@ -2094,7 +2094,7 @@
     <rPh sb="3" eb="4">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>答え方が人生を変える　最強の答え方</t>
@@ -2119,7 +2119,7 @@
     <rPh sb="16" eb="17">
       <t>カタ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>コミュニケーションは質問力ではなく回答力であるというのが本書の基本的な概念。
@@ -2208,7 +2208,7 @@
     <rPh sb="170" eb="172">
       <t>ブブン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>仕事で必要な「本当のコミュニケーション能力」はどう身につければいいのか</t>
@@ -2227,7 +2227,7 @@
     <rPh sb="25" eb="26">
       <t>ミ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>軽微なスキルアピールとなってしまいますが、業界標準スキルとなるため記載します。</t>
@@ -2243,14 +2243,14 @@
     <rPh sb="33" eb="35">
       <t>キサイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>区分</t>
     <rPh sb="0" eb="2">
       <t>クブン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>実務使用経験</t>
@@ -2263,7 +2263,7 @@
     <rPh sb="4" eb="6">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>自宅学習経験</t>
@@ -2276,101 +2276,101 @@
     <rPh sb="4" eb="6">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>VisualStudio 2022</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>IDE</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>有</t>
     <rPh sb="0" eb="1">
       <t>ア</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Eclipse/STS</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Windbg</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>デバッガ</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>A5:SQL Mk-2</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>WinMerge</t>
   </si>
   <si>
     <t>Diff</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>JMeter</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>試験用ドライバ</t>
     <rPh sb="0" eb="3">
       <t>シケンヨウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>JP1</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ジョブ管理</t>
     <rPh sb="3" eb="5">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Systemwalker</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Jira Service Desk</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>チケット管理ツール</t>
     <rPh sb="4" eb="6">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Backlog</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Teams</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Source Tree</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>バージョン管理</t>
     <rPh sb="5" eb="7">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>中規模開発でのコンフリクトを経験しているため、定期的にプルする作法を身に着けております。</t>
@@ -2395,119 +2395,113 @@
     <rPh sb="36" eb="37">
       <t>ツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Git Bash</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>TeraTerm</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>リモート接続</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>PowerPoint</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Office</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Excel</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>OutLook</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>WinShot</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>キャプチャ系</t>
     <rPh sb="5" eb="6">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>サクラエディタ</t>
   </si>
   <si>
     <t>テキストエディタ</t>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>秀丸</t>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Google Chrome</t>
   </si>
   <si>
     <t>ブラウザ</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>thunderbird</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>メーラー</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Oracle SQL Developer</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>H2</t>
   </si>
   <si>
     <t>FileZilla</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>FTP</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>WinSCP</t>
   </si>
   <si>
     <t>Microsoft Access</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Office</t>
   </si>
   <si>
     <t>Word</t>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>Virtual Box</t>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>VM</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ウイルスバスター</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>アンチウイルスソフト</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Symantec</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>インターネットから不要なファイルを無断でインストールしないなど留意し、セキュリティソフトにトラップされないように意識しておりました。</t>
@@ -2523,7 +2517,7 @@
     <rPh sb="56" eb="58">
       <t>イシキ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t xml:space="preserve">Norton </t>
@@ -2539,11 +2533,11 @@
     <rPh sb="24" eb="26">
       <t>サホウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Zabbix</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>運用管理ツール</t>
@@ -2553,18 +2547,15 @@
     <rPh sb="2" eb="4">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Redmine</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Rocket.Chat</t>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>Slack</t>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ジョブの夜間監視結果の日時報告の際に使用しておりましたので、
@@ -2602,11 +2593,11 @@
     <rPh sb="46" eb="47">
       <t>ツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>SVN</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>設計書を管理しているSVNにコミットやチェックアウト経験あり</t>
@@ -2619,26 +2610,26 @@
     <rPh sb="26" eb="28">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Stirling</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>バイナリエディタ</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>SharePoint</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ファイル共有</t>
     <rPh sb="4" eb="6">
       <t>キョウユウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>OneDriveと連携しローカル上のエクスプローラーから操作した経験あり</t>
@@ -2654,18 +2645,18 @@
     <rPh sb="32" eb="34">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Firefox</t>
   </si>
   <si>
     <t>Internet Explorer</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Photoshop</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>レイヤーを使用した基本的な操作やWeb用画像のスライスなど</t>
@@ -2684,29 +2675,29 @@
     <rPh sb="20" eb="22">
       <t>ガゾウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>IP Messenger</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Windows機能別</t>
     <rPh sb="9" eb="10">
       <t>ベツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Windows機能名</t>
     <rPh sb="7" eb="10">
       <t>キノウメイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>VBE(Visual Basic Editor)</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>クラスの作成やイミディエイトウィンドウの使用など基本的な操作が可能です。</t>
@@ -2725,11 +2716,11 @@
     <rPh sb="31" eb="33">
       <t>カノウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Windows PowerShell ISE</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>デバッグや変数の値の確認といった基本的な操作が可能です。</t>
@@ -2751,11 +2742,11 @@
     <rPh sb="23" eb="25">
       <t>カノウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>hosts</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>バッチ処理でhostsを書き換え、試験環境を変更する現場を経験しています。</t>
@@ -2783,11 +2774,11 @@
     <rPh sb="29" eb="31">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>コマンドプロンプト</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ほかの人が書いたバッチを解析した経験があるので、pauseや変数値をechoで出力するなどして、エラーを自力で特定できます。</t>
@@ -2818,15 +2809,15 @@
     <rPh sb="55" eb="57">
       <t>トクテイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>グループポリシー</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>レジストリ</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>過去３世代（次期・現行・旧環境）のシステムの設定値をドキュメント化した経験あります。</t>
@@ -2845,11 +2836,11 @@
     <rPh sb="35" eb="37">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>イベントビューア</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>次期開発システムで異常なイベントが取得されていないか調査する必要があったため、CSV化して次期と現行のログを比較した経験があります。</t>
@@ -2886,18 +2877,18 @@
     <rPh sb="58" eb="60">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>エクスプローラー</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>共有フォルダ</t>
     <rPh sb="0" eb="2">
       <t>キョウユウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>システムの移行手順に従い、お客様環境の共有フォルダで参照できるユーザーの追加やアクセス許可などを設定した経験があります。また、お客様環境での作業がスムーズになるように事前に共有フォルダにアクセスするユーザーを作成するためにバッチを準備・実行した経験があります。</t>
@@ -2964,11 +2955,11 @@
     <rPh sb="122" eb="124">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>タスクマネージャー</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>環境変数</t>
@@ -2978,15 +2969,15 @@
     <rPh sb="2" eb="4">
       <t>ヘンスウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>過去３世代（次期・現行・旧環境）のシステムの設定値をドキュメント化し、現行の設定値と同じになるように次期業務システムの設定を行った経験があります。</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ペイント</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>スリープ画面時にPrintScreenキーを押すことにより、スリープを解除しながらデスクトップアプリの様子を撮影し、スリープ中の障害発生条件を解決した経験があります。ほか、レガシー環境など証跡自動取得ツールがない状態で活用することが多かったので、１分間に証跡が5つ程度保存することができます。</t>
@@ -3059,11 +3050,11 @@
     <rPh sb="134" eb="136">
       <t>ホゾン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ワードパッド</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Officeのインストールされていない試験端末での作業経験があり、試験端末でも参照できる手順書を作成した実績があります。(約50件)</t>
@@ -3106,14 +3097,14 @@
     <rPh sb="64" eb="65">
       <t>ケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>リモートデスクトップ接続</t>
     <rPh sb="10" eb="12">
       <t>セツゾク</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>多人数で共通の端末をリモート接続する現場経験があったので、ゾンビセッションを残さないように接続を終了する作法を心得ております。</t>
@@ -3150,11 +3141,11 @@
     <rPh sb="55" eb="57">
       <t>ココロエ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>サービス</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>過去３世代のシステムの設定値をドキュメント化した経験があり、
@@ -3195,11 +3186,11 @@
     <rPh sb="73" eb="75">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ノートパッド</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ファイル名を指定して実行</t>
@@ -3212,14 +3203,14 @@
     <rPh sb="10" eb="12">
       <t>ジッコウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>電卓</t>
     <rPh sb="0" eb="2">
       <t>デンタク</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>カウンタとして使用したり、16進数や2進数の値のチェックなどに使用した経験あり</t>
@@ -3241,15 +3232,15 @@
     <rPh sb="35" eb="37">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>IME</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>LANケーブル</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>業務中LANケーブルの抜き差しを行う場合でも、VLANを意識して、元のケーブル差込口に戻すことができます。</t>
@@ -3283,7 +3274,7 @@
     <rPh sb="43" eb="44">
       <t>モド</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>外付けUSB</t>
@@ -3293,11 +3284,11 @@
     <rPh sb="1" eb="2">
       <t>ヅ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>クロック</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ラップ機能などを使用し、業務システムのCSVエクスポート機能の性能試験などに使用した経験あり</t>
@@ -3325,14 +3316,14 @@
     <rPh sb="42" eb="44">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>業種</t>
     <rPh sb="0" eb="2">
       <t>ギョウシュ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>製造系</t>
@@ -3342,7 +3333,7 @@
     <rPh sb="2" eb="3">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>非エンジニア時代に自動車部品製造(3年)をやっており、製造工程の機械が人に与える影響を理解しております。
@@ -3417,21 +3408,21 @@
     <rPh sb="126" eb="128">
       <t>イシキ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>銀行系</t>
     <rPh sb="0" eb="3">
       <t>ギンコウケイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ロジスティクス系</t>
     <rPh sb="7" eb="8">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ロジスティクス向けアプリのテスト経験があり、
@@ -3560,7 +3551,7 @@
     <rPh sb="193" eb="195">
       <t>シヨウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>人事系</t>
@@ -3570,14 +3561,14 @@
     <rPh sb="2" eb="3">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ファッション系</t>
     <rPh sb="6" eb="7">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>特別専門に勉強したレベルではありませんが、開発を通じファッション系の通販サイトなどのメニューや新商品追加、セールなどの業務背景に触れた経験はあります。</t>
@@ -3620,7 +3611,7 @@
     <rPh sb="67" eb="69">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>大手通信業界でのお客様環境でサードパーティアプリのインストールや開発アプリ資源のデプロイ、および総合試験の実施を行った経験があります。業務知識については特別専門に勉強したレベルではありません。</t>
@@ -3666,15 +3657,15 @@
     <rPh sb="69" eb="71">
       <t>チシキ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>仕事の進め方や考え方などについて</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>以下、現場のミスマッチを防ぐために私の考えや求めていることを記載いたします。</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>私の強みはプログラミング関係です。</t>
@@ -3687,7 +3678,7 @@
     <rPh sb="12" eb="14">
       <t>カンケイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>キャリアビジョン</t>
@@ -3712,7 +3703,7 @@
     <rPh sb="37" eb="38">
       <t>カンガ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>言語について</t>
@@ -3731,7 +3722,7 @@
     <rPh sb="28" eb="30">
       <t>エンカツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>その次に言語としては将来性のありそうな言語や伝統のある言語であるほうが良いと考えております。</t>
@@ -3747,7 +3738,7 @@
     <rPh sb="38" eb="39">
       <t>カンガ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>自身の性格について</t>
@@ -3763,7 +3754,7 @@
     <rPh sb="9" eb="11">
       <t>セイカク</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>実装について</t>
@@ -3776,29 +3767,10 @@
     <rPh sb="17" eb="19">
       <t>キボウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>その他</t>
-  </si>
-  <si>
-    <t>趣味はネット将棋です。アマ二段を取得した実績があります。</t>
-    <rPh sb="0" eb="2">
-      <t>シュミ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ショウギ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ニダン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ジッセキ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>2017年1月からの趣味です。</t>
@@ -3811,7 +3783,7 @@
     <rPh sb="10" eb="12">
       <t>シュミ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>一人称、自走</t>
@@ -3821,7 +3793,7 @@
     <rPh sb="4" eb="6">
       <t>ジソウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>健康面</t>
@@ -3831,7 +3803,7 @@
     <rPh sb="2" eb="3">
       <t>メン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>IT技術ではなく業務仕様の深い理解が必要だと考えています。</t>
@@ -3856,7 +3828,7 @@
     <rPh sb="22" eb="23">
       <t>カンガ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>長期的な観点で自走するためにも現場の有識者への質問が必要不可欠だと考えております。</t>
@@ -3887,7 +3859,7 @@
     <rPh sb="33" eb="34">
       <t>カンガ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>以下は計測した内容の一例
@@ -3953,7 +3925,7 @@
     <rPh sb="70" eb="72">
       <t>ケイソク</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>特に慢性的な持病があるというわけではありません。</t>
@@ -3966,7 +3938,7 @@
     <rPh sb="6" eb="8">
       <t>ジビョウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>基本的に良好です。</t>
@@ -3976,14 +3948,14 @@
     <rPh sb="4" eb="6">
       <t>リョウコウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>小分類</t>
     <rPh sb="0" eb="3">
       <t>ショウブンルイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Java Silver白本。SE8とSE11のどちらか迷ったため、購入。取得には至らなかったが、var（型推論）やモジュールなどが追加されたことは概念として理解しております。</t>
@@ -4020,7 +3992,7 @@
     <rPh sb="78" eb="80">
       <t>リカイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>開発者ツールのFirebugの使用経験などあり</t>
@@ -4033,7 +4005,7 @@
     <rPh sb="17" eb="19">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>障害発生時の事象の報告など経験あり(10～20件)。
@@ -4089,7 +4061,7 @@
     <rPh sb="59" eb="61">
       <t>イシキ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>銀行システム利用者が使用するための銀行業務用IME辞書を現新比較、および設定した経験があります。</t>
@@ -4129,7 +4101,7 @@
     <rPh sb="40" eb="42">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>システム利用者向けの可搬媒体を使用した手順書の作成経験がありますので、高速スタートアップ設定時にUSBの動作不良が起きやすいことを認識しております。
@@ -4203,7 +4175,7 @@
     <rPh sb="117" eb="119">
       <t>ココロエ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>設計書を編集する際なども元の状態に戻せるようにバックアップしておく作法を心得ております。
@@ -4232,7 +4204,7 @@
     <rPh sb="36" eb="38">
       <t>ココロエ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>InternetExplorer終了中に別プロセスのInternetExplorerが立ち上がらないシステム障害の原因の調査を経験しているので、コマンドライン列などからプロセスがどのファイルから起動され、どのパラメータを受け取っているか特定できます。</t>
@@ -4278,14 +4250,14 @@
     <rPh sb="118" eb="120">
       <t>トクテイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>イメージ管理</t>
     <rPh sb="4" eb="6">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>端末構築手順にそって設定・デプロイなどした試験用端末のイメージをバックアップ・リストアした経験があります。ほかチームも利用する端末のリストアも含めるため、1回のリストア依頼で２６件規模の対応の実績あり。プロジェクト完了後の運用チーム、および次回更改プロジェクトメンバー宛てにバックアップ・リストアのフローチャート付き手順書を作成。</t>
@@ -4367,19 +4339,19 @@
     <rPh sb="162" eb="164">
       <t>サクセイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>DataCloningWizard（データクローニングウィザード）</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Acrobat Reader 2020</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>PDF</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>実務を通して以下の経験があります。
@@ -4406,7 +4378,7 @@
     <rPh sb="80" eb="82">
       <t>チョウサ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>過去３世代（次期・現行・旧環境）のシステムの設定値をドキュメント化し、現行の設定値と同じになるように次期業務システムの設定を行った経験があります。次期環境で非推奨(非サポート)となっていないかなど調査した経験があります。</t>
@@ -4467,11 +4439,11 @@
     <rPh sb="102" eb="104">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Oracle Certified Java Programmer, Gold SE 8</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>・スリープ解除時のWM_PAINT受信時のエディットコントロール描画障害調査(1件)
@@ -4509,7 +4481,7 @@
     <rPh sb="67" eb="69">
       <t>サギョウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ほぼ解析専門。
@@ -4565,7 +4537,7 @@
     <rPh sb="99" eb="101">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・修正箇所の関連機能や類似機能の確認
@@ -4627,7 +4599,7 @@
     <rPh sb="53" eb="55">
       <t>カクニン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・ネットワークと共有センター有効無効切替スクリプトの解析、および設計書作成
@@ -4674,7 +4646,7 @@
     <rPh sb="67" eb="69">
       <t>タイオウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・シーケンス図や表などを用いたプログラムデザイン設計書の作成経験あり(約20件)
@@ -4730,7 +4702,7 @@
     <rPh sb="80" eb="81">
       <t>ケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>時刻指定保存機能やプリントスクリーン長押し機能を使用してスリープ中のアプリの画面状態を撮影して障害の発生条件を特定した実績があります。</t>
@@ -4782,76 +4754,7 @@
     <rPh sb="59" eb="61">
       <t>ジッセキ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>ほぼ解析専門。
-デスクトップアプリ(MFC)のエディットコントロールの罫線が表示されなくなる画面描画障害があっため、調査の経験あり。(1か月程度)
-ログ取得関数をコンストラクタ～デストラクタなどの一連の処理の間に複数呼び出し宣言を行い、ログから障害を調査した経験あり(1件)</t>
-    <rPh sb="2" eb="4">
-      <t>カイセキ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>センモン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ケイセン</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ビョウガ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>ショウガイ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>チョウサ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="69" eb="70">
-      <t>ゲツ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>テイド</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="78" eb="80">
-      <t>カンスウ</t>
-    </rPh>
-    <rPh sb="98" eb="100">
-      <t>イチレン</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="104" eb="105">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="106" eb="108">
-      <t>フクスウ</t>
-    </rPh>
-    <rPh sb="122" eb="124">
-      <t>ショウガイ</t>
-    </rPh>
-    <rPh sb="125" eb="127">
-      <t>チョウサ</t>
-    </rPh>
-    <rPh sb="129" eb="131">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="135" eb="136">
-      <t>ケン</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>外部とのメールのやり取りが多い時期に勉強しました。
@@ -4895,7 +4798,7 @@
     <rPh sb="77" eb="79">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>言語ごとに技術レベルのムラがあるので現場で必要なスキルを直接保有しているか面談の際に確認していただければ幸いです。</t>
@@ -4929,7 +4832,7 @@
     <rPh sb="52" eb="53">
       <t>サイワ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>クライアントからの機能追加要望に対し、対応可否や対応工数など回答経験あり(約10件前後)</t>
@@ -4972,7 +4875,7 @@
     <rPh sb="41" eb="43">
       <t>ゼンゴ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>固定長電文やログの16進数やパック10進数を解析した経験があります。</t>
@@ -4994,7 +4897,7 @@
     <rPh sb="26" eb="28">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>業務システムの基本的な機能</t>
@@ -5007,11 +4910,11 @@
     <rPh sb="11" eb="13">
       <t>キノウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>－</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>業務内容について</t>
@@ -5021,7 +4924,7 @@
     <rPh sb="2" eb="4">
       <t>ナイヨウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ファイル共有システム
@@ -5045,21 +4948,21 @@
     <rPh sb="50" eb="52">
       <t>セイギョ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>C言語</t>
     <rPh sb="1" eb="3">
       <t>ゲンゴ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>年月</t>
     <rPh sb="0" eb="2">
       <t>ネンゲツ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>5年6か月</t>
@@ -5069,7 +4972,7 @@
     <rPh sb="4" eb="5">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>3年1か月</t>
@@ -5079,38 +4982,38 @@
     <rPh sb="4" eb="5">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>9か月</t>
     <rPh sb="2" eb="3">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>3か月</t>
     <rPh sb="2" eb="3">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>4か月</t>
     <rPh sb="2" eb="3">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>Perl
 HTML</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>Java
 (Spring)</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>以下は開発を通じ触れた業務の内容や業務システムの経験です。ただし、機能実装経験のみではなく、システム利用者側の観点でテストを行ったことがある経験を含みます。</t>
@@ -5138,7 +5041,7 @@
     <rPh sb="24" eb="26">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>在庫管理システム
@@ -5176,24 +5079,24 @@
     <rPh sb="54" eb="56">
       <t>キノウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>JQuery</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>win32API</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>Microsoft Foundation Class</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>CGI.pm
 DBI</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>使用ライブラリ例</t>
@@ -5203,12 +5106,12 @@
     <rPh sb="7" eb="8">
       <t>レイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>CSS
 Bootstrap</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>・通販サイトの期間限定セールCGI修正（2BUY価格や消費税など）
@@ -5298,7 +5201,7 @@
     <rPh sb="165" eb="167">
       <t>サクセイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>以下は項目作成・実施した項目の一例
@@ -5439,7 +5342,7 @@
     <rPh sb="185" eb="187">
       <t>カクニン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>「なぜ」と聞かない質問術</t>
@@ -5452,7 +5355,7 @@
     <rPh sb="11" eb="12">
       <t>ジュツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>独習 JSP&amp;サーブレット第3版</t>
@@ -5465,7 +5368,7 @@
     <rPh sb="15" eb="16">
       <t>ハン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>Java Gold白本。４周程度実施。</t>
@@ -5481,7 +5384,7 @@
     <rPh sb="16" eb="18">
       <t>ジッシ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>以下のことを理解しました。
@@ -5529,7 +5432,7 @@
     <rPh sb="70" eb="71">
       <t>ウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>以下は学んだことの一例です。
@@ -5591,15 +5494,15 @@
     <rPh sb="151" eb="153">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ポートフォリオ</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>https://github.com/Test-Information/portfolio</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>JQueryの実装やWordPressへの対応など行い実務外でのポートフォリオ作品を作成した経験があります。2016年に学んでから最新技術にアップデートできていないので、保有技術はレガシー寄りになってるかもしれません。</t>
@@ -5648,7 +5551,7 @@
     <rPh sb="94" eb="95">
       <t>ヨ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>預金業務～為替など、大枠は理解しています。顧客登録、口座作成、入金、出金、為替など。口座の登録～口座の解約までのシナリオを想像し、総合試験項目を作成した経験があります。通帳への書き込みやページめくり、新通帳発行など利用したビジネスロジックの修正の経験もあります。</t>
@@ -5742,7 +5645,7 @@
     <rPh sb="123" eb="125">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>以下の内容を理解しました。
@@ -5772,7 +5675,7 @@
     <rPh sb="39" eb="41">
       <t>シヨウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>本資料は案件別のスキルシートとは別の経験やスキルの詳細を伝えるために作成しました。</t>
@@ -5794,7 +5697,7 @@
     <rPh sb="18" eb="20">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>資料に記載してある内容でも遠慮なく質問していただければと思います。</t>
@@ -5816,7 +5719,7 @@
     <rPh sb="28" eb="29">
       <t>オモ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>面談の際に、セルの塗りつぶしやフィルタリングなどを行っていただいても問題ございません。</t>
@@ -5835,7 +5738,7 @@
     <rPh sb="34" eb="36">
       <t>モンダイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>以下の手順を学びました。
@@ -5869,20 +5772,7 @@
     <rPh sb="64" eb="66">
       <t>ホウホウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>ポインタがアドレスを指し示す概念であることなど理解しました。</t>
-    <rPh sb="10" eb="13">
-      <t>サシシメ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ガイネン</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>リカイ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>CDBやPDB、トランザクションの開始、終了条件に付いては学びましたが、知らない機能のほうが多いです。</t>
@@ -5910,7 +5800,7 @@
     <rPh sb="46" eb="47">
       <t>オオ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Pingを使用した別の階の端末の起動状態の確認やARPテーブルを使用した端末の特定などができるようになりました。</t>
@@ -5944,7 +5834,7 @@
     <rPh sb="39" eb="41">
       <t>トクテイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>VLANやDNS・HOSTS、MACアドレスなどネットワーク以外の実務を行う上でも知識が水面下で生きている実感があります。</t>
@@ -5969,7 +5859,7 @@
     <rPh sb="53" eb="55">
       <t>ジッカン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>以下に習得技術や経験を記述します。
@@ -6014,7 +5904,7 @@
     <rPh sb="128" eb="130">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Where条件をCase条件に置き換えることができることに感銘を受けました。</t>
@@ -6036,7 +5926,7 @@
     <rPh sb="32" eb="33">
       <t>ウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>以下の内容を理解しました
@@ -6057,7 +5947,7 @@
     <rPh sb="92" eb="94">
       <t>サクセイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>コメント（スキルや経験、作法など）</t>
@@ -6067,7 +5957,7 @@
     <rPh sb="12" eb="14">
       <t>サホウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>以下に習得技術や経験を記述します。
@@ -6143,7 +6033,7 @@
     <rPh sb="183" eb="186">
       <t>セイゴウセイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>応用情報資格取得のため3週ほど実施。
@@ -6225,7 +6115,7 @@
     <rPh sb="131" eb="133">
       <t>シク</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t xml:space="preserve">
@@ -6233,60 +6123,11 @@
     <rPh sb="1" eb="3">
       <t>ソウゴウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>DB GUIツール</t>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>JP1で運用試験を担当したときに知識がなかったため補強していました。即時実行や保留などの操作は行えるが、設定面に関する知識は保有していません。</t>
-    <rPh sb="4" eb="6">
-      <t>ウンヨウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シケン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>タントウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>チシキ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ホキョウ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ソクジ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ホリュウ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>メン</t>
-    </rPh>
-    <rPh sb="56" eb="57">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>チシキ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>ホユウ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>以下の内容を理解しました。
@@ -6341,7 +6182,7 @@
     <rPh sb="182" eb="184">
       <t>セッテイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>デベロッパーツールのElementsやConsole、スマホシミュレータ等の使用経験あり</t>
@@ -6354,7 +6195,7 @@
     <rPh sb="40" eb="42">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・Q&amp;Aページの新規実装
@@ -6426,7 +6267,7 @@
     <rPh sb="118" eb="119">
       <t>カ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>コレクションやジェネリクス、JDBCなどについて学びました。Stream APIやラムダ式はデバッグ効率が下がる可能性があるため現場を選ぶと考えております。</t>
@@ -6454,11 +6295,11 @@
     <rPh sb="70" eb="71">
       <t>カンガ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Oracle Certified Java Programmer, Silver SE 8</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>Linux関係の現場に参画した際に必要だと感じたため、6割程度実施。
@@ -6514,7 +6355,7 @@
     <rPh sb="92" eb="94">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>以下に習得技術や経験を記述します。
@@ -6533,128 +6374,7 @@
     <rPh sb="163" eb="165">
       <t>コウブンレンケイシヨウソウサ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>・外部ライブラリを使用しないJSONデータの作成や構文チェックおよび、制御文字のエスケープ対応(1件)
-・外部ライブラリを使用しないXMLデータの作成や構文チェック、実体参照文字のエスケープ対応
-・パック10進数からゾーン10進数へのシフト演算を使用した変換処理(1件)
-・固定長電文の処理結果ビットに応じたエラーメッセージ処理の追加
-・他プロセスの変更したグローバル変数などと連携した処理の実装
-・画面項目の変更に伴う入力チェック処理の追加
-・関数ポインタを使用したポリモーフィズムの実装(1件のみ)</t>
-    <rPh sb="1" eb="3">
-      <t>ガイブ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>コウブン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>セイギョ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>コウブン</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>ジッタイ</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>サンショウ</t>
-    </rPh>
-    <rPh sb="87" eb="89">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="95" eb="97">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="104" eb="106">
-      <t>シンスウ</t>
-    </rPh>
-    <rPh sb="113" eb="115">
-      <t>シンスウ</t>
-    </rPh>
-    <rPh sb="120" eb="122">
-      <t>エンザン</t>
-    </rPh>
-    <rPh sb="131" eb="133">
-      <t>ヘンカン</t>
-    </rPh>
-    <rPh sb="133" eb="135">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="137" eb="140">
-      <t>コテイチョウ</t>
-    </rPh>
-    <rPh sb="140" eb="142">
-      <t>デンブン</t>
-    </rPh>
-    <rPh sb="143" eb="145">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="145" eb="147">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="156" eb="157">
-      <t>トモナ</t>
-    </rPh>
-    <rPh sb="162" eb="164">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="169" eb="171">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="173" eb="174">
-      <t>ホカ</t>
-    </rPh>
-    <rPh sb="179" eb="181">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="188" eb="190">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="193" eb="195">
-      <t>レンケイ</t>
-    </rPh>
-    <rPh sb="200" eb="202">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="212" eb="213">
-      <t>トモナ</t>
-    </rPh>
-    <rPh sb="214" eb="216">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="223" eb="225">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="227" eb="229">
-      <t>カンスウ</t>
-    </rPh>
-    <rPh sb="243" eb="245">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="247" eb="249">
-      <t>ジッソウケン</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>C言語は他多くの言語と違いエラーが出ずにクラッシュしてしまう言語です。</t>
@@ -6679,7 +6399,7 @@
     <rPh sb="30" eb="32">
       <t>ゲンゴ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>Gitなどもない環境でコーディングすることが多かったので、デグレ防止の意識が高まったと感じております。</t>
@@ -6701,7 +6421,7 @@
     <rPh sb="43" eb="44">
       <t>カン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>繰り返しの中でメモリ生成を避けたコーディングができ、内部ツールなどの作成経験もあります。</t>
@@ -6720,14 +6440,14 @@
     <rPh sb="13" eb="14">
       <t>サ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>強みと弱み</t>
     <rPh sb="3" eb="4">
       <t>ヨワ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>通信系2</t>
@@ -6737,7 +6457,7 @@
     <rPh sb="2" eb="3">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>通信系1</t>
@@ -6747,19 +6467,19 @@
     <rPh sb="2" eb="3">
       <t>ケイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Java</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>VSCODE</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>テキストエディタ</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <r>
@@ -6810,14 +6530,14 @@
     <rPh sb="31" eb="33">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>更新日：</t>
     <rPh sb="0" eb="3">
       <t>コウシンビ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>手順書に従ったZabbixエージェントのお客様環境端末へのインストール経験あり</t>
@@ -6839,22 +6559,22 @@
     <rPh sb="35" eb="37">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Google Workspace</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>グループウェア</t>
   </si>
   <si>
     <t>グループウェア</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Proself</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>月次定例作業の手順書にインポート作業の経験あり。
@@ -6886,14 +6606,14 @@
     <rPh sb="43" eb="45">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>1か月</t>
     <rPh sb="2" eb="3">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>プロビジョニングシステム
@@ -6910,7 +6630,7 @@
     <rPh sb="35" eb="37">
       <t>カイシュウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>銀行向け取引システム
@@ -6966,7 +6686,7 @@
     <rPh sb="72" eb="74">
       <t>キノウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>人事イベント管理システム
@@ -6993,7 +6713,7 @@
     <rPh sb="33" eb="35">
       <t>セッテイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t xml:space="preserve">ファッション系ECサイト
@@ -7035,7 +6755,7 @@
     <rPh sb="83" eb="85">
       <t>キノウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>スマホ購入時の新規契約時の回線開通時の処理工程内で使用されるプロビジョニングシステムの電文受入処理の緊急リリース対応を担当。対抗システムへのレスポンス返却個所の調査、およびRFC 9112に準拠し、Httpレスポンスヘッダ内の改行コードのLFをCRLFに統一する処理の実装、テストを担当。</t>
@@ -7123,7 +6843,7 @@
     <rPh sb="141" eb="143">
       <t>タントウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>人事イベント（入社、異動、昇進、結婚、出産、退職等）を管理しているシステムのテスト経験がありました。前回の更改プロジェクトの残したテストデータを使用し、更改予定のDBのカラム定義に合わせSQLを修正し試験を行った経験があります。</t>
@@ -7175,7 +6895,7 @@
     <rPh sb="113" eb="114">
       <t>オコナケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・Google Meetでの画面共有経験
@@ -7208,15 +6928,15 @@
     <rPh sb="50" eb="52">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Cisco AnyConnect</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>VPN</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>以下のような内容を想定した試験項目の作成、実施経験あり
@@ -7267,7 +6987,7 @@
     <rPh sb="88" eb="90">
       <t>ツイカ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>条件網羅などの試験項目の作成、実施経験あり。
@@ -7332,7 +7052,7 @@
     <rPh sb="72" eb="74">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>JMeterやCurlコマンドをドライバとした試験の経験あり</t>
@@ -7342,7 +7062,7 @@
     <rPh sb="26" eb="28">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>タブレットチーム開発資源を開発環境に配置し、試験を行った実績あり。</t>
@@ -7370,289 +7090,20 @@
     <rPh sb="28" eb="30">
       <t>ジッセキ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>ログイン時のメールアドレス入力規則チェックなど、Httpリクエスト、レスポンス時の処理の実装経験があります。
-開発経験の一例を以下に記載します。
-1)Linuxデーモン(常駐システム)のソケット間通信電文の返却処理の修正経験
-2)人事イベント管理Webアプリの給与管理画面ロジック修正
-3)入学受験アドバイス用チャットWebアプリの問い合わせフォーム画面修正
-4)宿泊予約Androidアプリのログイン規則、予約ロジック修正
-&lt;注意&gt;
-JavaEE等、サーバサイドで使用している画面の修正の経験はありますが、JavaSEのみの画面開発やオンラインバッチの修正経験などは現状ありません。
-log4jは環境構築の経験はありません。</t>
-    <rPh sb="4" eb="5">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>キソク</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>カイハツ</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>イチレイ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>キサイ</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>ジョウチュウ</t>
-    </rPh>
-    <rPh sb="97" eb="98">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="98" eb="100">
-      <t>ツウシン</t>
-    </rPh>
-    <rPh sb="100" eb="102">
-      <t>デンブン</t>
-    </rPh>
-    <rPh sb="103" eb="105">
-      <t>ヘンキャク</t>
-    </rPh>
-    <rPh sb="105" eb="107">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="108" eb="110">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="115" eb="117">
-      <t>ジンジ</t>
-    </rPh>
-    <rPh sb="121" eb="123">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="130" eb="132">
-      <t>キュウヨ</t>
-    </rPh>
-    <rPh sb="132" eb="134">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="134" eb="136">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="140" eb="142">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="145" eb="147">
-      <t>ニュウガク</t>
-    </rPh>
-    <rPh sb="147" eb="149">
-      <t>ジュケン</t>
-    </rPh>
-    <rPh sb="154" eb="155">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="166" eb="167">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="168" eb="169">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="175" eb="177">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="177" eb="179">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="194" eb="196">
-      <t>シュクハク</t>
-    </rPh>
-    <rPh sb="201" eb="203">
-      <t>キソク</t>
-    </rPh>
-    <rPh sb="204" eb="206">
-      <t>ヨヤク</t>
-    </rPh>
-    <rPh sb="210" eb="212">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="246" eb="248">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="252" eb="254">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="255" eb="257">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="263" eb="265">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="265" eb="267">
-      <t>カイハツ</t>
-    </rPh>
-    <rPh sb="290" eb="292">
-      <t>シュウセイケイケンゲンジョウ</t>
-    </rPh>
-    <rPh sb="299" eb="301">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="301" eb="303">
-      <t>コウチク</t>
-    </rPh>
-    <rPh sb="304" eb="306">
-      <t>ケイケン</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>C言語プログラム(PC)とJavaプログラム(タブレット)の連携の際に使用していた経験があります。</t>
-    <rPh sb="1" eb="3">
-      <t>ゲンゴ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>レンケイ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ケイケン</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>・Xpathによる孫要素や複数同名タグ存在時の要素指定の経験あり
-・ブラウザやデザインビューによる構文違反のチェック</t>
-    <rPh sb="9" eb="10">
-      <t>マゴ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヨウソ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>フクスウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ドウメイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>コウブン</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>イハン</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>JSON</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>XML</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Linux
 シェル</t>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>・JSONキー名に"や\が含まれていた場合の試験経験あり
-・XMLタグにJSONが含まれていた場合の二重構文チェックの経験あり</t>
-    <rPh sb="7" eb="8">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>シケン</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>ニジュウ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>コウブン</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ケイケン</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>C言語プログラム(PC)とJavaプログラム(タブレット)の連携の際に使用していた経験があります。テストで定例的に使用するタグなどはExcelのフラッシュフィル機能を使用し、タグの生成などを行い試験データを作成したことがあります。</t>
-    <rPh sb="1" eb="3">
-      <t>ゲンゴ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>レンケイ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="53" eb="56">
-      <t>テイレイテキ</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="80" eb="82">
-      <t>キノウ</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="90" eb="92">
-      <t>セイセイ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ant</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>ビルドツール</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>SpringBoot
@@ -7661,7 +7112,7 @@
 Lombok
 log4j
 Mockito</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>リフレクションやMockitoを使用したJUnitコードの作成経験あり。</t>
@@ -7674,7 +7125,7 @@
     <rPh sb="31" eb="33">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>だまし絵を描かないための－－要件定義のセオリー</t>
@@ -7690,7 +7141,7 @@
     <rPh sb="16" eb="18">
       <t>テイギ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>はじめよう！要件定義～ビギナーからベテランまで</t>
@@ -7700,15 +7151,15 @@
     <rPh sb="8" eb="10">
       <t>テイギ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>未読了</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>未読</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>Q&amp;A資料の作成経験</t>
@@ -7721,23 +7172,11 @@
     <rPh sb="8" eb="10">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>・本番環境へのファイルのアップロード経験あり
-・アップロード時の確認ダイアログの設定やサイズや更新日時の確認
-・テキストモードやバイナリモードを考慮したアップロード経験</t>
-    <rPh sb="72" eb="74">
-      <t>コウリョ</t>
-    </rPh>
-    <rPh sb="82" eb="84">
-      <t>ケイケン</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>TortoiseGit</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・.gitignore等、ローカル資源を考慮したコミット経験
@@ -7755,7 +7194,7 @@
     <rPh sb="28" eb="30">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>コンパイル環境でのビルド経験や、実行環境でのログの確認経験があります。</t>
@@ -7777,7 +7216,7 @@
     <rPh sb="27" eb="29">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>マークアップ</t>
@@ -7787,22 +7226,18 @@
   </si>
   <si>
     <t>コンパイル</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>インタプリタ</t>
   </si>
   <si>
     <t>インタプリタ</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>OSシェル</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>データ記述言語</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>・build.xmlへの外部 jarのクラスパスの設定経験</t>
@@ -7815,7 +7250,7 @@
     <rPh sb="27" eb="29">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・リモートワーク使用用途でのVPNの接続経験あり</t>
@@ -7831,18 +7266,11 @@
     <rPh sb="20" eb="22">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>CentOS6のインストール経験</t>
-    <rPh sb="14" eb="16">
-      <t>ケイケン</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>デザイン</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>次期試験端末へのインストール、およびウイルス定義ファイルの最新化作業など</t>
@@ -7867,7 +7295,7 @@
     <rPh sb="32" eb="34">
       <t>サギョウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>Linuxを用いた案件は経験していますが、開発案件ではなかったためLinux上での開発経験に少し難があるかもしれません。</t>
@@ -7901,14 +7329,14 @@
     <rPh sb="48" eb="49">
       <t>ナン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>JavaSilver資格 PDF</t>
     <rPh sb="10" eb="12">
       <t>シカク</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>stdio.h
@@ -7920,198 +7348,7 @@
     <rPh sb="38" eb="40">
       <t>ザガク</t>
     </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>標準ライブラリでのプログラミング経験が豊富。メモリ領域初期化漏れや他変数の領域破壊などがないように意識しながら実装する作法を心得ております。別プロセスやタブレットから呼び出されるインターフェースの修正を主に担当し、パラメータに応じたデータの加工処理のロジックの実装経験あり。30年運用されているシステムでの実装だったので完全新規での仕様追加は少なく、既存仕様に対応する関数を流用し、機能拡張していくという業務が中心。ビルド時の警告は全て対応する作法を心得ております。
-&lt;注意&gt;
-1)VisualStudioを使用していたのでGCCは実務経験なし
-2)DBアクセスは他チームが担当していたので、C言語ではDB連携経験なし
-※ただしPRO*Cに関しては、自社待期期間で１週間程度のコードの読み取り経験あり。</t>
-    <rPh sb="16" eb="18">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ホウフ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>リョウイキ</t>
-    </rPh>
-    <rPh sb="27" eb="30">
-      <t>ショキカ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>モ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ホカ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>リョウイキ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ハカイ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>イシキ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>サホウ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>ココロエ</t>
-    </rPh>
-    <rPh sb="70" eb="71">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="83" eb="84">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="85" eb="86">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="98" eb="100">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="101" eb="102">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="103" eb="105">
-      <t>タントウ</t>
-    </rPh>
-    <rPh sb="112" eb="113">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="114" eb="115">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="118" eb="120">
-      <t>カコウ</t>
-    </rPh>
-    <rPh sb="120" eb="122">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="128" eb="130">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="132" eb="134">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="137" eb="138">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="138" eb="140">
-      <t>ウンヨウ</t>
-    </rPh>
-    <rPh sb="151" eb="153">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="158" eb="160">
-      <t>カンゼン</t>
-    </rPh>
-    <rPh sb="160" eb="162">
-      <t>シンキ</t>
-    </rPh>
-    <rPh sb="164" eb="166">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="166" eb="168">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="169" eb="170">
-      <t>スク</t>
-    </rPh>
-    <rPh sb="173" eb="175">
-      <t>キゾン</t>
-    </rPh>
-    <rPh sb="175" eb="177">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="178" eb="180">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="182" eb="184">
-      <t>カンスウ</t>
-    </rPh>
-    <rPh sb="185" eb="187">
-      <t>リュウヨウ</t>
-    </rPh>
-    <rPh sb="189" eb="191">
-      <t>キノウ</t>
-    </rPh>
-    <rPh sb="191" eb="193">
-      <t>カクチョウ</t>
-    </rPh>
-    <rPh sb="200" eb="202">
-      <t>ギョウム</t>
-    </rPh>
-    <rPh sb="203" eb="205">
-      <t>チュウシン</t>
-    </rPh>
-    <rPh sb="211" eb="212">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="213" eb="215">
-      <t>ケイコク</t>
-    </rPh>
-    <rPh sb="216" eb="217">
-      <t>スベ</t>
-    </rPh>
-    <rPh sb="218" eb="220">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="222" eb="224">
-      <t>サホウ</t>
-    </rPh>
-    <rPh sb="225" eb="227">
-      <t>ココロエ</t>
-    </rPh>
-    <rPh sb="282" eb="283">
-      <t>ホカ</t>
-    </rPh>
-    <rPh sb="287" eb="289">
-      <t>タントウ</t>
-    </rPh>
-    <rPh sb="297" eb="299">
-      <t>ゲンゴ</t>
-    </rPh>
-    <rPh sb="303" eb="305">
-      <t>レンケイ</t>
-    </rPh>
-    <rPh sb="305" eb="307">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="320" eb="321">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="325" eb="327">
-      <t>ジシャ</t>
-    </rPh>
-    <rPh sb="327" eb="331">
-      <t>タイキキカン</t>
-    </rPh>
-    <rPh sb="333" eb="335">
-      <t>シュウカン</t>
-    </rPh>
-    <rPh sb="335" eb="337">
-      <t>テイド</t>
-    </rPh>
-    <rPh sb="342" eb="343">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="344" eb="345">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="346" eb="348">
-      <t>ケイケン</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>・除外拡張子などを考慮した関数の呼び出し元や環境変数等のGrep経験
@@ -8171,7 +7408,7 @@
     <rPh sb="81" eb="83">
       <t>ホゾン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・Httpレスポンスヘッダの改行コードの調査・改修（RFC9112準拠対応）
@@ -8246,7 +7483,7 @@
     <rPh sb="246" eb="248">
       <t>ツイカ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>以下の内容を理解しました。
@@ -8295,14 +7532,14 @@
     <rPh sb="211" eb="212">
       <t>ツカ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>　　　HTML Lv1合格レポート</t>
     <rPh sb="11" eb="13">
       <t>ゴウカク</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>合格資格や学習状況などの画面証跡</t>
@@ -8318,14 +7555,14 @@
     <rPh sb="14" eb="16">
       <t>ショウセキ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t xml:space="preserve">  JavaGold資格 PDF</t>
     <rPh sb="10" eb="12">
       <t>シカク</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t xml:space="preserve"> SQL系の基礎知識証明</t>
@@ -8341,7 +7578,7 @@
     <rPh sb="10" eb="12">
       <t>ショウメイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t xml:space="preserve"> ネットワーク系の基礎知識証明</t>
@@ -8357,11 +7594,11 @@
     <rPh sb="13" eb="15">
       <t>ショウメイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t xml:space="preserve"> 応用情報</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t xml:space="preserve"> 午前 勉強状況</t>
@@ -8374,11 +7611,11 @@
     <rPh sb="6" eb="8">
       <t>ジョウキョウ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>午後 勉強状況</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t xml:space="preserve">  購入したKindle本</t>
@@ -8388,7 +7625,7 @@
     <rPh sb="12" eb="13">
       <t>ホン</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>・ファイル名検索バッチの新規作成(約150ステップ)【ポートフォリオ掲載作品】
@@ -8412,7 +7649,7 @@
     <rPh sb="78" eb="79">
       <t>ヤク</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・勤務表自動入力マクロ【ポートフォリオ掲載作品】
@@ -8475,7 +7712,7 @@
     <rPh sb="98" eb="100">
       <t>ジッソウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・端末ステータス確認スクリプト【モックアップのみ掲載】(約50×8ステップ)
@@ -8511,7 +7748,7 @@
     <rPh sb="86" eb="89">
       <t>ジタクヨウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・最終リクエストのログ抽出shの新規作成(約50ステップ)
@@ -8551,11 +7788,11 @@
     <rPh sb="111" eb="113">
       <t>サクセイ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>https://ma.educo-j.or.jp/h/EID900059008/ngxv3stpqf</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>・試験で使用するテーブルやレコードの作成などの経験
@@ -8578,11 +7815,7 @@
     <rPh sb="48" eb="50">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>・Send Later（指定時刻メール送信機能）の使用経験</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>レコードの更新が他開発者のタスクに影響を与えることを理解しているので、
@@ -8627,11 +7860,11 @@
     <rPh sb="82" eb="83">
       <t>レイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・営業、非営業日を考慮したジョブの即時実行、保留の経験(運用テスト)</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・JSON(XML)送信ツールとして単発的な使い方での使用経験あり
@@ -8679,7 +7912,7 @@
     <rPh sb="69" eb="71">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・レンタルサーバへの接続経験
@@ -8696,34 +7929,7 @@
     <rPh sb="43" eb="45">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>・フォルダ単位での環境資源の比較経験
-・同期ポイントの使用
-・保存時の自動バックアップ設定経験</t>
-    <rPh sb="5" eb="7">
-      <t>タンイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シゲン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ヒカク</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ケイケン</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ドウキ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・システムの本番リリース直後の約１か月、夜間監視の経験
@@ -8755,7 +7961,7 @@
     <rPh sb="40" eb="42">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・システム障害調査経験あり。(Loosely-Coupled IEや398日ルール等)
@@ -8772,7 +7978,7 @@
     <rPh sb="41" eb="42">
       <t>トウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・SQLワークシートの使用
@@ -8783,14 +7989,14 @@
     <rPh sb="24" eb="26">
       <t>シヨウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>DB GUIツール</t>
   </si>
   <si>
     <t>phpMyAdmin</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・環境構築の経験
@@ -8813,15 +8019,15 @@
     <rPh sb="20" eb="22">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>MySQL Workbench</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・環境構築の経験</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・チケットの作成経験や小規模な仕様の変更管理等</t>
@@ -8846,7 +8052,7 @@
     <rPh sb="22" eb="23">
       <t>トウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・featureブランチの作成
@@ -8855,7 +8061,7 @@
 ・Git status
 ・Git commit(Amend)
 ・Git push(Force)</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・ログ監視専用ttlファイル作成(TeraTermマクロ)
@@ -8916,7 +8122,7 @@
     <rPh sb="92" eb="94">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・アプリログ時刻補正 秀丸マクロの作成経験
@@ -8977,7 +8183,7 @@
     <rPh sb="75" eb="77">
       <t>セッテイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・検索フォルダを使用した開発アプリのエラーメッセージの抽出経験
@@ -9000,7 +8206,7 @@
     <rPh sb="50" eb="52">
       <t>シヨウ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>時限ファイルの使用経験</t>
@@ -9013,7 +8219,7 @@
     <rPh sb="9" eb="11">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>サードパーティ製
@@ -9024,7 +8230,7 @@
     <rPh sb="12" eb="13">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・複数人への送信の際、To、CCを明示的に記載して送信した経験
@@ -9059,32 +8265,7 @@
     <rPh sb="43" eb="45">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
-  </si>
-  <si>
-    <t>・画面共有を使用した制作物の説明経験</t>
-    <rPh sb="1" eb="3">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>キョウユウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ブツ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ケイケン</t>
-    </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・マルウェア対策のためマクロ自動実行ブロックのまま閲覧する習慣あり
@@ -9104,15 +8285,15 @@
     <rPh sb="62" eb="64">
       <t>シュウカン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>WebLogic</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>サーバ</t>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>・手順書を参考としたコマンドによる再起動経験</t>
@@ -9128,19 +8309,1010 @@
     <rPh sb="20" eb="22">
       <t>ケイケン</t>
     </rPh>
-    <phoneticPr fontId="15"/>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>Slack</t>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>秀丸</t>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>Oracle Master Silver SQL 2019</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>トランザクションや権限、データディクショナリビューなどについて理解を深めました。</t>
+    <rPh sb="9" eb="11">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>約80点</t>
+    <rPh sb="0" eb="1">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テン</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>4か月</t>
+    <rPh sb="2" eb="3">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>オラクルマスター教科書 Silver SQL</t>
+    <rPh sb="8" eb="11">
+      <t>キョウカショ</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>以下のことを理解しました。
+・Oracle独自構文とANSI標準構文の違い
+・DML、DCL、DDLの自動コミットタイミングの違い
+・オブジェクト権限とシステム権限の違い
+・通常ロールとPublicロールの違い
+・SQL句の実行順序
+・算術演算子のNULLの扱いとNVL等によるNULLの回避方法
+・索引のメンテナンスタイミング
+・正常終了、異常終了時のコミット／ロールバックの違い</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ドクジ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>コウブン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヒョウジュン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>コウブン</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="103" eb="104">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>サンジュツ</t>
+    </rPh>
+    <rPh sb="120" eb="123">
+      <t>エンザンシ</t>
+    </rPh>
+    <rPh sb="129" eb="130">
+      <t>アツカ</t>
+    </rPh>
+    <rPh sb="135" eb="136">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="144" eb="146">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="146" eb="148">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="150" eb="152">
+      <t>サクイン</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>趣味はネット将棋です。アマ三段を取得した実績があります。</t>
+    <rPh sb="0" eb="2">
+      <t>シュミ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショウギ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>サン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ダン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジッセキ</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>https://catalog-education.oracle.com/pls/certview/sharebadge?id=FB80C7C559C10DA4A543B0C59CEA0021F8CABD3E716F3C5B49479F57433AA3C4</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>ITエンジニアとして思考の土台となっている実感があります。</t>
+    <rPh sb="10" eb="12">
+      <t>シコウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ドダイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジッカン</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>・メール送信後の送信トレイの確認習慣あり
+・Send Later（指定時刻メール送信機能）の使用経験あり</t>
+    <rPh sb="4" eb="6">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュウカン</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>Cisco Certified Network Associate</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>パケット構造やルーティングなどについて理解を深めました。</t>
+    <rPh sb="4" eb="6">
+      <t>コウゾウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>2か月</t>
+    <rPh sb="2" eb="3">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>不明</t>
+    <rPh sb="0" eb="2">
+      <t>フメイ</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>https://www.credly.com/users/username.a62dba10/edit/badges/credly</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>・フォルダ単位での環境資源の比較経験
+・同期ポイントの使用
+・保存時の自動バックアップ設定経験
+・HTMLレポート証跡の作成経験</t>
+    <rPh sb="5" eb="7">
+      <t>タンイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シゲン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ドウキ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ショウセキ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ほぼ解析専門。
+デスクトップアプリ(MFC)のエディットコントロールの罫線が表示されなくなる画面描画障害があっため、調査の経験あり。(1か月程度)
+ログ取得関数をコンストラクタ～デストラクタなどの一連の処理の間に複数呼び出し宣言を行い、ログから障害を調査した経験あり(1件)
+</t>
+    <rPh sb="2" eb="4">
+      <t>カイセキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センモン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ケイセン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ビョウガ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ショウガイ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>ゲツ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>テイド</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>イチレン</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="104" eb="105">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="122" eb="124">
+      <t>ショウガイ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="129" eb="131">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="135" eb="136">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>標準ライブラリでのプログラミング経験が豊富。
+メモリ領域初期化漏れや他変数の領域破壊などを考慮した実装経験あり。
+別プロセスやタブレットから呼び出されるインターフェースの修正を主に担当し、パラメータに応じた呼出ロジックの修正経験あり。
+既存システムへの機能追加が主のため、デグレ防止を意識した実装の経験が豊富。
+ビルド時の警告やエラーに全て対応する作法を習得済み。
+構造体のバイトアライメントルールによるパディングの発生を理解しております。
+&lt;注意&gt;
+1)組み込み系の経験なし
+2)VisualStudioを使用していたのでGCCの使用経験なし
+3)DBアクセスは他チームが担当していたので、C言語ではDB連携経験なし
+※ただしPRO*Cに関しては、自社待期期間で１週間程度のコードの読み取り経験あり。</t>
+    <rPh sb="16" eb="18">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ホウフ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>リョウイキ</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>ショキカ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>リョウイキ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ハカイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>コウリョ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>タントウ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="101" eb="102">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>ヨビダ</t>
+    </rPh>
+    <rPh sb="108" eb="110">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>キゾン</t>
+    </rPh>
+    <rPh sb="126" eb="128">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="128" eb="130">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="131" eb="132">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="139" eb="141">
+      <t>ボウシ</t>
+    </rPh>
+    <rPh sb="142" eb="144">
+      <t>イシキ</t>
+    </rPh>
+    <rPh sb="146" eb="148">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="149" eb="151">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="152" eb="154">
+      <t>ホウフ</t>
+    </rPh>
+    <rPh sb="183" eb="186">
+      <t>コウゾウタイ</t>
+    </rPh>
+    <rPh sb="208" eb="210">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="211" eb="213">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="230" eb="231">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="232" eb="233">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="234" eb="235">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="236" eb="238">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="268" eb="270">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="270" eb="272">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="284" eb="285">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="289" eb="291">
+      <t>タントウ</t>
+    </rPh>
+    <rPh sb="299" eb="301">
+      <t>ゲンゴ</t>
+    </rPh>
+    <rPh sb="305" eb="307">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="307" eb="309">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="322" eb="323">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="327" eb="329">
+      <t>ジシャ</t>
+    </rPh>
+    <rPh sb="329" eb="333">
+      <t>タイキキカン</t>
+    </rPh>
+    <rPh sb="335" eb="337">
+      <t>シュウカン</t>
+    </rPh>
+    <rPh sb="337" eb="339">
+      <t>テイド</t>
+    </rPh>
+    <rPh sb="344" eb="345">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="346" eb="347">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="348" eb="350">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>・外部ライブラリを使用しないJSONデータの作成や構文チェックおよび、制御文字のエスケープ対応(1件)
+・外部ライブラリを使用しないXMLデータの作成や構文チェック、実体参照文字のエスケープ対応
+・パック10進数からゾーン10進数へのシフト演算を使用した変換処理(1件)
+・固定長電文の処理結果ビットに応じたエラーメッセージ処理の追加
+・他プロセスの変更したグローバル変数などと連携した処理の実装
+・画面項目の変更に伴う入力チェック処理の追加
+・関数ポインタを使用した動的関数呼び出しの実装(1件のみ)</t>
+    <rPh sb="1" eb="3">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>コウブン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>コウブン</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>ジッタイ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>シンスウ</t>
+    </rPh>
+    <rPh sb="113" eb="115">
+      <t>シンスウ</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>エンザン</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="137" eb="140">
+      <t>コテイチョウ</t>
+    </rPh>
+    <rPh sb="140" eb="142">
+      <t>デンブン</t>
+    </rPh>
+    <rPh sb="143" eb="145">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="145" eb="147">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="156" eb="157">
+      <t>トモナ</t>
+    </rPh>
+    <rPh sb="162" eb="164">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="169" eb="171">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="173" eb="174">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="179" eb="181">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="188" eb="190">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="193" eb="195">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="200" eb="202">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="212" eb="213">
+      <t>トモナ</t>
+    </rPh>
+    <rPh sb="214" eb="216">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="223" eb="225">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="227" eb="229">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="234" eb="236">
+      <t>ドウテキ</t>
+    </rPh>
+    <rPh sb="236" eb="238">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="238" eb="239">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="240" eb="241">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="243" eb="245">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="247" eb="249">
+      <t>ジッソウケン</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>以下の内容を理解しました。
+・C言語には二次元配列はなく、配列の配列しかないこと。
+・アドレスが同じでも型が違うと警告の原因になること。
+・実引数で渡した配列は、内部的には一番外側の配列がポインタに変換されること。
+・long型等が処理系のレジスタによって、サイズが変わること。
+・共用体メンバが同じアドレスを参照していること。
+・構造体自体へのconstとメンバポインタ変数へのconstの範囲の違い
+・Javaの配列はヒープだが、Cの配列はスタックかヒープに作成できるということ</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ゲンゴ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ニ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジゲン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ケイコク</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>ゲンインカタ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ジツ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>ワタ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>イチバン</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>ソトガワ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="113" eb="114">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="114" eb="115">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="116" eb="119">
+      <t>ショリケイ</t>
+    </rPh>
+    <rPh sb="133" eb="134">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="141" eb="143">
+      <t>キョウヨウ</t>
+    </rPh>
+    <rPh sb="143" eb="144">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="148" eb="149">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="155" eb="157">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="166" eb="169">
+      <t>コウゾウタイ</t>
+    </rPh>
+    <rPh sb="169" eb="171">
+      <t>ジタイ</t>
+    </rPh>
+    <rPh sb="186" eb="188">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="196" eb="198">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="199" eb="200">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="208" eb="210">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="219" eb="221">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="231" eb="233">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>Docker Desktop</t>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>・本番環境へのファイルのアップロード経験あり
+・アップロード時の確認ダイアログの設定やサイズや更新日時の確認
+・テキストモードやバイナリモードを考慮したアップロード経験
+・セッション、共有等のお気に入りの設定</t>
+    <rPh sb="72" eb="74">
+      <t>コウリョ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="94" eb="95">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="97" eb="98">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="102" eb="104">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>Oracle Virtual Box</t>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>・CentOS6/7のインストール経験
+・メモリ割り当ての設定経験
+・GUIなしでの起動経験</t>
+    <rPh sb="17" eb="19">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>キドウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>・Web会議での進捗報告の経験
+・画面共有を使用した制作物の説明経験
+・Copilotの利用</t>
+    <rPh sb="4" eb="6">
+      <t>カイギ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シンチョク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ホウコク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ブツ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>リヨウ</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>ログイン時のメールアドレス入力規則チェックなど、HTTPリクエスト、レスポンス時の処理の実装経験があります。
+開発経験の一例を以下に記載します。
+1)Linuxデーモン(常駐システム)のソケット間通信電文の返却処理の修正経験
+2)人事イベント管理Webアプリの給与管理画面ロジック修正
+3)入学受験アドバイス用チャットWebアプリの問い合わせフォーム画面修正
+4)宿泊予約Androidアプリのログイン規則、予約ロジック修正</t>
+    <rPh sb="4" eb="5">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キソク</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>イチレイ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>ジョウチュウ</t>
+    </rPh>
+    <rPh sb="97" eb="98">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="100" eb="102">
+      <t>デンブン</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>ヘンキャク</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="108" eb="110">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>ジンジ</t>
+    </rPh>
+    <rPh sb="121" eb="123">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="130" eb="132">
+      <t>キュウヨ</t>
+    </rPh>
+    <rPh sb="132" eb="134">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="140" eb="142">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="145" eb="147">
+      <t>ニュウガク</t>
+    </rPh>
+    <rPh sb="147" eb="149">
+      <t>ジュケン</t>
+    </rPh>
+    <rPh sb="154" eb="155">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="166" eb="167">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="168" eb="169">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="175" eb="177">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="177" eb="179">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="194" eb="196">
+      <t>シュクハク</t>
+    </rPh>
+    <rPh sb="201" eb="203">
+      <t>キソク</t>
+    </rPh>
+    <rPh sb="204" eb="206">
+      <t>ヨヤク</t>
+    </rPh>
+    <rPh sb="210" eb="212">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -9315,7 +9487,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9325,6 +9497,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89996032593768116"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -9449,92 +9627,101 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1">
@@ -9543,31 +9730,25 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
@@ -9576,28 +9757,49 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="18" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9607,7 +9809,15 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{881AF4ED-5A7A-40C7-919C-B6B36BAD065A}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -10659,7 +10869,7 @@
     </row>
     <row r="3" spans="2:10">
       <c r="B3" s="30" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="2:10">
@@ -10669,7 +10879,7 @@
     </row>
     <row r="5" spans="2:10">
       <c r="B5" s="31" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="19.5" thickBot="1"/>
@@ -10833,14 +11043,14 @@
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="10" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="14"/>
+  <phoneticPr fontId="16"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -10864,51 +11074,51 @@
   <sheetData>
     <row r="2" spans="1:10" ht="24">
       <c r="A2" s="1" t="s">
-        <v>458</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="39" t="s">
-        <v>459</v>
-      </c>
-      <c r="J4" s="39" t="s">
-        <v>457</v>
+      <c r="A4" s="37" t="s">
+        <v>440</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="38" t="s">
-        <v>451</v>
+      <c r="A16" s="36" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="39" t="s">
-        <v>462</v>
+      <c r="A29" s="37" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="39" t="s">
-        <v>463</v>
-      </c>
-      <c r="H30" s="39" t="s">
-        <v>464</v>
+      <c r="A30" s="37" t="s">
+        <v>444</v>
+      </c>
+      <c r="H30" s="37" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="39" t="s">
-        <v>460</v>
+      <c r="A54" s="37" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="B59" s="38"/>
+      <c r="B59" s="36"/>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="39" t="s">
-        <v>461</v>
+      <c r="A81" s="37" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="39" t="s">
-        <v>465</v>
+      <c r="A109" s="37" t="s">
+        <v>446</v>
       </c>
       <c r="B109" s="25"/>
       <c r="C109" s="25"/>
@@ -10948,7 +11158,7 @@
       <c r="C129" s="26"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="14"/>
+  <phoneticPr fontId="16"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -10967,7 +11177,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="45.375" style="2" customWidth="1"/>
@@ -11017,110 +11227,158 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="57" thickTop="1">
+    <row r="5" spans="1:7" ht="75.75" thickTop="1">
       <c r="A5" s="13" t="s">
-        <v>33</v>
+        <v>489</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>470</v>
+        <v>490</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>493</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>35</v>
+        <v>492</v>
       </c>
       <c r="E5" s="16">
         <v>1</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>36</v>
+        <v>491</v>
       </c>
       <c r="G5" s="15">
-        <v>45962</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="73.5" customHeight="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="150">
       <c r="A6" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>37</v>
+        <v>479</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>486</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>38</v>
+        <v>481</v>
       </c>
       <c r="E6" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="19">
-        <v>45436</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="43.5" customHeight="1">
+        <v>482</v>
+      </c>
+      <c r="G6" s="15">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="56.25">
       <c r="A7" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>41</v>
+        <v>33</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>451</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E7" s="16">
         <v>1</v>
       </c>
       <c r="F7" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="15">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="73.5" customHeight="1">
+      <c r="A8" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="16">
+        <v>1</v>
+      </c>
+      <c r="F8" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G8" s="19">
+        <v>45436</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="43.5" customHeight="1">
+      <c r="A9" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="16">
+        <v>1</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="19">
         <v>45233</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="56.25">
-      <c r="A8" s="20" t="s">
+    <row r="10" spans="1:7" ht="56.25">
+      <c r="A10" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B10" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="16">
+      <c r="C10" s="20"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16">
         <v>3</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F10" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G10" s="19">
         <v>44969</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="10"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="10"/>
+    <row r="11" spans="1:7">
+      <c r="A11" s="10"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:G4" xr:uid="{21FFF12F-B684-4050-9B34-306B03FBB89B}"/>
-  <phoneticPr fontId="14"/>
+  <phoneticPr fontId="16"/>
   <hyperlinks>
-    <hyperlink ref="C6" r:id="rId1" xr:uid="{27A4E6AC-D535-4917-9A75-E6F6C321D2F1}"/>
-    <hyperlink ref="C7" r:id="rId2" xr:uid="{30F668CC-9B59-46FD-807B-98AF09EED418}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{32A79625-C4AE-442D-8202-0214BE5E6252}"/>
+    <hyperlink ref="C8" r:id="rId1" xr:uid="{27A4E6AC-D535-4917-9A75-E6F6C321D2F1}"/>
+    <hyperlink ref="C9" r:id="rId2" xr:uid="{30F668CC-9B59-46FD-807B-98AF09EED418}"/>
+    <hyperlink ref="C7" r:id="rId3" xr:uid="{32A79625-C4AE-442D-8202-0214BE5E6252}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{F3BA62BD-6C63-44AA-BADB-8F3EABDAB5FB}"/>
+    <hyperlink ref="C5" r:id="rId5" xr:uid="{303CA509-0E9F-47EE-8AB5-A1AB43737766}"/>
   </hyperlinks>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="92" fitToHeight="0" orientation="landscape" r:id="rId4"/>
+  <pageSetup paperSize="9" scale="92" fitToHeight="0" orientation="landscape" r:id="rId6"/>
   <headerFooter>
     <oddFooter>&amp;P / &amp;N ページ</oddFooter>
   </headerFooter>
@@ -11160,7 +11418,7 @@
         <v>48</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>49</v>
@@ -11170,7 +11428,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="19.5" customHeight="1" thickTop="1">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="55" t="s">
         <v>51</v>
       </c>
       <c r="B5" s="16" t="s">
@@ -11187,7 +11445,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="45"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="16" t="s">
         <v>55</v>
       </c>
@@ -11202,7 +11460,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="45"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="16" t="s">
         <v>56</v>
       </c>
@@ -11217,7 +11475,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="45"/>
+      <c r="A8" s="53"/>
       <c r="B8" s="16" t="s">
         <v>58</v>
       </c>
@@ -11232,8 +11490,8 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="45"/>
-      <c r="B9" s="41" t="s">
+      <c r="A9" s="53"/>
+      <c r="B9" s="49" t="s">
         <v>60</v>
       </c>
       <c r="C9" s="16" t="s">
@@ -11247,90 +11505,90 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="56.25">
-      <c r="A10" s="45"/>
-      <c r="B10" s="42"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="50"/>
       <c r="C10" s="16" t="s">
         <v>63</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="E10" s="21">
         <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="45"/>
-      <c r="B11" s="43"/>
+      <c r="A11" s="53"/>
+      <c r="B11" s="51"/>
       <c r="C11" s="16" t="s">
         <v>64</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="E11" s="21">
         <v>0.2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="45"/>
-      <c r="B12" s="41" t="s">
+      <c r="A12" s="53"/>
+      <c r="B12" s="49" t="s">
         <v>65</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>66</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E12" s="21">
         <v>0.9</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="45"/>
-      <c r="B13" s="43"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="51"/>
       <c r="C13" s="16" t="s">
         <v>67</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="E13" s="21">
         <v>0.9</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="112.5">
-      <c r="A14" s="45"/>
-      <c r="B14" s="44" t="s">
-        <v>375</v>
+      <c r="A14" s="53"/>
+      <c r="B14" s="52" t="s">
+        <v>369</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E14" s="21">
         <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="56.25">
-      <c r="A15" s="45"/>
-      <c r="B15" s="45"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="53"/>
       <c r="C15" s="16" t="s">
         <v>69</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E15" s="21">
         <v>0.8</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="57" customHeight="1">
-      <c r="A16" s="45"/>
-      <c r="B16" s="45"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="53"/>
       <c r="C16" s="16" t="s">
         <v>70</v>
       </c>
@@ -11342,33 +11600,33 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="168.75">
-      <c r="A17" s="45"/>
-      <c r="B17" s="45"/>
+      <c r="A17" s="53"/>
+      <c r="B17" s="53"/>
       <c r="C17" s="16" t="s">
         <v>72</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E17" s="21">
         <v>0.9</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="57" customHeight="1">
-      <c r="A18" s="45"/>
-      <c r="B18" s="46"/>
+      <c r="A18" s="53"/>
+      <c r="B18" s="54"/>
       <c r="C18" s="16" t="s">
         <v>73</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E18" s="21">
         <v>0.8</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="45"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="22" t="s">
         <v>74</v>
       </c>
@@ -11383,7 +11641,7 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="45"/>
+      <c r="A20" s="53"/>
       <c r="B20" s="22" t="s">
         <v>76</v>
       </c>
@@ -11398,7 +11656,7 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="46"/>
+      <c r="A21" s="54"/>
       <c r="B21" s="22" t="s">
         <v>79</v>
       </c>
@@ -11461,7 +11719,7 @@
     <mergeCell ref="B14:B18"/>
     <mergeCell ref="A5:A21"/>
   </mergeCells>
-  <phoneticPr fontId="14"/>
+  <phoneticPr fontId="16"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -11478,7 +11736,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="2" width="11.25" style="2" bestFit="1" customWidth="1"/>
@@ -11497,7 +11755,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="27" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B2" s="27"/>
     </row>
@@ -11520,7 +11778,7 @@
         <v>89</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>90</v>
@@ -11532,21 +11790,21 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="225.75" thickTop="1">
+    <row r="5" spans="1:8" ht="282" thickTop="1">
       <c r="A5" s="23" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>92</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>453</v>
+        <v>496</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>385</v>
+        <v>497</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="F5" s="23">
         <v>2026</v>
@@ -11558,21 +11816,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="206.25">
+    <row r="6" spans="1:8" ht="168.75">
       <c r="A6" s="23" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>93</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>417</v>
+        <v>504</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="F6" s="23">
         <v>2026</v>
@@ -11584,33 +11842,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="93.75">
-      <c r="A7" s="23" t="s">
-        <v>439</v>
-      </c>
-      <c r="B7" s="23" t="s">
+    <row r="7" spans="1:8" ht="112.5">
+      <c r="A7" s="41" t="s">
+        <v>423</v>
+      </c>
+      <c r="B7" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>345</v>
-      </c>
-      <c r="F7" s="23" t="s">
+      <c r="C7" s="43" t="s">
+        <v>495</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>313</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>340</v>
+      </c>
+      <c r="F7" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="44">
         <v>0.1</v>
       </c>
-      <c r="H7" s="23"/>
+      <c r="H7" s="41"/>
     </row>
     <row r="8" spans="1:8" ht="56.25">
       <c r="A8" s="16" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>98</v>
@@ -11619,7 +11877,7 @@
         <v>99</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="E8" s="16"/>
       <c r="F8" s="16">
@@ -11632,16 +11890,16 @@
     </row>
     <row r="9" spans="1:8" ht="75">
       <c r="A9" s="23" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="23" t="s">
@@ -11654,7 +11912,7 @@
     </row>
     <row r="10" spans="1:8" ht="56.25">
       <c r="A10" s="16" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>94</v>
@@ -11663,10 +11921,10 @@
         <v>95</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F10" s="23">
         <v>2026</v>
@@ -11678,7 +11936,7 @@
     </row>
     <row r="11" spans="1:8" ht="75">
       <c r="A11" s="16" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>96</v>
@@ -11687,7 +11945,7 @@
         <v>97</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="23">
@@ -11700,7 +11958,7 @@
     </row>
     <row r="12" spans="1:8" ht="75">
       <c r="A12" s="23" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="B12" s="23" t="s">
         <v>101</v>
@@ -11712,7 +11970,7 @@
         <v>103</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="F12" s="23">
         <v>2026</v>
@@ -11724,7 +11982,7 @@
     </row>
     <row r="13" spans="1:8" ht="131.25">
       <c r="A13" s="23" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="B13" s="23" t="s">
         <v>104</v>
@@ -11733,10 +11991,10 @@
         <v>105</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F13" s="23">
         <v>2018</v>
@@ -11747,128 +12005,87 @@
       <c r="H13" s="23"/>
     </row>
     <row r="14" spans="1:8" ht="75">
-      <c r="A14" s="16" t="s">
-        <v>441</v>
-      </c>
-      <c r="B14" s="16" t="s">
+      <c r="A14" s="45" t="s">
+        <v>425</v>
+      </c>
+      <c r="B14" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23">
+      <c r="C14" s="43" t="s">
+        <v>314</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>316</v>
+      </c>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41">
         <v>2022</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="44">
         <v>0.2</v>
       </c>
-      <c r="H14" s="23"/>
-    </row>
-    <row r="15" spans="1:8" ht="37.5">
+      <c r="H14" s="41"/>
+    </row>
+    <row r="15" spans="1:8" ht="112.5">
       <c r="A15" s="23" t="s">
-        <v>444</v>
+        <v>422</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>420</v>
+        <v>100</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>418</v>
+        <v>353</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>423</v>
-      </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23" t="s">
-        <v>77</v>
+        <v>373</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="F15" s="23">
+        <v>2026</v>
       </c>
       <c r="G15" s="24">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H15" s="23"/>
     </row>
-    <row r="16" spans="1:8" ht="112.5">
-      <c r="A16" s="23" t="s">
-        <v>438</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="F16" s="23">
-        <v>2026</v>
-      </c>
-      <c r="G16" s="24">
-        <v>0.7</v>
-      </c>
-      <c r="H16" s="23"/>
-    </row>
-    <row r="17" spans="1:8" ht="56.25">
-      <c r="A17" s="23" t="s">
-        <v>438</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>421</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>424</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>419</v>
-      </c>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="H17" s="23"/>
-    </row>
-    <row r="19" spans="1:8">
+    <row r="17" spans="1:1">
+      <c r="A17" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="2" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:H4" xr:uid="{7CDA57F4-69DB-4015-855F-7F84EEE34219}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:H17">
-    <sortCondition ref="A8:A17"/>
-    <sortCondition descending="1" ref="G8:G17"/>
-    <sortCondition descending="1" ref="F8:F17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:H15">
+    <sortCondition ref="A8:A15"/>
+    <sortCondition descending="1" ref="G8:G15"/>
+    <sortCondition descending="1" ref="F8:F15"/>
   </sortState>
-  <phoneticPr fontId="14"/>
+  <phoneticPr fontId="16"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;P / &amp;N ページ</oddFooter>
   </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="15" max="7" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -11877,7 +12094,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="15.125" style="2" bestFit="1" customWidth="1"/>
@@ -11912,7 +12129,7 @@
         <v>110</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>111</v>
@@ -11924,21 +12141,19 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="38.25" thickTop="1">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:6" ht="19.5" thickTop="1">
+      <c r="A5" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16">
+      <c r="C5" s="42"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45">
         <v>2018</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="46">
         <v>0.1</v>
       </c>
     </row>
@@ -11966,7 +12181,7 @@
         <v>123</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>115</v>
@@ -12004,7 +12219,7 @@
         <v>117</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="23">
@@ -12030,7 +12245,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" ht="150">
       <c r="A11" s="23" t="s">
         <v>113</v>
       </c>
@@ -12038,33 +12253,33 @@
         <v>114</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>365</v>
+        <v>498</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>115</v>
       </c>
       <c r="E11" s="23">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="37.5">
+      <c r="A12" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41">
         <v>2023</v>
       </c>
-      <c r="F11" s="24">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="37.5">
-      <c r="A12" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23">
-        <v>2023</v>
-      </c>
-      <c r="F12" s="24">
+      <c r="F12" s="44">
         <v>0</v>
       </c>
     </row>
@@ -12076,7 +12291,7 @@
         <v>128</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D13" s="23" t="s">
         <v>129</v>
@@ -12096,7 +12311,7 @@
         <v>131</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>129</v>
@@ -12116,7 +12331,7 @@
         <v>121</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23">
@@ -12134,7 +12349,7 @@
         <v>125</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="23">
@@ -12152,7 +12367,7 @@
         <v>116</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="23">
@@ -12170,7 +12385,7 @@
         <v>130</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="23">
@@ -12185,10 +12400,10 @@
         <v>113</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="23">
@@ -12199,38 +12414,38 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>429</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>432</v>
-      </c>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23">
+      <c r="B20" s="43" t="s">
+        <v>414</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>417</v>
+      </c>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41">
         <v>2026</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="44">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="20" t="s">
-        <v>430</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>431</v>
-      </c>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23">
+      <c r="B21" s="43" t="s">
+        <v>415</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>416</v>
+      </c>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41">
         <v>2026</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="44">
         <v>0.1</v>
       </c>
     </row>
@@ -12242,7 +12457,7 @@
         <v>141</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="23">
@@ -12292,7 +12507,7 @@
         <v>139</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>115</v>
@@ -12332,7 +12547,7 @@
         <v>138</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D27" s="23" t="s">
         <v>115</v>
@@ -12390,7 +12605,7 @@
         <v>137</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D30" s="23"/>
       <c r="E30" s="23">
@@ -12408,7 +12623,7 @@
         <v>140</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D31" s="23" t="s">
         <v>129</v>
@@ -12446,7 +12661,7 @@
         <v>143</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>129</v>
@@ -12476,87 +12691,107 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="93.75">
+    <row r="35" spans="1:6" ht="168.75">
       <c r="A35" s="23" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>152</v>
+        <v>483</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>153</v>
+        <v>484</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="E35" s="23">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="F35" s="24">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="37.5">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="93.75">
       <c r="A36" s="23" t="s">
         <v>151</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="23"/>
+        <v>152</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>115</v>
+      </c>
       <c r="E36" s="23">
         <v>2018</v>
       </c>
       <c r="F36" s="24">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="56.25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="37.5">
       <c r="A37" s="23" t="s">
         <v>151</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>354</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C37" s="20"/>
       <c r="D37" s="23"/>
       <c r="E37" s="23">
-        <v>2026</v>
+        <v>2018</v>
       </c>
       <c r="F37" s="24">
         <v>0.05</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="2" t="s">
-        <v>83</v>
+    <row r="38" spans="1:6" ht="56.25">
+      <c r="A38" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>349</v>
+      </c>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="24">
+        <v>0.05</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="2" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B4:F4" xr:uid="{9AB8815A-545D-43FD-9F73-16180910990E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:F37">
-    <sortCondition ref="A5:A37"/>
-    <sortCondition ref="E5:E37"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:F38">
+    <sortCondition ref="A5:A38"/>
+    <sortCondition ref="E5:E38"/>
   </sortState>
-  <phoneticPr fontId="14"/>
+  <phoneticPr fontId="16"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="77" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -12570,7 +12805,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="20.875" style="2" customWidth="1"/>
@@ -12600,13 +12835,13 @@
     </row>
     <row r="4" spans="1:8" ht="54.75" thickBot="1">
       <c r="A4" s="12" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>157</v>
@@ -12632,7 +12867,7 @@
         <v>160</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16" t="s">
@@ -12656,7 +12891,7 @@
         <v>160</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>161</v>
@@ -12682,7 +12917,7 @@
         <v>164</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>161</v>
@@ -12705,10 +12940,10 @@
         <v>165</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>481</v>
+        <v>460</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>161</v>
@@ -12724,7 +12959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="56.25">
+    <row r="9" spans="1:8" ht="75">
       <c r="A9" s="20" t="s">
         <v>166</v>
       </c>
@@ -12732,7 +12967,7 @@
         <v>167</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>161</v>
@@ -12750,15 +12985,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" ht="56.25">
       <c r="A10" s="20" t="s">
         <v>176</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>161</v>
@@ -12768,7 +13003,7 @@
         <v>2021</v>
       </c>
       <c r="G10" s="21">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H10" s="23">
         <v>2</v>
@@ -12782,7 +13017,7 @@
         <v>169</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>161</v>
@@ -12806,7 +13041,7 @@
         <v>171</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="D12" s="23" t="s">
         <v>161</v>
@@ -12830,7 +13065,7 @@
         <v>171</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="D13" s="23" t="s">
         <v>161</v>
@@ -12854,7 +13089,7 @@
         <v>174</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>161</v>
@@ -12880,7 +13115,7 @@
         <v>174</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>161</v>
@@ -12928,7 +13163,7 @@
         <v>178</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>487</v>
+        <v>466</v>
       </c>
       <c r="D17" s="23" t="s">
         <v>161</v>
@@ -12948,13 +13183,13 @@
     </row>
     <row r="18" spans="1:8" ht="56.25">
       <c r="A18" s="20" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="B18" s="20" t="s">
         <v>178</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="D18" s="23" t="s">
         <v>161</v>
@@ -12980,7 +13215,7 @@
         <v>182</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="D19" s="23" t="s">
         <v>161</v>
@@ -12992,7 +13227,7 @@
         <v>2018</v>
       </c>
       <c r="G19" s="24">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H19" s="23">
         <v>2</v>
@@ -13006,7 +13241,7 @@
         <v>184</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>495</v>
+        <v>473</v>
       </c>
       <c r="D20" s="23" t="s">
         <v>161</v>
@@ -13032,7 +13267,7 @@
         <v>184</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
       <c r="D21" s="23" t="s">
         <v>161</v>
@@ -13058,7 +13293,7 @@
         <v>184</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="D22" s="23" t="s">
         <v>161</v>
@@ -13068,7 +13303,7 @@
         <v>2025</v>
       </c>
       <c r="G22" s="24">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H22" s="23">
         <v>3</v>
@@ -13082,7 +13317,7 @@
         <v>188</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>161</v>
@@ -13108,7 +13343,7 @@
         <v>190</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="D24" s="23" t="s">
         <v>161</v>
@@ -13128,13 +13363,13 @@
     </row>
     <row r="25" spans="1:8" ht="75">
       <c r="A25" s="20" t="s">
-        <v>191</v>
+        <v>478</v>
       </c>
       <c r="B25" s="20" t="s">
         <v>190</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>489</v>
+        <v>468</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>161</v>
@@ -13154,13 +13389,13 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="B26" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>193</v>
-      </c>
       <c r="C26" s="20" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="D26" s="23" t="s">
         <v>161</v>
@@ -13178,15 +13413,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" ht="37.5">
       <c r="A27" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="B27" s="20" t="s">
-        <v>195</v>
-      </c>
       <c r="C27" s="20" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="D27" s="23" t="s">
         <v>161</v>
@@ -13198,7 +13433,7 @@
         <v>2025</v>
       </c>
       <c r="G27" s="24">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H27" s="23">
         <v>3</v>
@@ -13206,13 +13441,13 @@
     </row>
     <row r="28" spans="1:8" ht="37.5">
       <c r="A28" s="20" t="s">
-        <v>482</v>
+        <v>461</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="D28" s="23" t="s">
         <v>161</v>
@@ -13230,13 +13465,13 @@
     </row>
     <row r="29" spans="1:8" ht="37.5">
       <c r="A29" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>471</v>
+        <v>452</v>
       </c>
       <c r="D29" s="23" t="s">
         <v>161</v>
@@ -13252,13 +13487,13 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="20" t="s">
-        <v>484</v>
+        <v>463</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>485</v>
+        <v>464</v>
       </c>
       <c r="D30" s="23" t="s">
         <v>161</v>
@@ -13274,13 +13509,13 @@
     </row>
     <row r="31" spans="1:8" ht="37.5">
       <c r="A31" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>480</v>
+        <v>459</v>
       </c>
       <c r="D31" s="23"/>
       <c r="E31" s="23" t="s">
@@ -13294,15 +13529,15 @@
       </c>
       <c r="H31" s="23"/>
     </row>
-    <row r="32" spans="1:8" ht="56.25">
+    <row r="32" spans="1:8" ht="75">
       <c r="A32" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>434</v>
+        <v>500</v>
       </c>
       <c r="D32" s="23" t="s">
         <v>161</v>
@@ -13312,19 +13547,19 @@
         <v>2018</v>
       </c>
       <c r="G32" s="24">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H32" s="23"/>
     </row>
     <row r="33" spans="1:8" ht="37.5">
       <c r="A33" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="B33" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="B33" s="20" t="s">
-        <v>199</v>
-      </c>
       <c r="C33" s="20" t="s">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="D33" s="23"/>
       <c r="E33" s="23" t="s">
@@ -13340,13 +13575,13 @@
     </row>
     <row r="34" spans="1:8" ht="37.5">
       <c r="A34" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D34" s="23" t="s">
         <v>161</v>
@@ -13364,13 +13599,13 @@
     </row>
     <row r="35" spans="1:8" ht="37.5">
       <c r="A35" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="B35" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="B35" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="C35" s="36" t="s">
-        <v>402</v>
+      <c r="C35" s="47" t="s">
+        <v>394</v>
       </c>
       <c r="D35" s="23" t="s">
         <v>161</v>
@@ -13386,13 +13621,13 @@
     </row>
     <row r="36" spans="1:8" ht="56.25">
       <c r="A36" s="20" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D36" s="23" t="s">
         <v>161</v>
@@ -13402,19 +13637,19 @@
         <v>2020</v>
       </c>
       <c r="G36" s="24">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H36" s="23"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" ht="56.25">
       <c r="A37" s="20" t="s">
-        <v>204</v>
+        <v>501</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>447</v>
+        <v>502</v>
       </c>
       <c r="D37" s="23" t="s">
         <v>161</v>
@@ -13426,19 +13661,19 @@
         <v>2019</v>
       </c>
       <c r="G37" s="24">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="H37" s="23"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="20" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="D38" s="23" t="s">
         <v>161</v>
@@ -13448,19 +13683,19 @@
         <v>2026</v>
       </c>
       <c r="G38" s="24">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H38" s="23"/>
     </row>
     <row r="39" spans="1:8" ht="37.5">
       <c r="A39" s="20" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="D39" s="23" t="s">
         <v>161</v>
@@ -13476,13 +13711,13 @@
     </row>
     <row r="40" spans="1:8" ht="37.5">
       <c r="A40" s="20" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D40" s="23"/>
       <c r="E40" s="23" t="s">
@@ -13498,13 +13733,13 @@
     </row>
     <row r="41" spans="1:8" ht="37.5">
       <c r="A41" s="20" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B41" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="C41" s="20" t="s">
         <v>207</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>209</v>
       </c>
       <c r="D41" s="23" t="s">
         <v>161</v>
@@ -13520,13 +13755,13 @@
     </row>
     <row r="42" spans="1:8" ht="93.75">
       <c r="A42" s="20" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D42" s="23" t="s">
         <v>161</v>
@@ -13542,13 +13777,13 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="20" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="C43" s="36" t="s">
-        <v>397</v>
+        <v>211</v>
+      </c>
+      <c r="C43" s="47" t="s">
+        <v>389</v>
       </c>
       <c r="D43" s="23" t="s">
         <v>161</v>
@@ -13564,13 +13799,13 @@
     </row>
     <row r="44" spans="1:8" ht="37.5">
       <c r="A44" s="20" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>493</v>
+        <v>472</v>
       </c>
       <c r="D44" s="23" t="s">
         <v>161</v>
@@ -13586,13 +13821,13 @@
     </row>
     <row r="45" spans="1:8" ht="37.5">
       <c r="A45" s="20" t="s">
-        <v>216</v>
+        <v>477</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>399</v>
-      </c>
-      <c r="C45" s="37" t="s">
-        <v>217</v>
+        <v>391</v>
+      </c>
+      <c r="C45" s="48" t="s">
+        <v>214</v>
       </c>
       <c r="D45" s="23" t="s">
         <v>161</v>
@@ -13608,10 +13843,10 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="20" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="23" t="s">
@@ -13628,13 +13863,13 @@
     </row>
     <row r="47" spans="1:8" ht="56.25">
       <c r="A47" s="20" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="D47" s="23" t="s">
         <v>161</v>
@@ -13650,13 +13885,13 @@
     </row>
     <row r="48" spans="1:8" ht="37.5">
       <c r="A48" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B48" s="20" t="s">
         <v>174</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="D48" s="23" t="s">
         <v>161</v>
@@ -13672,13 +13907,13 @@
     </row>
     <row r="49" spans="1:8" ht="37.5">
       <c r="A49" s="20" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>161</v>
@@ -13694,13 +13929,13 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="20" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>161</v>
@@ -13716,13 +13951,13 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="20" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B51" s="20" t="s">
         <v>178</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D51" s="23" t="s">
         <v>161</v>
@@ -13740,13 +13975,13 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="20" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>161</v>
@@ -13764,13 +13999,13 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="20" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="D53" s="23" t="s">
         <v>161</v>
@@ -13786,13 +14021,13 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="20" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D54" s="23" t="s">
         <v>161</v>
@@ -13808,13 +14043,13 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="20" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>491</v>
+        <v>470</v>
       </c>
       <c r="D55" s="23" t="s">
         <v>161</v>
@@ -13830,13 +14065,13 @@
     </row>
     <row r="56" spans="1:8" ht="37.5">
       <c r="A56" s="20" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="D56" s="23" t="s">
         <v>161</v>
@@ -13854,13 +14089,13 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="20" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D57" s="23" t="s">
         <v>161</v>
@@ -13878,13 +14113,13 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="20" t="s">
-        <v>496</v>
+        <v>474</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>497</v>
+        <v>475</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="D58" s="23" t="s">
         <v>161</v>
@@ -13899,34 +14134,57 @@
       <c r="H58" s="23"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="2" t="s">
-        <v>83</v>
-      </c>
+      <c r="A59" s="20" t="s">
+        <v>499</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>475</v>
+      </c>
+      <c r="C59" s="20"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="23">
+        <v>2026</v>
+      </c>
+      <c r="G59" s="24">
+        <v>0.05</v>
+      </c>
+      <c r="H59" s="23"/>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="2" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:H4" xr:uid="{21FFF12F-B684-4050-9B34-306B03FBB89B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:H62">
-    <sortCondition ref="H5:H62"/>
-    <sortCondition ref="B5:B62"/>
-    <sortCondition descending="1" ref="G5:G62"/>
-    <sortCondition ref="F5:F62"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:H63">
+    <sortCondition ref="H5:H63"/>
+    <sortCondition ref="B5:B63"/>
+    <sortCondition descending="1" ref="G5:G63"/>
+    <sortCondition ref="F5:F63"/>
   </sortState>
-  <phoneticPr fontId="15"/>
+  <phoneticPr fontId="17"/>
+  <conditionalFormatting sqref="A5:H59">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G5&lt;=40%</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="88" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -13952,7 +14210,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30">
       <c r="A1" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -13962,10 +14220,10 @@
     </row>
     <row r="4" spans="1:4" ht="19.5" thickBot="1">
       <c r="A4" s="12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>50</v>
@@ -13976,10 +14234,10 @@
     </row>
     <row r="5" spans="1:4" ht="19.5" thickTop="1">
       <c r="A5" s="13" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C5" s="21">
         <v>0.7</v>
@@ -13990,10 +14248,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="20" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C6" s="21">
         <v>0.7</v>
@@ -14004,10 +14262,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="20" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C7" s="24">
         <v>0.9</v>
@@ -14018,10 +14276,10 @@
     </row>
     <row r="8" spans="1:4" ht="37.5">
       <c r="A8" s="20" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C8" s="21">
         <v>0.8</v>
@@ -14032,10 +14290,10 @@
     </row>
     <row r="9" spans="1:4" ht="56.25">
       <c r="A9" s="20" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C9" s="21">
         <v>0.4</v>
@@ -14046,10 +14304,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="20" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C10" s="21">
         <v>0.2</v>
@@ -14060,10 +14318,10 @@
     </row>
     <row r="11" spans="1:4" ht="37.5">
       <c r="A11" s="20" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C11" s="21">
         <v>0.1</v>
@@ -14074,10 +14332,10 @@
     </row>
     <row r="12" spans="1:4" ht="56.25">
       <c r="A12" s="13" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C12" s="21">
         <v>0.8</v>
@@ -14088,10 +14346,10 @@
     </row>
     <row r="13" spans="1:4" ht="56.25">
       <c r="A13" s="20" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C13" s="24">
         <v>0.8</v>
@@ -14102,10 +14360,10 @@
     </row>
     <row r="14" spans="1:4" ht="56.25">
       <c r="A14" s="20" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C14" s="24">
         <v>0.8</v>
@@ -14116,10 +14374,10 @@
     </row>
     <row r="15" spans="1:4" ht="37.5">
       <c r="A15" s="20" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C15" s="24">
         <v>0.3</v>
@@ -14130,10 +14388,10 @@
     </row>
     <row r="16" spans="1:4" ht="75">
       <c r="A16" s="13" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C16" s="24">
         <v>0.95</v>
@@ -14142,10 +14400,10 @@
     </row>
     <row r="17" spans="1:4" ht="37.5">
       <c r="A17" s="20" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C17" s="24">
         <v>0.95</v>
@@ -14154,10 +14412,10 @@
     </row>
     <row r="18" spans="1:4" ht="37.5">
       <c r="A18" s="20" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C18" s="24">
         <v>0.8</v>
@@ -14166,10 +14424,10 @@
     </row>
     <row r="19" spans="1:4" ht="56.25">
       <c r="A19" s="20" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C19" s="24">
         <v>0.6</v>
@@ -14178,7 +14436,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="20" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="24">
@@ -14188,7 +14446,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="20" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="24">
@@ -14198,10 +14456,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="20" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C22" s="24">
         <v>0.5</v>
@@ -14210,10 +14468,10 @@
     </row>
     <row r="23" spans="1:4" ht="37.5">
       <c r="A23" s="20" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C23" s="24">
         <v>0.3</v>
@@ -14222,10 +14480,10 @@
     </row>
     <row r="24" spans="1:4" ht="37.5">
       <c r="A24" s="20" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C24" s="24">
         <v>0.3</v>
@@ -14234,10 +14492,10 @@
     </row>
     <row r="25" spans="1:4" ht="75">
       <c r="A25" s="20" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C25" s="24">
         <v>0.3</v>
@@ -14246,10 +14504,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="20" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C26" s="24">
         <v>0.1</v>
@@ -14284,7 +14542,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:D4" xr:uid="{BA60F202-06F6-4430-911F-CE81B59CEF26}"/>
-  <phoneticPr fontId="15"/>
+  <phoneticPr fontId="17"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -14317,7 +14575,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="28" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -14325,16 +14583,16 @@
     </row>
     <row r="4" spans="1:6" ht="19.5" thickBot="1">
       <c r="A4" s="12" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>328</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>333</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>88</v>
@@ -14345,16 +14603,16 @@
     </row>
     <row r="5" spans="1:6" ht="94.5" thickTop="1">
       <c r="A5" s="16" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>329</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>334</v>
       </c>
       <c r="E5" s="21"/>
       <c r="F5" s="21">
@@ -14363,19 +14621,19 @@
     </row>
     <row r="6" spans="1:6" ht="93.75">
       <c r="A6" s="23" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="F6" s="24">
         <v>0.7</v>
@@ -14383,16 +14641,16 @@
     </row>
     <row r="7" spans="1:6" ht="112.5">
       <c r="A7" s="23" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="24">
@@ -14401,19 +14659,19 @@
     </row>
     <row r="8" spans="1:6" ht="56.25">
       <c r="A8" s="23" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F8" s="24">
         <v>0.05</v>
@@ -14421,19 +14679,19 @@
     </row>
     <row r="9" spans="1:6" ht="112.5">
       <c r="A9" s="23" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="F9" s="24">
         <v>0.05</v>
@@ -14441,16 +14699,16 @@
     </row>
     <row r="10" spans="1:6" ht="56.25">
       <c r="A10" s="23" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E10" s="24"/>
       <c r="F10" s="24">
@@ -14459,19 +14717,19 @@
     </row>
     <row r="11" spans="1:6" ht="75">
       <c r="A11" s="23" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="F11" s="24">
         <v>0.05</v>
@@ -14503,7 +14761,7 @@
       <sortCondition descending="1" ref="F4"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="14"/>
+  <phoneticPr fontId="16"/>
   <pageMargins left="0.23622047244094491" right="0" top="0.62992125984251968" bottom="0.62992125984251968" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -14520,7 +14778,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L41"/>
+  <dimension ref="B2:L42"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -14532,12 +14790,12 @@
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="25" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="2:3">
@@ -14545,32 +14803,32 @@
         <v>1</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="C8" s="32" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="2:3">
-      <c r="C9" s="38" t="s">
-        <v>387</v>
+      <c r="C9" s="36" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" s="32" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="2:3">
-      <c r="C11" s="38" t="s">
-        <v>450</v>
+      <c r="C11" s="36" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="2:3">
@@ -14581,12 +14839,12 @@
         <v>2</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="2:3">
@@ -14594,17 +14852,17 @@
         <v>3</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="C18" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="C19" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="2:3">
@@ -14612,12 +14870,12 @@
         <v>4</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="C22" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="2:3">
@@ -14625,12 +14883,12 @@
         <v>5</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="C25" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="2:3">
@@ -14641,17 +14899,17 @@
         <v>6</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="2:3">
       <c r="C28" s="26" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="C29" s="26" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="2:3">
@@ -14659,17 +14917,17 @@
         <v>7</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="2:3">
       <c r="C32" s="26" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="2:12">
       <c r="C33" s="26" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -14680,12 +14938,12 @@
         <v>8</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="36" spans="2:12">
       <c r="C36" s="29" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="38" spans="2:12">
@@ -14693,30 +14951,35 @@
         <v>9</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" spans="2:12">
-      <c r="C39" s="2" t="s">
-        <v>292</v>
+      <c r="C39" s="39" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="40" spans="2:12">
-      <c r="C40" s="2" t="s">
-        <v>293</v>
+      <c r="C40" s="40" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="41" spans="2:12">
-      <c r="K41" s="35" t="s">
-        <v>396</v>
-      </c>
-      <c r="L41" s="34">
+      <c r="C41" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12">
+      <c r="K42" s="35" t="s">
+        <v>388</v>
+      </c>
+      <c r="L42" s="34">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46264</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="14"/>
+  <phoneticPr fontId="16"/>
   <hyperlinks>
     <hyperlink ref="C36" r:id="rId1" xr:uid="{02BDDA31-576A-4688-8EFA-472077AEE200}"/>
   </hyperlinks>
